--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E1"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -423,26 +423,9 @@
         <v>备注</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>2026-09-17</v>
-      </c>
-      <c r="B2" t="str">
-        <v>2026-09-17</v>
-      </c>
-      <c r="C2" t="str">
-        <v>test</v>
-      </c>
-      <c r="D2" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E2" t="str">
-        <v/>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E13"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -423,9 +423,213 @@
         <v>备注</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>2022-10-16</v>
+      </c>
+      <c r="B2" t="str">
+        <v>2024-11-15</v>
+      </c>
+      <c r="C2" t="str">
+        <v>松江区启民苑20栋201</v>
+      </c>
+      <c r="D2" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2021-10-31</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2022-10-31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>松江区启民苑15号楼102</v>
+      </c>
+      <c r="D3" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>2020-08-09</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2021-11-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>宝山区和家欣苑B区40-201</v>
+      </c>
+      <c r="D4" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>2017-06-15</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2020-06-15</v>
+      </c>
+      <c r="C5" t="str">
+        <v>北京华严北里小区59-6-501</v>
+      </c>
+      <c r="D5" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>2016-07-16</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2017-07-16</v>
+      </c>
+      <c r="C6" t="str">
+        <v>北京清河清缘东里8-B102</v>
+      </c>
+      <c r="D6" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>2015-05-18</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2016-07-16</v>
+      </c>
+      <c r="C7" t="str">
+        <v>永泰东里16-6-601</v>
+      </c>
+      <c r="D7" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E7" t="str">
+        <v>11500</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>2014-05-18</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2015-05-18</v>
+      </c>
+      <c r="C8" t="str">
+        <v>永泰庄22-2-301</v>
+      </c>
+      <c r="D8" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E8" t="str">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2014-03-20</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2014-05-18</v>
+      </c>
+      <c r="C9" t="str">
+        <v>清缘商厦</v>
+      </c>
+      <c r="D9" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>2013-06-07</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C10" t="str">
+        <v>青海·海石湾</v>
+      </c>
+      <c r="D10" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="C11" t="str">
+        <v>北京清河永泰庄新地标32-12</v>
+      </c>
+      <c r="D11" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C12" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D12" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C13" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D13" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E13" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -425,13 +425,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2022-10-16</v>
+        <v>2024-11-15</v>
       </c>
       <c r="B2" t="str">
-        <v>2024-11-15</v>
+        <v>2026-09-17</v>
       </c>
       <c r="C2" t="str">
-        <v>松江区启民苑20栋201</v>
+        <v>松江区启民苑19栋1402</v>
       </c>
       <c r="D2" t="str">
         <v>居住</v>
@@ -442,13 +442,13 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2021-10-31</v>
+        <v>2022-10-16</v>
       </c>
       <c r="B3" t="str">
-        <v>2022-10-31</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C3" t="str">
-        <v>松江区启民苑15号楼102</v>
+        <v>松江区启民苑20栋201</v>
       </c>
       <c r="D3" t="str">
         <v>居住</v>
@@ -459,13 +459,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2020-08-09</v>
+        <v>2021-10-31</v>
       </c>
       <c r="B4" t="str">
-        <v>2021-11-01</v>
+        <v>2022-10-31</v>
       </c>
       <c r="C4" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>松江区启民苑15号楼102</v>
       </c>
       <c r="D4" t="str">
         <v>居住</v>
@@ -476,13 +476,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2017-06-15</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B5" t="str">
-        <v>2020-06-15</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C5" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D5" t="str">
         <v>居住</v>
@@ -493,13 +493,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2016-07-16</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B6" t="str">
-        <v>2017-07-16</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C6" t="str">
-        <v>北京清河清缘东里8-B102</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D6" t="str">
         <v>居住</v>
@@ -510,67 +510,67 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2015-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="B7" t="str">
-        <v>2016-07-16</v>
+        <v>2017-07-16</v>
       </c>
       <c r="C7" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>北京清河清缘东里8-B102</v>
       </c>
       <c r="D7" t="str">
         <v>居住</v>
       </c>
       <c r="E7" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B8" t="str">
-        <v>2015-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C8" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D8" t="str">
         <v>居住</v>
       </c>
       <c r="E8" t="str">
-        <v>10400</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2014-03-20</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B9" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C9" t="str">
-        <v>清缘商厦</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D9" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2013-06-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B10" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C10" t="str">
-        <v>青海·海石湾</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D10" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -578,13 +578,13 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2012-12-07</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B11" t="str">
-        <v>2013-06-08</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C11" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D11" t="str">
         <v>居住</v>
@@ -595,13 +595,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2012-02-07</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B12" t="str">
-        <v>2012-11-29</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C12" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D12" t="str">
         <v>居住</v>
@@ -612,24 +612,41 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C13" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D13" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
         <v>2010-07-20</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B14" t="str">
         <v>2012-02-01</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C14" t="str">
         <v>北京清河宝盛西里</v>
       </c>
-      <c r="D13" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E13" t="str">
+      <c r="D14" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E14" t="str">
         <v>宿舍</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -570,7 +570,7 @@
         <v>清缘商厦</v>
       </c>
       <c r="D10" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E10" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -493,30 +493,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2017-06-15</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B6" t="str">
-        <v>2020-06-15</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C6" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>待业</v>
       </c>
       <c r="D6" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2016-07-16</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B7" t="str">
-        <v>2017-07-16</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C7" t="str">
-        <v>北京清河清缘东里8-B102</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D7" t="str">
         <v>居住</v>
@@ -527,81 +527,81 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2015-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="B8" t="str">
-        <v>2016-07-16</v>
+        <v>2017-07-16</v>
       </c>
       <c r="C8" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>北京清河清缘东里8-B102</v>
       </c>
       <c r="D8" t="str">
         <v>居住</v>
       </c>
       <c r="E8" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2014-05-18</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B9" t="str">
-        <v>2015-05-18</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C9" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>待业</v>
       </c>
       <c r="D9" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E9" t="str">
-        <v>10400</v>
+        <v>343天</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2014-03-20</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B10" t="str">
-        <v>2014-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C10" t="str">
-        <v>清缘商厦</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D10" t="str">
         <v>居住</v>
       </c>
       <c r="E10" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2013-06-07</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B11" t="str">
-        <v>2013-09-16</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C11" t="str">
-        <v>青海·海石湾</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D11" t="str">
         <v>居住</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2012-12-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B12" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C12" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D12" t="str">
         <v>居住</v>
@@ -612,41 +612,92 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2012-02-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B13" t="str">
-        <v>2012-11-29</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C13" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>待业</v>
       </c>
       <c r="D13" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
+        <v>2013-06-07</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C14" t="str">
+        <v>青海·海石湾</v>
+      </c>
+      <c r="D14" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="C15" t="str">
+        <v>北京清河永泰庄新地标32-12</v>
+      </c>
+      <c r="D15" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C16" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D16" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
         <v>2010-07-20</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B17" t="str">
         <v>2012-02-01</v>
       </c>
-      <c r="C14" t="str">
+      <c r="C17" t="str">
         <v>北京清河宝盛西里</v>
       </c>
-      <c r="D14" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E14" t="str">
+      <c r="D17" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E17" t="str">
         <v>宿舍</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -499,7 +499,7 @@
         <v>2020-11-01</v>
       </c>
       <c r="C6" t="str">
-        <v>待业</v>
+        <v>待业155天</v>
       </c>
       <c r="D6" t="str">
         <v>其他</v>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -550,7 +550,7 @@
         <v>2017-03-12</v>
       </c>
       <c r="C9" t="str">
-        <v>待业</v>
+        <v>待业343天</v>
       </c>
       <c r="D9" t="str">
         <v>其他</v>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -618,7 +618,7 @@
         <v>2014-03-26</v>
       </c>
       <c r="C13" t="str">
-        <v>待业</v>
+        <v>待业291天</v>
       </c>
       <c r="D13" t="str">
         <v>其他</v>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E33"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -578,33 +578,33 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2014-05-18</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B11" t="str">
-        <v>2015-05-18</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C11" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D11" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E11" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B12" t="str">
-        <v>2014-05-18</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C12" t="str">
-        <v>清缘商厦</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D12" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,50 +612,50 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2013-06-08</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B13" t="str">
-        <v>2014-03-26</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C13" t="str">
-        <v>待业291天</v>
+        <v>青海聚 五姨</v>
       </c>
       <c r="D13" t="str">
         <v>其他</v>
       </c>
       <c r="E13" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2013-06-07</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B14" t="str">
-        <v>2013-09-16</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C14" t="str">
-        <v>青海·海石湾</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D14" t="str">
         <v>居住</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2012-12-07</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B15" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C15" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>青海聚</v>
       </c>
       <c r="D15" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2012-02-07</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B16" t="str">
-        <v>2012-11-29</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C16" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D16" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,24 +680,296 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
+        <v>2014-03-20</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2014-05-18</v>
+      </c>
+      <c r="C17" t="str">
+        <v>清缘商厦</v>
+      </c>
+      <c r="D17" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2014-03-20</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2014-03-22</v>
+      </c>
+      <c r="C18" t="str">
+        <v>上海韩后全智贤</v>
+      </c>
+      <c r="D18" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2013-11-26</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2013-11-26</v>
+      </c>
+      <c r="C19" t="str">
+        <v>大连和s小聚</v>
+      </c>
+      <c r="D19" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2013-06-11</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C20" t="str">
+        <v>青海聚</v>
+      </c>
+      <c r="D20" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2014-03-26</v>
+      </c>
+      <c r="C21" t="str">
+        <v>待业291天</v>
+      </c>
+      <c r="D21" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E21" t="str">
+        <v>291天</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2013-06-07</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C22" t="str">
+        <v>青海·海石湾</v>
+      </c>
+      <c r="D22" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2013-02</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2013-02</v>
+      </c>
+      <c r="C23" t="str">
+        <v>不详s至青海转乘 北京聚</v>
+      </c>
+      <c r="D23" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="C24" t="str">
+        <v>北京清河永泰庄新地标32-12</v>
+      </c>
+      <c r="D24" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="C25" t="str">
+        <v>北京送返鸡西</v>
+      </c>
+      <c r="D25" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C26" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D26" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C27" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D27" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C28" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D28" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C29" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D29" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v>2010-07-20</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B30" t="str">
         <v>2012-02-01</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C30" t="str">
         <v>北京清河宝盛西里</v>
       </c>
-      <c r="D17" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E17" t="str">
+      <c r="D30" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E30" t="str">
         <v>宿舍</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2010-07</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2011-12</v>
+      </c>
+      <c r="C31" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D31" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2010-06</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2010-06</v>
+      </c>
+      <c r="C32" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D32" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2010-01</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2010-01</v>
+      </c>
+      <c r="C33" t="str">
+        <v>YY语音相识·若</v>
+      </c>
+      <c r="D33" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -621,7 +621,7 @@
         <v>青海聚 五姨</v>
       </c>
       <c r="D13" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E13" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -655,7 +655,7 @@
         <v>青海聚</v>
       </c>
       <c r="D15" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E15" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -706,7 +706,7 @@
         <v>上海韩后全智贤</v>
       </c>
       <c r="D18" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E18" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -740,7 +740,7 @@
         <v>青海聚</v>
       </c>
       <c r="D20" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E20" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -927,7 +927,7 @@
         <v>北京北大青鸟</v>
       </c>
       <c r="D31" t="str">
-        <v>其他</v>
+        <v>学业</v>
       </c>
       <c r="E31" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -944,7 +944,7 @@
         <v>高考</v>
       </c>
       <c r="D32" t="str">
-        <v>其他</v>
+        <v>学业</v>
       </c>
       <c r="E32" t="str">
         <v/>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E32"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -612,50 +612,50 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2014-10-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B13" t="str">
-        <v>2014-10-01</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C13" t="str">
-        <v>青海聚 五姨</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D13" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2014-05-18</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B14" t="str">
-        <v>2015-05-18</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C14" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>青海聚</v>
       </c>
       <c r="D14" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E14" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2014-05-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B15" t="str">
-        <v>2014-05-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C15" t="str">
-        <v>青海聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D15" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2014-03-27</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B16" t="str">
-        <v>2014-03-27</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C16" t="str">
-        <v>二次入职世代泉源</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D16" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -683,13 +683,13 @@
         <v>2014-03-20</v>
       </c>
       <c r="B17" t="str">
-        <v>2014-05-18</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C17" t="str">
-        <v>清缘商厦</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D17" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -697,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2014-03-20</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B18" t="str">
-        <v>2014-03-22</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C18" t="str">
-        <v>上海韩后全智贤</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D18" t="str">
-        <v>观演</v>
+        <v>其他</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2013-11-26</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B19" t="str">
-        <v>2013-11-26</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C19" t="str">
-        <v>大连和s小聚</v>
+        <v>青海聚</v>
       </c>
       <c r="D19" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,50 +731,50 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2013-06-11</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B20" t="str">
-        <v>2013-09-16</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C20" t="str">
-        <v>青海聚</v>
+        <v>待业291天</v>
       </c>
       <c r="D20" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E20" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2013-06-08</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B21" t="str">
-        <v>2014-03-26</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C21" t="str">
-        <v>待业291天</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D21" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E21" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2013-06-07</v>
+        <v>2013-02</v>
       </c>
       <c r="B22" t="str">
-        <v>2013-09-16</v>
+        <v>2013-02</v>
       </c>
       <c r="C22" t="str">
-        <v>青海·海石湾</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D22" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2013-02</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B23" t="str">
-        <v>2013-02</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C23" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D23" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2012-12-07</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B24" t="str">
-        <v>2013-06-08</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C24" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D24" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,16 +816,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2012-11-04</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B25" t="str">
-        <v>2012-11-04</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C25" t="str">
-        <v>北京送返鸡西</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D25" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2012-09-24</v>
+        <v>2012-08-21</v>
       </c>
       <c r="B26" t="str">
-        <v>2012-09-24</v>
+        <v>2012-08-23</v>
       </c>
       <c r="C26" t="str">
-        <v>入职世代泉源</v>
+        <v>辽宁兴城</v>
       </c>
       <c r="D26" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,13 +850,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2012-08-21</v>
+        <v>2012-02-07</v>
       </c>
       <c r="B27" t="str">
-        <v>2012-08-23</v>
+        <v>2012-11-29</v>
       </c>
       <c r="C27" t="str">
-        <v>辽宁兴城</v>
+        <v>北京清河永泰庄新地标31-9-5</v>
       </c>
       <c r="D27" t="str">
         <v>居住</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2012-02-07</v>
+        <v>2012-02-01</v>
       </c>
       <c r="B28" t="str">
-        <v>2012-11-29</v>
+        <v>2012-02-01</v>
       </c>
       <c r="C28" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>北京接站sister</v>
       </c>
       <c r="D28" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -884,47 +884,47 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2012-02-01</v>
+        <v>2010-07-20</v>
       </c>
       <c r="B29" t="str">
         <v>2012-02-01</v>
       </c>
       <c r="C29" t="str">
-        <v>北京接站sister</v>
+        <v>北京清河宝盛西里</v>
       </c>
       <c r="D29" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>宿舍</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2010-07-20</v>
+        <v>2010-07</v>
       </c>
       <c r="B30" t="str">
-        <v>2012-02-01</v>
+        <v>2011-12</v>
       </c>
       <c r="C30" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>北京北大青鸟</v>
       </c>
       <c r="D30" t="str">
-        <v>居住</v>
+        <v>学业</v>
       </c>
       <c r="E30" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2010-07</v>
+        <v>2010-06</v>
       </c>
       <c r="B31" t="str">
-        <v>2011-12</v>
+        <v>2010-06</v>
       </c>
       <c r="C31" t="str">
-        <v>北京北大青鸟</v>
+        <v>高考</v>
       </c>
       <c r="D31" t="str">
         <v>学业</v>
@@ -935,41 +935,24 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2010-06</v>
+        <v>2010-01</v>
       </c>
       <c r="B32" t="str">
-        <v>2010-06</v>
+        <v>2010-01</v>
       </c>
       <c r="C32" t="str">
-        <v>高考</v>
+        <v>YY语音相识·若</v>
       </c>
       <c r="D32" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>2010-01</v>
-      </c>
-      <c r="B33" t="str">
-        <v>2010-01</v>
-      </c>
-      <c r="C33" t="str">
-        <v>YY语音相识·若</v>
-      </c>
-      <c r="D33" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E33" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -612,50 +612,50 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2014-05-18</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B13" t="str">
-        <v>2015-05-18</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C13" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D13" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E13" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2014-05-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B14" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C14" t="str">
-        <v>青海聚</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D14" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E14" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2014-03-27</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B15" t="str">
-        <v>2014-03-27</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C15" t="str">
-        <v>二次入职世代泉源</v>
+        <v>青海聚</v>
       </c>
       <c r="D15" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2014-03-20</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B16" t="str">
-        <v>2014-05-18</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C16" t="str">
-        <v>清缘商厦</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D16" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -683,13 +683,13 @@
         <v>2014-03-20</v>
       </c>
       <c r="B17" t="str">
-        <v>2014-03-22</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C17" t="str">
-        <v>上海韩后全智贤</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D17" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -697,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2013-11-26</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B18" t="str">
-        <v>2013-11-26</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C18" t="str">
-        <v>大连和s小聚</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D18" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2013-06-11</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B19" t="str">
-        <v>2013-09-16</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C19" t="str">
-        <v>青海聚</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D19" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,50 +731,50 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2013-06-08</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B20" t="str">
-        <v>2014-03-26</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C20" t="str">
-        <v>待业291天</v>
+        <v>青海聚</v>
       </c>
       <c r="D20" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E20" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2013-06-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B21" t="str">
-        <v>2013-09-16</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C21" t="str">
-        <v>青海·海石湾</v>
+        <v>待业291天</v>
       </c>
       <c r="D21" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E21" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2013-02</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B22" t="str">
-        <v>2013-02</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C22" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D22" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2012-12-07</v>
+        <v>2013-02</v>
       </c>
       <c r="B23" t="str">
-        <v>2013-06-08</v>
+        <v>2013-02</v>
       </c>
       <c r="C23" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D23" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2012-11-04</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B24" t="str">
-        <v>2012-11-04</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C24" t="str">
-        <v>北京送返鸡西</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D24" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,16 +816,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2012-09-24</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B25" t="str">
-        <v>2012-09-24</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C25" t="str">
-        <v>入职世代泉源</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D25" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2012-08-21</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B26" t="str">
-        <v>2012-08-23</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C26" t="str">
-        <v>辽宁兴城</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D26" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,13 +850,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2012-02-07</v>
+        <v>2012-08-21</v>
       </c>
       <c r="B27" t="str">
-        <v>2012-11-29</v>
+        <v>2012-08-23</v>
       </c>
       <c r="C27" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>辽宁兴城</v>
       </c>
       <c r="D27" t="str">
         <v>居住</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2012-02-01</v>
+        <v>2012-02-07</v>
       </c>
       <c r="B28" t="str">
-        <v>2012-02-01</v>
+        <v>2012-11-29</v>
       </c>
       <c r="C28" t="str">
-        <v>北京接站sister</v>
+        <v>北京清河永泰庄新地标31-9-5</v>
       </c>
       <c r="D28" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -884,47 +884,47 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2010-07-20</v>
+        <v>2012-02-01</v>
       </c>
       <c r="B29" t="str">
         <v>2012-02-01</v>
       </c>
       <c r="C29" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>北京接站sister</v>
       </c>
       <c r="D29" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E29" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2010-07</v>
+        <v>2010-07-20</v>
       </c>
       <c r="B30" t="str">
-        <v>2011-12</v>
+        <v>2012-02-01</v>
       </c>
       <c r="C30" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京清河宝盛西里</v>
       </c>
       <c r="D30" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>宿舍</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2010-06</v>
+        <v>2010-07</v>
       </c>
       <c r="B31" t="str">
-        <v>2010-06</v>
+        <v>2011-12</v>
       </c>
       <c r="C31" t="str">
-        <v>高考</v>
+        <v>北京北大青鸟</v>
       </c>
       <c r="D31" t="str">
         <v>学业</v>
@@ -935,24 +935,41 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
+        <v>2010-06</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2010-06</v>
+      </c>
+      <c r="C32" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D32" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
         <v>2010-01</v>
       </c>
-      <c r="B32" t="str">
+      <c r="B33" t="str">
         <v>2010-01</v>
       </c>
-      <c r="C32" t="str">
+      <c r="C33" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D32" t="str">
+      <c r="D33" t="str">
         <v>其他</v>
       </c>
-      <c r="E32" t="str">
+      <c r="E33" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E32"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E33"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -428,7 +428,7 @@
         <v>2024-11-15</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C2" t="str">
         <v>松江区启民苑19栋1402</v>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2013-02</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B23" t="str">
-        <v>2013-02</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C23" t="str">
         <v>不详s至青海转乘 北京聚</v>
@@ -918,10 +918,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2010-07</v>
+        <v>2010-07-01</v>
       </c>
       <c r="B31" t="str">
-        <v>2011-12</v>
+        <v>2011-12-01</v>
       </c>
       <c r="C31" t="str">
         <v>北京北大青鸟</v>
@@ -935,10 +935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2010-06</v>
+        <v>2010-06-01</v>
       </c>
       <c r="B32" t="str">
-        <v>2010-06</v>
+        <v>2010-06-01</v>
       </c>
       <c r="C32" t="str">
         <v>高考</v>
@@ -952,10 +952,10 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2010-01</v>
+        <v>2010-01-01</v>
       </c>
       <c r="B33" t="str">
-        <v>2010-01</v>
+        <v>2010-01-01</v>
       </c>
       <c r="C33" t="str">
         <v>YY语音相识·若</v>

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E40"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -561,30 +561,30 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2015-05-18</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B10" t="str">
-        <v>2016-07-16</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C10" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D10" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E10" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2014-11-21</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B11" t="str">
-        <v>2014-11-23</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C11" t="str">
-        <v>天津旅游s</v>
+        <v>大连 s</v>
       </c>
       <c r="D11" t="str">
         <v>旅行</v>
@@ -595,16 +595,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2014-11-10</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B12" t="str">
-        <v>2014-11-30</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C12" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连 s</v>
       </c>
       <c r="D12" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,13 +612,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B13" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C13" t="str">
-        <v>青海聚五姨</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D13" t="str">
         <v>旅行</v>
@@ -629,30 +629,30 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B14" t="str">
-        <v>2015-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C14" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D14" t="str">
         <v>居住</v>
       </c>
       <c r="E14" t="str">
-        <v>10400</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B15" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C15" t="str">
-        <v>青海聚</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D15" t="str">
         <v>旅行</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B16" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C16" t="str">
-        <v>二次入职世代泉源</v>
+        <v>大连 s</v>
       </c>
       <c r="D16" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,16 +680,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2014-03-20</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B17" t="str">
-        <v>2014-05-18</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C17" t="str">
-        <v>清缘商厦</v>
+        <v>北京接 s</v>
       </c>
       <c r="D17" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -697,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B18" t="str">
-        <v>2014-03-22</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C18" t="str">
-        <v>上海韩后全智贤</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D18" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -714,13 +714,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B19" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C19" t="str">
-        <v>大连和s小聚</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D19" t="str">
         <v>其他</v>
@@ -731,13 +731,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2013-06-11</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B20" t="str">
-        <v>2013-09-16</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C20" t="str">
-        <v>青海聚</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D20" t="str">
         <v>旅行</v>
@@ -748,33 +748,33 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B21" t="str">
-        <v>2014-03-26</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C21" t="str">
-        <v>待业291天</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D21" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E21" t="str">
-        <v>291天</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2013-06-07</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B22" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C22" t="str">
-        <v>青海·海石湾</v>
+        <v>青海聚</v>
       </c>
       <c r="D22" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B23" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C23" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D23" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2012-12-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B24" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C24" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D24" t="str">
         <v>居住</v>
@@ -816,16 +816,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B25" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C25" t="str">
-        <v>北京送返鸡西</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D25" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2012-09-24</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B26" t="str">
-        <v>2012-09-24</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C26" t="str">
-        <v>入职世代泉源</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D26" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,16 +850,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2012-08-21</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B27" t="str">
-        <v>2012-08-23</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C27" t="str">
-        <v>辽宁兴城</v>
+        <v>青海聚</v>
       </c>
       <c r="D27" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -867,33 +867,33 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2012-02-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B28" t="str">
-        <v>2012-11-29</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C28" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>待业291天</v>
       </c>
       <c r="D28" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2012-02-01</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B29" t="str">
-        <v>2012-02-01</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C29" t="str">
-        <v>北京接站sister</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D29" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -901,33 +901,33 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2010-07-20</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B30" t="str">
-        <v>2012-02-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C30" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D30" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E30" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2010-07-01</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B31" t="str">
-        <v>2011-12-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C31" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D31" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -935,16 +935,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B32" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C32" t="str">
-        <v>高考</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D32" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -952,24 +952,143 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C33" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D33" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C34" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D34" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C35" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D35" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C36" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D36" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C37" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D37" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E37" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C38" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D38" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C39" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D39" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B40" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C33" t="str">
+      <c r="C40" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D33" t="str">
+      <c r="D40" t="str">
         <v>其他</v>
       </c>
-      <c r="E33" t="str">
+      <c r="E40" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E40"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E47"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -527,16 +527,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2016-07-16</v>
+        <v>2016-12-23</v>
       </c>
       <c r="B8" t="str">
-        <v>2017-07-16</v>
+        <v>2017-01-08</v>
       </c>
       <c r="C8" t="str">
-        <v>北京清河清缘东里8-B102</v>
+        <v>武汉·徐东</v>
       </c>
       <c r="D8" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -544,33 +544,33 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2016-04-03</v>
+        <v>2016-10-07</v>
       </c>
       <c r="B9" t="str">
-        <v>2017-03-12</v>
+        <v>2016-10-14</v>
       </c>
       <c r="C9" t="str">
-        <v>待业343天</v>
+        <v>武汉</v>
       </c>
       <c r="D9" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E9" t="str">
-        <v>343天</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2015-12-31</v>
+        <v>2016-10-01</v>
       </c>
       <c r="B10" t="str">
-        <v>2015-12-31</v>
+        <v>2016-10-07</v>
       </c>
       <c r="C10" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
+        <v>兰州 陇南 天水</v>
       </c>
       <c r="D10" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2015-10-01</v>
+        <v>2016-07-16</v>
       </c>
       <c r="B11" t="str">
-        <v>2015-10-07</v>
+        <v>2017-07-16</v>
       </c>
       <c r="C11" t="str">
-        <v>大连 s</v>
+        <v>北京清河清缘东里8-B102</v>
       </c>
       <c r="D11" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,13 +595,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2015-06-09</v>
+        <v>2016-07-06</v>
       </c>
       <c r="B12" t="str">
-        <v>2015-06-14</v>
+        <v>2016-07-13</v>
       </c>
       <c r="C12" t="str">
-        <v>大连 s</v>
+        <v>武汉·游</v>
       </c>
       <c r="D12" t="str">
         <v>旅行</v>
@@ -612,16 +612,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2015-06-06</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B13" t="str">
-        <v>2015-06-08</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C13" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D13" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -629,50 +629,50 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2015-05-18</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B14" t="str">
-        <v>2016-07-16</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C14" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D14" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E14" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2015-05-01</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B15" t="str">
-        <v>2015-05-03</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C15" t="str">
-        <v>大连·游 s</v>
+        <v>待业343天</v>
       </c>
       <c r="D15" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2015-03-28</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B16" t="str">
-        <v>2015-03-29</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C16" t="str">
-        <v>大连 s</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D16" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,16 +680,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2015-03-27</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B17" t="str">
-        <v>2015-03-27</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C17" t="str">
-        <v>北京接 s</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D17" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -697,13 +697,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2014-11-21</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B18" t="str">
-        <v>2014-11-23</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C18" t="str">
-        <v>天津旅游s</v>
+        <v>大连 s</v>
       </c>
       <c r="D18" t="str">
         <v>旅行</v>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2014-11-10</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B19" t="str">
-        <v>2014-11-30</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C19" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连 s</v>
       </c>
       <c r="D19" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,13 +731,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B20" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C20" t="str">
-        <v>青海聚五姨</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D20" t="str">
         <v>旅行</v>
@@ -748,30 +748,30 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B21" t="str">
-        <v>2015-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C21" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D21" t="str">
         <v>居住</v>
       </c>
       <c r="E21" t="str">
-        <v>10400</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B22" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C22" t="str">
-        <v>青海聚</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D22" t="str">
         <v>旅行</v>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B23" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C23" t="str">
-        <v>二次入职世代泉源</v>
+        <v>大连 s</v>
       </c>
       <c r="D23" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2014-03-20</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B24" t="str">
-        <v>2014-05-18</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C24" t="str">
-        <v>清缘商厦</v>
+        <v>北京接 s</v>
       </c>
       <c r="D24" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,16 +816,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B25" t="str">
-        <v>2014-03-22</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C25" t="str">
-        <v>上海韩后全智贤</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D25" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -833,13 +833,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B26" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C26" t="str">
-        <v>大连和s小聚</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D26" t="str">
         <v>其他</v>
@@ -850,13 +850,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2013-06-11</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B27" t="str">
-        <v>2013-09-16</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C27" t="str">
-        <v>青海聚</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D27" t="str">
         <v>旅行</v>
@@ -867,33 +867,33 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B28" t="str">
-        <v>2014-03-26</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C28" t="str">
-        <v>待业291天</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D28" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E28" t="str">
-        <v>291天</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2013-06-07</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B29" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C29" t="str">
-        <v>青海·海石湾</v>
+        <v>青海聚</v>
       </c>
       <c r="D29" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -901,16 +901,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B30" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C30" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D30" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -918,13 +918,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2012-12-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B31" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C31" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D31" t="str">
         <v>居住</v>
@@ -935,16 +935,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B32" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C32" t="str">
-        <v>北京送返鸡西</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D32" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -952,16 +952,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2012-09-24</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B33" t="str">
-        <v>2012-09-24</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C33" t="str">
-        <v>入职世代泉源</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D33" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -969,16 +969,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2012-08-21</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B34" t="str">
-        <v>2012-08-23</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C34" t="str">
-        <v>辽宁兴城</v>
+        <v>青海聚</v>
       </c>
       <c r="D34" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -986,33 +986,33 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2012-02-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B35" t="str">
-        <v>2012-11-29</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C35" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>待业291天</v>
       </c>
       <c r="D35" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E35" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2012-02-01</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B36" t="str">
-        <v>2012-02-01</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C36" t="str">
-        <v>北京接站sister</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D36" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1020,33 +1020,33 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2010-07-20</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B37" t="str">
-        <v>2012-02-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C37" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D37" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E37" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2010-07-01</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B38" t="str">
-        <v>2011-12-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C38" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D38" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B39" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C39" t="str">
-        <v>高考</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D39" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1071,24 +1071,143 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C40" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D40" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C41" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D41" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C42" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D42" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C43" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D43" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C44" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D44" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E44" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C45" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D45" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C46" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D46" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B40" t="str">
+      <c r="B47" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C40" t="str">
+      <c r="C47" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D40" t="str">
+      <c r="D47" t="str">
         <v>其他</v>
       </c>
-      <c r="E40" t="str">
+      <c r="E47" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E40"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E47"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -593,7 +593,7 @@
         <v/>
       </c>
     </row>
-    <row r="12">
+    <row r="12" xml:space="preserve">
       <c r="A12" t="str">
         <v>2016-07-06</v>
       </c>
@@ -606,8 +606,10 @@
       <c r="D12" t="str">
         <v>旅行</v>
       </c>
-      <c r="E12" t="str">
-        <v/>
+      <c r="E12" t="str" xml:space="preserve">
+        <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
+┣ 20160707 四季如家(徐东大街店)/1晚
+┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
     <row r="13">

--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E61"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -510,16 +510,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2017-06-15</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B7" t="str">
-        <v>2020-06-15</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C7" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>上海·路演</v>
       </c>
       <c r="D7" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -527,47 +527,47 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2016-12-23</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B8" t="str">
-        <v>2017-01-08</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C8" t="str">
-        <v>武汉·徐东</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D8" t="str">
         <v>旅行</v>
       </c>
       <c r="E8" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2016-10-07</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B9" t="str">
-        <v>2016-10-14</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C9" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D9" t="str">
         <v>旅行</v>
       </c>
       <c r="E9" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2016-10-01</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B10" t="str">
-        <v>2016-10-07</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C10" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D10" t="str">
         <v>旅行</v>
@@ -578,27 +578,27 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2016-07-16</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>2017-07-16</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C11" t="str">
-        <v>北京清河清缘东里8-B102</v>
+        <v>萌 北京</v>
       </c>
       <c r="D11" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
     </row>
-    <row r="12" xml:space="preserve">
+    <row r="12">
       <c r="A12" t="str">
-        <v>2016-07-06</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B12" t="str">
-        <v>2016-07-13</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C12" t="str">
         <v>武汉·游</v>
@@ -606,262 +606,262 @@
       <c r="D12" t="str">
         <v>旅行</v>
       </c>
-      <c r="E12" t="str" xml:space="preserve">
+      <c r="E12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>2017-08-18</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2017-08-20</v>
+      </c>
+      <c r="C13" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D13" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>2017-08-11</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2017-08-13</v>
+      </c>
+      <c r="C14" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D14" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E14" t="str">
+        <v>大聚会</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>2017-08-04</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2017-08-07</v>
+      </c>
+      <c r="C15" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D15" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>2017-06-15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2020-06-15</v>
+      </c>
+      <c r="C16" t="str">
+        <v>北京华严北里小区59-6-501</v>
+      </c>
+      <c r="D16" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>2017-06-10</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2017-06-11</v>
+      </c>
+      <c r="C17" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D17" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>2017-05-28</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2017-05-30</v>
+      </c>
+      <c r="C18" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D18" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>2017-04-29</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2017-05-01</v>
+      </c>
+      <c r="C19" t="str">
+        <v>大连 s</v>
+      </c>
+      <c r="D19" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C20" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D20" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C21" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D21" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C22" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D22" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C23" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D23" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C24" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D24" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>2016-07-16</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2017-07-16</v>
+      </c>
+      <c r="C25" t="str">
+        <v>北京清河清缘东里8-B102</v>
+      </c>
+      <c r="D25" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>2016-07-06</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2016-07-13</v>
+      </c>
+      <c r="C26" t="str">
+        <v>武汉·游</v>
+      </c>
+      <c r="D26" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E26" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C13" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D13" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C14" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D14" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C15" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D15" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E15" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C16" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D16" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B17" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C17" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D17" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>2015-10-01</v>
-      </c>
-      <c r="B18" t="str">
-        <v>2015-10-07</v>
-      </c>
-      <c r="C18" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D18" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>2015-06-09</v>
-      </c>
-      <c r="B19" t="str">
-        <v>2015-06-14</v>
-      </c>
-      <c r="C19" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D19" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>2015-06-06</v>
-      </c>
-      <c r="B20" t="str">
-        <v>2015-06-08</v>
-      </c>
-      <c r="C20" t="str">
-        <v>湘西·凤凰古城</v>
-      </c>
-      <c r="D20" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>2015-05-18</v>
-      </c>
-      <c r="B21" t="str">
-        <v>2016-07-16</v>
-      </c>
-      <c r="C21" t="str">
-        <v>永泰东里16-6-601</v>
-      </c>
-      <c r="D21" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E21" t="str">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>2015-05-01</v>
-      </c>
-      <c r="B22" t="str">
-        <v>2015-05-03</v>
-      </c>
-      <c r="C22" t="str">
-        <v>大连·游 s</v>
-      </c>
-      <c r="D22" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>2015-03-28</v>
-      </c>
-      <c r="B23" t="str">
-        <v>2015-03-29</v>
-      </c>
-      <c r="C23" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D23" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>2015-03-27</v>
-      </c>
-      <c r="B24" t="str">
-        <v>2015-03-27</v>
-      </c>
-      <c r="C24" t="str">
-        <v>北京接 s</v>
-      </c>
-      <c r="D24" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>2014-11-21</v>
-      </c>
-      <c r="B25" t="str">
-        <v>2014-11-23</v>
-      </c>
-      <c r="C25" t="str">
-        <v>天津旅游s</v>
-      </c>
-      <c r="D25" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>2014-11-10</v>
-      </c>
-      <c r="B26" t="str">
-        <v>2014-11-30</v>
-      </c>
-      <c r="C26" t="str">
-        <v>北京转车聚 新地标租房</v>
-      </c>
-      <c r="D26" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E26" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2014-10-01</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B27" t="str">
-        <v>2014-10-01</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C27" t="str">
-        <v>青海聚五姨</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D27" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -869,50 +869,50 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2014-05-18</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B28" t="str">
-        <v>2015-05-18</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C28" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D28" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E28" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2014-05-01</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B29" t="str">
-        <v>2014-05-01</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C29" t="str">
-        <v>青海聚</v>
+        <v>待业343天</v>
       </c>
       <c r="D29" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2014-03-27</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B30" t="str">
-        <v>2014-03-27</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C30" t="str">
-        <v>二次入职世代泉源</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D30" t="str">
-        <v>工作</v>
+        <v>观演</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -920,16 +920,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2014-03-20</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B31" t="str">
-        <v>2014-05-18</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C31" t="str">
-        <v>清缘商厦</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D31" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -937,16 +937,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2014-03-20</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B32" t="str">
-        <v>2014-03-22</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C32" t="str">
-        <v>上海韩后全智贤</v>
+        <v>大连 s</v>
       </c>
       <c r="D32" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -954,16 +954,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2013-11-26</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B33" t="str">
-        <v>2013-11-26</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C33" t="str">
-        <v>大连和s小聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D33" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -971,13 +971,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2013-06-11</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B34" t="str">
-        <v>2013-09-16</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C34" t="str">
-        <v>青海聚</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D34" t="str">
         <v>旅行</v>
@@ -988,33 +988,33 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2013-06-08</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B35" t="str">
-        <v>2014-03-26</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C35" t="str">
-        <v>待业291天</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D35" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E35" t="str">
-        <v>291天</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2013-06-07</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B36" t="str">
-        <v>2013-09-16</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C36" t="str">
-        <v>青海·海石湾</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D36" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1022,16 +1022,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2013-02-01</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B37" t="str">
-        <v>2013-02-01</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C37" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D37" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1039,16 +1039,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2012-12-07</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B38" t="str">
-        <v>2013-06-08</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C38" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>北京接 s</v>
       </c>
       <c r="D38" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1056,16 +1056,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2012-11-04</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B39" t="str">
-        <v>2012-11-04</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C39" t="str">
-        <v>北京送返鸡西</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D39" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1073,16 +1073,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2012-09-24</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B40" t="str">
-        <v>2012-09-24</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C40" t="str">
-        <v>入职世代泉源</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D40" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1090,16 +1090,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2012-08-21</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B41" t="str">
-        <v>2012-08-23</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C41" t="str">
-        <v>辽宁兴城</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D41" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1107,33 +1107,33 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2012-02-07</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B42" t="str">
-        <v>2012-11-29</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C42" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D42" t="str">
         <v>居住</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2012-02-01</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B43" t="str">
-        <v>2012-02-01</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C43" t="str">
-        <v>北京接站sister</v>
+        <v>青海聚</v>
       </c>
       <c r="D43" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1141,33 +1141,33 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2010-07-20</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B44" t="str">
-        <v>2012-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C44" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D44" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E44" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2010-07-01</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B45" t="str">
-        <v>2011-12-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C45" t="str">
-        <v>北京北大青鸟</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D45" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1175,16 +1175,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2010-06-01</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B46" t="str">
-        <v>2010-06-01</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C46" t="str">
-        <v>高考</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D46" t="str">
-        <v>学业</v>
+        <v>观演</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1192,13 +1192,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2010-01-01</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B47" t="str">
-        <v>2010-01-01</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C47" t="str">
-        <v>YY语音相识·若</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D47" t="str">
         <v>其他</v>
@@ -1207,9 +1207,247 @@
         <v/>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2013-06-11</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C48" t="str">
+        <v>青海聚</v>
+      </c>
+      <c r="D48" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2014-03-26</v>
+      </c>
+      <c r="C49" t="str">
+        <v>待业291天</v>
+      </c>
+      <c r="D49" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E49" t="str">
+        <v>291天</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2013-06-07</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C50" t="str">
+        <v>青海·海石湾</v>
+      </c>
+      <c r="D50" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2013-02-01</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2013-02-01</v>
+      </c>
+      <c r="C51" t="str">
+        <v>不详s至青海转乘 北京聚</v>
+      </c>
+      <c r="D51" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="C52" t="str">
+        <v>北京清河永泰庄新地标32-12</v>
+      </c>
+      <c r="D52" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="C53" t="str">
+        <v>北京送返鸡西</v>
+      </c>
+      <c r="D53" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C54" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D54" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C55" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D55" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C56" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D56" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C57" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D57" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C58" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D58" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E58" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C59" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D59" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C60" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D60" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2010-01-01</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2010-01-01</v>
+      </c>
+      <c r="C61" t="str">
+        <v>YY语音相识·若</v>
+      </c>
+      <c r="D61" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E47"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E66"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -510,16 +510,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2017-12-23</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B7" t="str">
-        <v>2017-22-24</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C7" t="str">
-        <v>上海·路演</v>
+        <v>广州·萌</v>
       </c>
       <c r="D7" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -527,47 +527,47 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2017-11-11</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B8" t="str">
-        <v>2017-11-16</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C8" t="str">
-        <v>小熊 北京</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D8" t="str">
         <v>旅行</v>
       </c>
       <c r="E8" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2017-10-10</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B9" t="str">
-        <v>2017-10-17</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C9" t="str">
-        <v>萌 北京</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D9" t="str">
         <v>旅行</v>
       </c>
       <c r="E9" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2017-09-29</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B10" t="str">
-        <v>2017-10-09</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C10" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D10" t="str">
         <v>旅行</v>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2017-09-27</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B11" t="str">
-        <v>2017-09-29</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C11" t="str">
-        <v>萌 北京</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D11" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,16 +595,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2017-09-09</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B12" t="str">
-        <v>2017-09-10</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C12" t="str">
-        <v>武汉·游</v>
+        <v>上海·路演</v>
       </c>
       <c r="D12" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,47 +612,47 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2017-08-18</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B13" t="str">
-        <v>2017-08-20</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C13" t="str">
-        <v>萌 北京</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D13" t="str">
         <v>旅行</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2017-08-11</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B14" t="str">
-        <v>2017-08-13</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C14" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D14" t="str">
         <v>旅行</v>
       </c>
       <c r="E14" t="str">
-        <v>大聚会</v>
+        <v>11:47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2017-08-04</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B15" t="str">
-        <v>2017-08-07</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C15" t="str">
-        <v>武汉</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D15" t="str">
         <v>旅行</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2017-06-15</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B16" t="str">
-        <v>2020-06-15</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C16" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>萌 北京</v>
       </c>
       <c r="D16" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,13 +680,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2017-06-10</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B17" t="str">
-        <v>2017-06-11</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C17" t="str">
-        <v>萌 北京</v>
+        <v>武汉·游</v>
       </c>
       <c r="D17" t="str">
         <v>旅行</v>
@@ -697,13 +697,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2017-05-28</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B18" t="str">
-        <v>2017-05-30</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C18" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D18" t="str">
         <v>旅行</v>
@@ -714,27 +714,27 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2017-04-29</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B19" t="str">
-        <v>2017-05-01</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C19" t="str">
-        <v>大连 s</v>
+        <v>武汉</v>
       </c>
       <c r="D19" t="str">
         <v>旅行</v>
       </c>
       <c r="E19" t="str">
-        <v/>
+        <v>大聚会</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2017-04-21</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B20" t="str">
-        <v>2017-04-23</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C20" t="str">
         <v>武汉</v>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2017-03-13</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B21" t="str">
-        <v>2017-03-13</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C21" t="str">
-        <v>入职ZKDA</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D21" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,13 +765,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2016-12-23</v>
+        <v>2017-06-10</v>
       </c>
       <c r="B22" t="str">
-        <v>2017-01-08</v>
+        <v>2017-06-11</v>
       </c>
       <c r="C22" t="str">
-        <v>武汉·徐东</v>
+        <v>萌 北京</v>
       </c>
       <c r="D22" t="str">
         <v>旅行</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2016-10-07</v>
+        <v>2017-05-28</v>
       </c>
       <c r="B23" t="str">
-        <v>2016-10-14</v>
+        <v>2017-05-30</v>
       </c>
       <c r="C23" t="str">
         <v>武汉</v>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2016-10-01</v>
+        <v>2017-04-29</v>
       </c>
       <c r="B24" t="str">
-        <v>2016-10-07</v>
+        <v>2017-05-01</v>
       </c>
       <c r="C24" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>大连 s</v>
       </c>
       <c r="D24" t="str">
         <v>旅行</v>
@@ -816,137 +816,137 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C25" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D25" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C26" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D26" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B27" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C27" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D27" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B28" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C28" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D28" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B29" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C29" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D29" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B30" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C25" t="str">
+      <c r="C30" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D30" t="str">
         <v>居住</v>
       </c>
-      <c r="E25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26" xml:space="preserve">
-      <c r="A26" t="str">
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31" xml:space="preserve">
+      <c r="A31" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B26" t="str">
+      <c r="B31" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C26" t="str">
+      <c r="C31" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D26" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E26" t="str" xml:space="preserve">
+      <c r="D31" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E31" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B27" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C27" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D27" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E27" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B28" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C28" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D28" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B29" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C29" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D29" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E29" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B30" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C30" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D30" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B31" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C31" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D31" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E31" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2015-10-01</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B32" t="str">
-        <v>2015-10-07</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C32" t="str">
-        <v>大连 s</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D32" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -954,16 +954,16 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2015-06-09</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B33" t="str">
-        <v>2015-06-14</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C33" t="str">
-        <v>大连 s</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D33" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -971,50 +971,50 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2015-06-06</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B34" t="str">
-        <v>2015-06-08</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C34" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>待业343天</v>
       </c>
       <c r="D34" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E34" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2015-05-18</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B35" t="str">
-        <v>2016-07-16</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C35" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D35" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E35" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2015-05-01</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B36" t="str">
-        <v>2015-05-03</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C36" t="str">
-        <v>大连·游 s</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D36" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1022,10 +1022,10 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2015-03-28</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B37" t="str">
-        <v>2015-03-29</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C37" t="str">
         <v>大连 s</v>
@@ -1039,16 +1039,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2015-03-27</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B38" t="str">
-        <v>2015-03-27</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C38" t="str">
-        <v>北京接 s</v>
+        <v>大连 s</v>
       </c>
       <c r="D38" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2014-11-21</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B39" t="str">
-        <v>2014-11-23</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C39" t="str">
-        <v>天津旅游s</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D39" t="str">
         <v>旅行</v>
@@ -1073,30 +1073,30 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2014-11-10</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B40" t="str">
-        <v>2014-11-30</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C40" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D40" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2014-10-01</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B41" t="str">
-        <v>2014-10-01</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C41" t="str">
-        <v>青海聚五姨</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D41" t="str">
         <v>旅行</v>
@@ -1107,33 +1107,33 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2014-05-18</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B42" t="str">
-        <v>2015-05-18</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C42" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>大连 s</v>
       </c>
       <c r="D42" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E42" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2014-05-01</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B43" t="str">
-        <v>2014-05-01</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C43" t="str">
-        <v>青海聚</v>
+        <v>北京接 s</v>
       </c>
       <c r="D43" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1141,16 +1141,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2014-03-27</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B44" t="str">
-        <v>2014-03-27</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C44" t="str">
-        <v>二次入职世代泉源</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D44" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1158,16 +1158,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B45" t="str">
-        <v>2014-05-18</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C45" t="str">
-        <v>清缘商厦</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D45" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1175,16 +1175,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2014-03-20</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B46" t="str">
-        <v>2014-03-22</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C46" t="str">
-        <v>上海韩后全智贤</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D46" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1192,27 +1192,27 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2013-11-26</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B47" t="str">
-        <v>2013-11-26</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C47" t="str">
-        <v>大连和s小聚</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D47" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E47" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2013-06-11</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B48" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C48" t="str">
         <v>青海聚</v>
@@ -1226,30 +1226,30 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B49" t="str">
-        <v>2014-03-26</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C49" t="str">
-        <v>待业291天</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D49" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E49" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2013-06-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B50" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C50" t="str">
-        <v>青海·海石湾</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D50" t="str">
         <v>居住</v>
@@ -1260,16 +1260,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B51" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C51" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D51" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1277,16 +1277,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2012-12-07</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B52" t="str">
-        <v>2013-06-08</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C52" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D52" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1294,16 +1294,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2012-11-04</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B53" t="str">
-        <v>2012-11-04</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C53" t="str">
-        <v>北京送返鸡西</v>
+        <v>青海聚</v>
       </c>
       <c r="D53" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1311,30 +1311,30 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2012-09-24</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B54" t="str">
-        <v>2012-09-24</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C54" t="str">
-        <v>入职世代泉源</v>
+        <v>待业291天</v>
       </c>
       <c r="D54" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E54" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2012-08-21</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B55" t="str">
-        <v>2012-08-23</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C55" t="str">
-        <v>辽宁兴城</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D55" t="str">
         <v>居住</v>
@@ -1345,16 +1345,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2012-02-07</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B56" t="str">
-        <v>2012-11-29</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C56" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D56" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -1362,16 +1362,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2012-02-01</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B57" t="str">
-        <v>2012-02-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C57" t="str">
-        <v>北京接站sister</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D57" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -1379,33 +1379,33 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2010-07-20</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B58" t="str">
-        <v>2012-02-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C58" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D58" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E58" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2010-07-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B59" t="str">
-        <v>2011-12-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C59" t="str">
-        <v>北京北大青鸟</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D59" t="str">
-        <v>学业</v>
+        <v>工作</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -1413,16 +1413,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2010-06-01</v>
+        <v>2012-08-21</v>
       </c>
       <c r="B60" t="str">
-        <v>2010-06-01</v>
+        <v>2012-08-23</v>
       </c>
       <c r="C60" t="str">
-        <v>高考</v>
+        <v>辽宁兴城</v>
       </c>
       <c r="D60" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -1430,24 +1430,109 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C61" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D61" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C62" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D62" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C63" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D63" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E63" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C64" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D64" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C65" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D65" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B61" t="str">
+      <c r="B66" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C61" t="str">
+      <c r="C66" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D61" t="str">
+      <c r="D66" t="str">
         <v>其他</v>
       </c>
-      <c r="E61" t="str">
+      <c r="E66" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E61"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E66"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E81"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -510,13 +510,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2018-10-05</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B7" t="str">
-        <v>2018-10-07</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C7" t="str">
-        <v>广州·萌</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D7" t="str">
         <v>旅行</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2018-10-01</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B8" t="str">
-        <v>2018-10-04</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C8" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·北京</v>
       </c>
       <c r="D8" t="str">
         <v>旅行</v>
@@ -544,13 +544,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2018-06-01</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B9" t="str">
-        <v>2018-06-03</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C9" t="str">
-        <v>河北 秦皇河</v>
+        <v>❤·北京</v>
       </c>
       <c r="D9" t="str">
         <v>旅行</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2018-02-18</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B10" t="str">
-        <v>2018-02-25</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C10" t="str">
-        <v>广州 深圳</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D10" t="str">
         <v>旅行</v>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2018-02-02</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B11" t="str">
-        <v>2018-02-03</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C11" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>❤·北京</v>
       </c>
       <c r="D11" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,16 +595,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2017-12-23</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B12" t="str">
-        <v>2017-22-24</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C12" t="str">
-        <v>上海·路演</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D12" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,50 +612,50 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2017-11-11</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B13" t="str">
-        <v>2017-11-16</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C13" t="str">
-        <v>小熊 北京</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D13" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E13" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2017-10-10</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B14" t="str">
-        <v>2017-10-17</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C14" t="str">
-        <v>萌 北京</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D14" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E14" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2017-09-29</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B15" t="str">
-        <v>2017-10-09</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C15" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D15" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2017-09-27</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B16" t="str">
-        <v>2017-09-29</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C16" t="str">
-        <v>萌 北京</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D16" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,13 +680,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2017-09-09</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B17" t="str">
-        <v>2017-09-10</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C17" t="str">
-        <v>武汉·游</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D17" t="str">
         <v>旅行</v>
@@ -697,13 +697,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2017-08-18</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B18" t="str">
-        <v>2017-08-20</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C18" t="str">
-        <v>萌 北京</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D18" t="str">
         <v>旅行</v>
@@ -714,30 +714,30 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2017-08-11</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B19" t="str">
-        <v>2017-08-13</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C19" t="str">
-        <v>武汉</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D19" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E19" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2017-08-04</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B20" t="str">
-        <v>2017-08-07</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C20" t="str">
-        <v>武汉</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D20" t="str">
         <v>旅行</v>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2017-06-15</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B21" t="str">
-        <v>2020-06-15</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C21" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D21" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,13 +765,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2017-06-10</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B22" t="str">
-        <v>2017-06-11</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C22" t="str">
-        <v>萌 北京</v>
+        <v>广州·萌</v>
       </c>
       <c r="D22" t="str">
         <v>旅行</v>
@@ -782,13 +782,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2017-05-28</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B23" t="str">
-        <v>2017-05-30</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C23" t="str">
-        <v>武汉</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D23" t="str">
         <v>旅行</v>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2017-04-29</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B24" t="str">
-        <v>2017-05-01</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C24" t="str">
-        <v>大连 s</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D24" t="str">
         <v>旅行</v>
@@ -816,13 +816,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2017-04-21</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B25" t="str">
-        <v>2017-04-23</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C25" t="str">
-        <v>武汉</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D25" t="str">
         <v>旅行</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2017-03-13</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B26" t="str">
-        <v>2017-03-13</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C26" t="str">
-        <v>入职ZKDA</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D26" t="str">
-        <v>工作</v>
+        <v>家庭</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,16 +850,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2016-12-23</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B27" t="str">
-        <v>2017-01-08</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C27" t="str">
-        <v>武汉·徐东</v>
+        <v>上海·路演</v>
       </c>
       <c r="D27" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -867,358 +867,358 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2016-10-07</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B28" t="str">
-        <v>2016-10-14</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C28" t="str">
-        <v>武汉</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D28" t="str">
         <v>旅行</v>
       </c>
       <c r="E28" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2016-10-01</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B29" t="str">
-        <v>2016-10-07</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C29" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>萌 北京</v>
       </c>
       <c r="D29" t="str">
         <v>旅行</v>
       </c>
       <c r="E29" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
+        <v>2017-09-29</v>
+      </c>
+      <c r="B30" t="str">
+        <v>2017-10-09</v>
+      </c>
+      <c r="C30" t="str">
+        <v>西藏·珠穆朗玛</v>
+      </c>
+      <c r="D30" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>2017-09-27</v>
+      </c>
+      <c r="B31" t="str">
+        <v>2017-09-29</v>
+      </c>
+      <c r="C31" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D31" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>2017-09-09</v>
+      </c>
+      <c r="B32" t="str">
+        <v>2017-09-10</v>
+      </c>
+      <c r="C32" t="str">
+        <v>武汉·游</v>
+      </c>
+      <c r="D32" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>2017-08-18</v>
+      </c>
+      <c r="B33" t="str">
+        <v>2017-08-20</v>
+      </c>
+      <c r="C33" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D33" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>2017-08-11</v>
+      </c>
+      <c r="B34" t="str">
+        <v>2017-08-13</v>
+      </c>
+      <c r="C34" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D34" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E34" t="str">
+        <v>大聚会</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>2017-08-04</v>
+      </c>
+      <c r="B35" t="str">
+        <v>2017-08-07</v>
+      </c>
+      <c r="C35" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D35" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>2017-06-15</v>
+      </c>
+      <c r="B36" t="str">
+        <v>2020-06-15</v>
+      </c>
+      <c r="C36" t="str">
+        <v>北京华严北里小区59-6-501</v>
+      </c>
+      <c r="D36" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>2017-06-10</v>
+      </c>
+      <c r="B37" t="str">
+        <v>2017-06-11</v>
+      </c>
+      <c r="C37" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D37" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>2017-05-28</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2017-05-30</v>
+      </c>
+      <c r="C38" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D38" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>2017-04-29</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2017-05-01</v>
+      </c>
+      <c r="C39" t="str">
+        <v>大连 s</v>
+      </c>
+      <c r="D39" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C40" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D40" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C41" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D41" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C42" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D42" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C43" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D43" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B44" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C44" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D44" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B30" t="str">
+      <c r="B45" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C30" t="str">
+      <c r="C45" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D30" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31" xml:space="preserve">
-      <c r="A31" t="str">
+      <c r="D45" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46" xml:space="preserve">
+      <c r="A46" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B31" t="str">
+      <c r="B46" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C31" t="str">
+      <c r="C46" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D31" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E31" t="str" xml:space="preserve">
+      <c r="D46" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E46" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B32" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C32" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D32" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B33" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C33" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D33" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E33" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B34" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C34" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D34" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E34" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B35" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C35" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D35" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B36" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C36" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D36" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E36" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>2015-10-01</v>
-      </c>
-      <c r="B37" t="str">
-        <v>2015-10-07</v>
-      </c>
-      <c r="C37" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D37" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E37" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>2015-06-09</v>
-      </c>
-      <c r="B38" t="str">
-        <v>2015-06-14</v>
-      </c>
-      <c r="C38" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D38" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>2015-06-06</v>
-      </c>
-      <c r="B39" t="str">
-        <v>2015-06-08</v>
-      </c>
-      <c r="C39" t="str">
-        <v>湘西·凤凰古城</v>
-      </c>
-      <c r="D39" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E39" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>2015-05-18</v>
-      </c>
-      <c r="B40" t="str">
-        <v>2016-07-16</v>
-      </c>
-      <c r="C40" t="str">
-        <v>永泰东里16-6-601</v>
-      </c>
-      <c r="D40" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E40" t="str">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>2015-05-01</v>
-      </c>
-      <c r="B41" t="str">
-        <v>2015-05-03</v>
-      </c>
-      <c r="C41" t="str">
-        <v>大连·游 s</v>
-      </c>
-      <c r="D41" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>2015-03-28</v>
-      </c>
-      <c r="B42" t="str">
-        <v>2015-03-29</v>
-      </c>
-      <c r="C42" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D42" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>2015-03-27</v>
-      </c>
-      <c r="B43" t="str">
-        <v>2015-03-27</v>
-      </c>
-      <c r="C43" t="str">
-        <v>北京接 s</v>
-      </c>
-      <c r="D43" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>2014-11-21</v>
-      </c>
-      <c r="B44" t="str">
-        <v>2014-11-23</v>
-      </c>
-      <c r="C44" t="str">
-        <v>天津旅游s</v>
-      </c>
-      <c r="D44" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>2014-11-10</v>
-      </c>
-      <c r="B45" t="str">
-        <v>2014-11-30</v>
-      </c>
-      <c r="C45" t="str">
-        <v>北京转车聚 新地标租房</v>
-      </c>
-      <c r="D45" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>2014-10-01</v>
-      </c>
-      <c r="B46" t="str">
-        <v>2014-10-01</v>
-      </c>
-      <c r="C46" t="str">
-        <v>青海聚五姨</v>
-      </c>
-      <c r="D46" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2014-05-18</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B47" t="str">
-        <v>2015-05-18</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C47" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D47" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E47" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2014-05-01</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B48" t="str">
-        <v>2014-05-01</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C48" t="str">
-        <v>青海聚</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D48" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1226,33 +1226,33 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2014-03-27</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B49" t="str">
-        <v>2014-03-27</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C49" t="str">
-        <v>二次入职世代泉源</v>
+        <v>待业343天</v>
       </c>
       <c r="D49" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E49" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2014-03-20</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B50" t="str">
-        <v>2014-05-18</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C50" t="str">
-        <v>清缘商厦</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D50" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1260,13 +1260,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2014-03-20</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B51" t="str">
-        <v>2014-03-22</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C51" t="str">
-        <v>上海韩后全智贤</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D51" t="str">
         <v>观演</v>
@@ -1277,16 +1277,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2013-11-26</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B52" t="str">
-        <v>2013-11-26</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C52" t="str">
-        <v>大连和s小聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D52" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1294,13 +1294,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2013-06-11</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B53" t="str">
-        <v>2013-09-16</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C53" t="str">
-        <v>青海聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D53" t="str">
         <v>旅行</v>
@@ -1311,50 +1311,50 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2013-06-08</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B54" t="str">
-        <v>2014-03-26</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C54" t="str">
-        <v>待业291天</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D54" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E54" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2013-06-07</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B55" t="str">
-        <v>2013-09-16</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C55" t="str">
-        <v>青海·海石湾</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D55" t="str">
         <v>居住</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2013-02-01</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B56" t="str">
-        <v>2013-02-01</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C56" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D56" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -1362,16 +1362,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2012-12-07</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B57" t="str">
-        <v>2013-06-08</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C57" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>大连 s</v>
       </c>
       <c r="D57" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -1379,13 +1379,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2012-11-04</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B58" t="str">
-        <v>2012-11-04</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C58" t="str">
-        <v>北京送返鸡西</v>
+        <v>北京接 s</v>
       </c>
       <c r="D58" t="str">
         <v>其他</v>
@@ -1396,16 +1396,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2012-09-24</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B59" t="str">
-        <v>2012-09-24</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C59" t="str">
-        <v>入职世代泉源</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D59" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -1413,16 +1413,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2012-08-21</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B60" t="str">
-        <v>2012-08-23</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C60" t="str">
-        <v>辽宁兴城</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D60" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -1430,16 +1430,16 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2012-02-07</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B61" t="str">
-        <v>2012-11-29</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C61" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D61" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -1447,50 +1447,50 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2012-02-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B62" t="str">
-        <v>2012-02-01</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C62" t="str">
-        <v>北京接站sister</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D62" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E62" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2010-07-20</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B63" t="str">
-        <v>2012-02-01</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C63" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>青海聚</v>
       </c>
       <c r="D63" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E63" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2010-07-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B64" t="str">
-        <v>2011-12-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C64" t="str">
-        <v>北京北大青鸟</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D64" t="str">
-        <v>学业</v>
+        <v>工作</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -1498,16 +1498,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2010-06-01</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B65" t="str">
-        <v>2010-06-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C65" t="str">
-        <v>高考</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D65" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -1515,24 +1515,279 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
+        <v>2014-03-20</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2014-03-22</v>
+      </c>
+      <c r="C66" t="str">
+        <v>上海韩后全智贤</v>
+      </c>
+      <c r="D66" t="str">
+        <v>观演</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2013-11-26</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2013-11-26</v>
+      </c>
+      <c r="C67" t="str">
+        <v>大连和s小聚</v>
+      </c>
+      <c r="D67" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2013-06-11</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C68" t="str">
+        <v>青海聚</v>
+      </c>
+      <c r="D68" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2014-03-26</v>
+      </c>
+      <c r="C69" t="str">
+        <v>待业291天</v>
+      </c>
+      <c r="D69" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E69" t="str">
+        <v>291天</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2013-06-07</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C70" t="str">
+        <v>青海·海石湾</v>
+      </c>
+      <c r="D70" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2013-02-01</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2013-02-01</v>
+      </c>
+      <c r="C71" t="str">
+        <v>不详s至青海转乘 北京聚</v>
+      </c>
+      <c r="D71" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="C72" t="str">
+        <v>北京清河永泰庄新地标32-12</v>
+      </c>
+      <c r="D72" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="C73" t="str">
+        <v>北京送返鸡西</v>
+      </c>
+      <c r="D73" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C74" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D74" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C75" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D75" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C76" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D76" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C77" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D77" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C78" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D78" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E78" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C79" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D79" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C80" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D80" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B66" t="str">
+      <c r="B81" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C66" t="str">
+      <c r="C81" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D66" t="str">
+      <c r="D81" t="str">
         <v>其他</v>
       </c>
-      <c r="E66" t="str">
+      <c r="E81" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E66"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E81"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E89"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -476,16 +476,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2020-08-09</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B5" t="str">
-        <v>2021-11-01</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C5" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D5" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -493,33 +493,33 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2020-05-29</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B6" t="str">
-        <v>2020-11-01</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C6" t="str">
-        <v>待业155天</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D6" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E6" t="str">
-        <v>155天</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2019-12-31</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B7" t="str">
-        <v>2020-01-05</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C7" t="str">
-        <v>❤·LangX 南京</v>
+        <v>到达上海</v>
       </c>
       <c r="D7" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -527,16 +527,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2019-11-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B8" t="str">
-        <v>2019-12-10</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C8" t="str">
-        <v>❤·北京</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D8" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -544,13 +544,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2019-09-26</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B9" t="str">
-        <v>2019-11-14</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C9" t="str">
-        <v>❤·北京</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D9" t="str">
         <v>旅行</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2019-09-13</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B10" t="str">
-        <v>2019-09-15</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C10" t="str">
-        <v>❤·秦皇岛</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D10" t="str">
         <v>旅行</v>
@@ -578,33 +578,33 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2019-08-22</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B11" t="str">
-        <v>2019-09-17</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C11" t="str">
-        <v>❤·北京</v>
+        <v>待业155天</v>
       </c>
       <c r="D11" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E11" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2019-08-09</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B12" t="str">
-        <v>2019-08-11</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C12" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D12" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,16 +612,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2019-07-26</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B13" t="str">
-        <v>2019-07-28</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C13" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D13" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -629,16 +629,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2019-07-13</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B14" t="str">
-        <v>2019-07-14</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C14" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>❤·南京</v>
       </c>
       <c r="D14" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -646,16 +646,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2019-06-29</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B15" t="str">
-        <v>2019-06-30</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C15" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D15" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2019-06-20</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B16" t="str">
-        <v>2019-06-25</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C16" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤·北京</v>
       </c>
       <c r="D16" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,13 +680,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2019-06-07</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B17" t="str">
-        <v>2019-06-09</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C17" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>❤·北京</v>
       </c>
       <c r="D17" t="str">
         <v>旅行</v>
@@ -697,13 +697,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2019-05-01</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B18" t="str">
-        <v>2019-05-01</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C18" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D18" t="str">
         <v>旅行</v>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2019-05-01</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B19" t="str">
-        <v>2019-05-04</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C19" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>❤·北京</v>
       </c>
       <c r="D19" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,16 +731,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2019-04-04</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B20" t="str">
-        <v>2019-04-07</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C20" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D20" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2019-02-10</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B21" t="str">
-        <v>2019-02-17</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C21" t="str">
-        <v>深圳 萌</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D21" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,16 +765,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2018-10-05</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B22" t="str">
-        <v>2018-10-07</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C22" t="str">
-        <v>广州·萌</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D22" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2018-10-01</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B23" t="str">
-        <v>2018-10-04</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C23" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D23" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2018-06-01</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B24" t="str">
-        <v>2018-06-03</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C24" t="str">
-        <v>河北 秦皇河</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D24" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,13 +816,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2018-02-18</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B25" t="str">
-        <v>2018-02-25</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C25" t="str">
-        <v>广州 深圳</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D25" t="str">
         <v>旅行</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2018-02-02</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B26" t="str">
-        <v>2018-02-03</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C26" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D26" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,16 +850,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2017-12-23</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B27" t="str">
-        <v>2017-22-24</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C27" t="str">
-        <v>上海·路演</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D27" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -867,47 +867,47 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2017-11-11</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B28" t="str">
-        <v>2017-11-16</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C28" t="str">
-        <v>小熊 北京</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D28" t="str">
         <v>旅行</v>
       </c>
       <c r="E28" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2017-10-10</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B29" t="str">
-        <v>2017-10-17</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C29" t="str">
-        <v>萌 北京</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D29" t="str">
         <v>旅行</v>
       </c>
       <c r="E29" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2017-09-29</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B30" t="str">
-        <v>2017-10-09</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C30" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>广州·萌</v>
       </c>
       <c r="D30" t="str">
         <v>旅行</v>
@@ -918,13 +918,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2017-09-27</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B31" t="str">
-        <v>2017-09-29</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C31" t="str">
-        <v>萌 北京</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D31" t="str">
         <v>旅行</v>
@@ -935,13 +935,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2017-09-09</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B32" t="str">
-        <v>2017-09-10</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C32" t="str">
-        <v>武汉·游</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D32" t="str">
         <v>旅行</v>
@@ -952,13 +952,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2017-08-18</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B33" t="str">
-        <v>2017-08-20</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C33" t="str">
-        <v>萌 北京</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D33" t="str">
         <v>旅行</v>
@@ -969,33 +969,33 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2017-08-11</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B34" t="str">
-        <v>2017-08-13</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C34" t="str">
-        <v>武汉</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D34" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E34" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2017-08-04</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B35" t="str">
-        <v>2017-08-07</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C35" t="str">
-        <v>武汉</v>
+        <v>上海·路演</v>
       </c>
       <c r="D35" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1003,27 +1003,27 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2017-06-15</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B36" t="str">
-        <v>2020-06-15</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C36" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D36" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E36" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2017-06-10</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B37" t="str">
-        <v>2017-06-11</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C37" t="str">
         <v>萌 北京</v>
@@ -1032,18 +1032,18 @@
         <v>旅行</v>
       </c>
       <c r="E37" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2017-05-28</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B38" t="str">
-        <v>2017-05-30</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C38" t="str">
-        <v>武汉</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D38" t="str">
         <v>旅行</v>
@@ -1054,13 +1054,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2017-04-29</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B39" t="str">
-        <v>2017-05-01</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C39" t="str">
-        <v>大连 s</v>
+        <v>萌 北京</v>
       </c>
       <c r="D39" t="str">
         <v>旅行</v>
@@ -1071,13 +1071,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2017-04-21</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B40" t="str">
-        <v>2017-04-23</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C40" t="str">
-        <v>武汉</v>
+        <v>武汉·游</v>
       </c>
       <c r="D40" t="str">
         <v>旅行</v>
@@ -1088,16 +1088,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2017-03-13</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B41" t="str">
-        <v>2017-03-13</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C41" t="str">
-        <v>入职ZKDA</v>
+        <v>萌 北京</v>
       </c>
       <c r="D41" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1105,27 +1105,27 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2016-12-23</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B42" t="str">
-        <v>2017-01-08</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C42" t="str">
-        <v>武汉·徐东</v>
+        <v>武汉</v>
       </c>
       <c r="D42" t="str">
         <v>旅行</v>
       </c>
       <c r="E42" t="str">
-        <v/>
+        <v>大聚会</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2016-10-07</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B43" t="str">
-        <v>2016-10-14</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C43" t="str">
         <v>武汉</v>
@@ -1139,16 +1139,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2016-10-01</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B44" t="str">
-        <v>2016-10-07</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C44" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D44" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1156,205 +1156,205 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v>2017-06-10</v>
+      </c>
+      <c r="B45" t="str">
+        <v>2017-06-11</v>
+      </c>
+      <c r="C45" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D45" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>2017-05-28</v>
+      </c>
+      <c r="B46" t="str">
+        <v>2017-05-30</v>
+      </c>
+      <c r="C46" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D46" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>2017-04-29</v>
+      </c>
+      <c r="B47" t="str">
+        <v>2017-05-01</v>
+      </c>
+      <c r="C47" t="str">
+        <v>大连 s</v>
+      </c>
+      <c r="D47" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B48" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C48" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D48" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B49" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C49" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D49" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B50" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C50" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D50" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B51" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C51" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D51" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B52" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C52" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D52" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B53" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C53" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D45" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46" xml:space="preserve">
-      <c r="A46" t="str">
+      <c r="D53" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54" xml:space="preserve">
+      <c r="A54" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B46" t="str">
+      <c r="B54" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C46" t="str">
+      <c r="C54" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D46" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E46" t="str" xml:space="preserve">
+      <c r="D54" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E54" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B47" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C47" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D47" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B48" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C48" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D48" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B49" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C49" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D49" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E49" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B50" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C50" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D50" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E50" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B51" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C51" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D51" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>2015-10-01</v>
-      </c>
-      <c r="B52" t="str">
-        <v>2015-10-07</v>
-      </c>
-      <c r="C52" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D52" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E52" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>2015-06-09</v>
-      </c>
-      <c r="B53" t="str">
-        <v>2015-06-14</v>
-      </c>
-      <c r="C53" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D53" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>2015-06-06</v>
-      </c>
-      <c r="B54" t="str">
-        <v>2015-06-08</v>
-      </c>
-      <c r="C54" t="str">
-        <v>湘西·凤凰古城</v>
-      </c>
-      <c r="D54" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E54" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2015-05-18</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B55" t="str">
-        <v>2016-07-16</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C55" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D55" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E55" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2015-05-01</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B56" t="str">
-        <v>2015-05-03</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C56" t="str">
-        <v>大连·游 s</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D56" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -1362,33 +1362,33 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2015-03-28</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B57" t="str">
-        <v>2015-03-29</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C57" t="str">
-        <v>大连 s</v>
+        <v>待业343天</v>
       </c>
       <c r="D57" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E57" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2015-03-27</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B58" t="str">
-        <v>2015-03-27</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C58" t="str">
-        <v>北京接 s</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D58" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -1396,16 +1396,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2014-11-21</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B59" t="str">
-        <v>2014-11-23</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C59" t="str">
-        <v>天津旅游s</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D59" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -1413,16 +1413,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2014-11-10</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B60" t="str">
-        <v>2014-11-30</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C60" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连 s</v>
       </c>
       <c r="D60" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -1430,13 +1430,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B61" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C61" t="str">
-        <v>青海聚五姨</v>
+        <v>大连 s</v>
       </c>
       <c r="D61" t="str">
         <v>旅行</v>
@@ -1447,50 +1447,50 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2014-05-18</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B62" t="str">
-        <v>2015-05-18</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C62" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D62" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E62" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B63" t="str">
-        <v>2014-05-01</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C63" t="str">
-        <v>青海聚</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D63" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E63" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2014-03-27</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B64" t="str">
-        <v>2014-03-27</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C64" t="str">
-        <v>二次入职世代泉源</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D64" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -1498,16 +1498,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2014-03-20</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B65" t="str">
-        <v>2014-05-18</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C65" t="str">
-        <v>清缘商厦</v>
+        <v>大连 s</v>
       </c>
       <c r="D65" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -1515,16 +1515,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2014-03-20</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B66" t="str">
-        <v>2014-03-22</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C66" t="str">
-        <v>上海韩后全智贤</v>
+        <v>北京接 s</v>
       </c>
       <c r="D66" t="str">
-        <v>观演</v>
+        <v>其他</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -1532,16 +1532,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B67" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C67" t="str">
-        <v>大连和s小聚</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D67" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -1549,16 +1549,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2013-06-11</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B68" t="str">
-        <v>2013-09-16</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C68" t="str">
-        <v>青海聚</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D68" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -1566,50 +1566,50 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2013-06-08</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B69" t="str">
-        <v>2014-03-26</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C69" t="str">
-        <v>待业291天</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D69" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E69" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2013-06-07</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B70" t="str">
-        <v>2013-09-16</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C70" t="str">
-        <v>青海·海石湾</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D70" t="str">
         <v>居住</v>
       </c>
       <c r="E70" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2013-02-01</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B71" t="str">
-        <v>2013-02-01</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C71" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>青海聚</v>
       </c>
       <c r="D71" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -1617,16 +1617,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2012-12-07</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B72" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C72" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D72" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B73" t="str">
-        <v>2012-11-04</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C73" t="str">
-        <v>北京送返鸡西</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D73" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -1651,16 +1651,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2012-09-24</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B74" t="str">
-        <v>2012-09-24</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C74" t="str">
-        <v>入职世代泉源</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D74" t="str">
-        <v>工作</v>
+        <v>观演</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -1668,16 +1668,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2012-08-21</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B75" t="str">
-        <v>2012-08-23</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C75" t="str">
-        <v>辽宁兴城</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D75" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -1685,16 +1685,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2012-02-07</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B76" t="str">
-        <v>2012-11-29</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C76" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>青海聚</v>
       </c>
       <c r="D76" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -1702,50 +1702,50 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2012-02-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B77" t="str">
-        <v>2012-02-01</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C77" t="str">
-        <v>北京接站sister</v>
+        <v>待业291天</v>
       </c>
       <c r="D77" t="str">
         <v>其他</v>
       </c>
       <c r="E77" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2010-07-20</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B78" t="str">
-        <v>2012-02-01</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C78" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D78" t="str">
         <v>居住</v>
       </c>
       <c r="E78" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2010-07-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B79" t="str">
-        <v>2011-12-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C79" t="str">
-        <v>北京北大青鸟</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D79" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -1753,16 +1753,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2010-06-01</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B80" t="str">
-        <v>2010-06-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C80" t="str">
-        <v>高考</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D80" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -1770,13 +1770,13 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2010-01-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B81" t="str">
-        <v>2010-01-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C81" t="str">
-        <v>YY语音相识·若</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D81" t="str">
         <v>其他</v>
@@ -1785,9 +1785,145 @@
         <v/>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C82" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D82" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C83" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D83" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C84" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D84" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C85" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D85" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C86" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D86" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E86" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C87" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D87" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C88" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D88" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2010-01-01</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2010-01-01</v>
+      </c>
+      <c r="C89" t="str">
+        <v>YY语音相识·若</v>
+      </c>
+      <c r="D89" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E81"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E89"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E93"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -476,16 +476,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2020-11-02</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B5" t="str">
-        <v>2020-11-02</v>
+        <v>1007-01-01</v>
       </c>
       <c r="C5" t="str">
-        <v>入职上海齐獭</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D5" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -493,16 +493,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2020-08-09</v>
+        <v>2021-09-17</v>
       </c>
       <c r="B6" t="str">
-        <v>2021-11-01</v>
+        <v>2021-09-17</v>
       </c>
       <c r="C6" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>舟山·海宁(杭州)·萌·鑫</v>
       </c>
       <c r="D6" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -510,16 +510,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2020-07-31</v>
+        <v>2021-06-10</v>
       </c>
       <c r="B7" t="str">
-        <v>2020-07-31</v>
+        <v>2021-06-10</v>
       </c>
       <c r="C7" t="str">
-        <v>到达上海</v>
+        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
       </c>
       <c r="D7" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -527,16 +527,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2020-07-17</v>
+        <v>2021-05-01</v>
       </c>
       <c r="B8" t="str">
-        <v>2020-07-31</v>
+        <v>2021-05-01</v>
       </c>
       <c r="C8" t="str">
-        <v>安徽 芜湖×宣城×马鞍山</v>
+        <v>舟山·嵊泗岛 发小</v>
       </c>
       <c r="D8" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -544,16 +544,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2020-06-06</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B9" t="str">
-        <v>2020-07-17</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C9" t="str">
-        <v>❤️·厦门</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D9" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -561,16 +561,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2020-05-30</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B10" t="str">
-        <v>2020-05-31</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C10" t="str">
-        <v>秦皇岛</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D10" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -578,33 +578,33 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B11" t="str">
-        <v>2020-11-01</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C11" t="str">
-        <v>待业155天</v>
+        <v>到达上海</v>
       </c>
       <c r="D11" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E11" t="str">
-        <v>155天</v>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B12" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C12" t="str">
-        <v>离职中科达奥</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D12" t="str">
-        <v>工作</v>
+        <v>家庭</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,13 +612,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2020-04-30</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B13" t="str">
-        <v>2020-05-05</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C13" t="str">
-        <v>❤·厦门</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D13" t="str">
         <v>旅行</v>
@@ -629,13 +629,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2020-01-27</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B14" t="str">
-        <v>2020-02-04</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C14" t="str">
-        <v>❤·南京</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D14" t="str">
         <v>旅行</v>
@@ -646,33 +646,33 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2019-12-31</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B15" t="str">
-        <v>2020-01-05</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C15" t="str">
-        <v>❤·LangX 南京</v>
+        <v>待业155天</v>
       </c>
       <c r="D15" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E15" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2019-11-29</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B16" t="str">
-        <v>2019-12-10</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C16" t="str">
-        <v>❤·北京</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D16" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,13 +680,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2019-09-26</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B17" t="str">
-        <v>2019-11-14</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C17" t="str">
-        <v>❤·北京</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D17" t="str">
         <v>旅行</v>
@@ -697,13 +697,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2019-09-13</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B18" t="str">
-        <v>2019-09-15</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C18" t="str">
-        <v>❤·秦皇岛</v>
+        <v>❤·南京</v>
       </c>
       <c r="D18" t="str">
         <v>旅行</v>
@@ -714,13 +714,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2019-08-22</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B19" t="str">
-        <v>2019-09-17</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C19" t="str">
-        <v>❤·北京</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D19" t="str">
         <v>旅行</v>
@@ -731,16 +731,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2019-08-09</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B20" t="str">
-        <v>2019-08-11</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C20" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>❤·北京</v>
       </c>
       <c r="D20" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2019-07-26</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B21" t="str">
-        <v>2019-07-28</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C21" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D21" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,16 +765,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2019-07-13</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B22" t="str">
-        <v>2019-07-14</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C22" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D22" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2019-06-29</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B23" t="str">
-        <v>2019-06-30</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C23" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D23" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2019-06-20</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B24" t="str">
-        <v>2019-06-25</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C24" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D24" t="str">
         <v>居住</v>
@@ -816,16 +816,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2019-06-07</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B25" t="str">
-        <v>2019-06-09</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C25" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D25" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2019-05-01</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B26" t="str">
-        <v>2019-05-01</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C26" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D26" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,13 +850,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B27" t="str">
-        <v>2019-05-04</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C27" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D27" t="str">
         <v>居住</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2019-04-04</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B28" t="str">
-        <v>2019-04-07</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C28" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D28" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -884,13 +884,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2019-02-10</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B29" t="str">
-        <v>2019-02-17</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C29" t="str">
-        <v>深圳 萌</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D29" t="str">
         <v>旅行</v>
@@ -901,13 +901,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2018-10-05</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B30" t="str">
-        <v>2018-10-07</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C30" t="str">
-        <v>广州·萌</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D30" t="str">
         <v>旅行</v>
@@ -918,16 +918,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2018-10-01</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B31" t="str">
-        <v>2018-10-04</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C31" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D31" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -935,13 +935,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2018-06-01</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B32" t="str">
-        <v>2018-06-03</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C32" t="str">
-        <v>河北 秦皇河</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D32" t="str">
         <v>旅行</v>
@@ -952,13 +952,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2018-02-18</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B33" t="str">
-        <v>2018-02-25</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C33" t="str">
-        <v>广州 深圳</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D33" t="str">
         <v>旅行</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2018-02-02</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B34" t="str">
-        <v>2018-02-03</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C34" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>广州·萌</v>
       </c>
       <c r="D34" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -986,16 +986,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2017-12-23</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B35" t="str">
-        <v>2017-22-24</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C35" t="str">
-        <v>上海·路演</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D35" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1003,50 +1003,50 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2017-11-11</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B36" t="str">
-        <v>2017-11-16</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C36" t="str">
-        <v>小熊 北京</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D36" t="str">
         <v>旅行</v>
       </c>
       <c r="E36" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2017-10-10</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B37" t="str">
-        <v>2017-10-17</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C37" t="str">
-        <v>萌 北京</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D37" t="str">
         <v>旅行</v>
       </c>
       <c r="E37" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2017-09-29</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B38" t="str">
-        <v>2017-10-09</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C38" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D38" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2017-09-27</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B39" t="str">
-        <v>2017-09-29</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C39" t="str">
-        <v>萌 北京</v>
+        <v>上海·路演</v>
       </c>
       <c r="D39" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1071,27 +1071,27 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2017-09-09</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B40" t="str">
-        <v>2017-09-10</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C40" t="str">
-        <v>武汉·游</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D40" t="str">
         <v>旅行</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2017-08-18</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B41" t="str">
-        <v>2017-08-20</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C41" t="str">
         <v>萌 北京</v>
@@ -1100,35 +1100,35 @@
         <v>旅行</v>
       </c>
       <c r="E41" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2017-08-11</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B42" t="str">
-        <v>2017-08-13</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C42" t="str">
-        <v>武汉</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D42" t="str">
         <v>旅行</v>
       </c>
       <c r="E42" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2017-08-04</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B43" t="str">
-        <v>2017-08-07</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C43" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D43" t="str">
         <v>旅行</v>
@@ -1139,16 +1139,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2017-06-15</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B44" t="str">
-        <v>2020-06-15</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C44" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>武汉·游</v>
       </c>
       <c r="D44" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1156,10 +1156,10 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2017-06-10</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B45" t="str">
-        <v>2017-06-11</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C45" t="str">
         <v>萌 北京</v>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2017-05-28</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B46" t="str">
-        <v>2017-05-30</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C46" t="str">
         <v>武汉</v>
@@ -1185,18 +1185,18 @@
         <v>旅行</v>
       </c>
       <c r="E46" t="str">
-        <v/>
+        <v>大聚会</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2017-04-29</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B47" t="str">
-        <v>2017-05-01</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C47" t="str">
-        <v>大连 s</v>
+        <v>武汉</v>
       </c>
       <c r="D47" t="str">
         <v>旅行</v>
@@ -1207,16 +1207,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2017-04-21</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B48" t="str">
-        <v>2017-04-23</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C48" t="str">
-        <v>武汉</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D48" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1224,16 +1224,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2017-03-13</v>
+        <v>2017-06-10</v>
       </c>
       <c r="B49" t="str">
-        <v>2017-03-13</v>
+        <v>2017-06-11</v>
       </c>
       <c r="C49" t="str">
-        <v>入职ZKDA</v>
+        <v>萌 北京</v>
       </c>
       <c r="D49" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2016-12-23</v>
+        <v>2017-05-28</v>
       </c>
       <c r="B50" t="str">
-        <v>2017-01-08</v>
+        <v>2017-05-30</v>
       </c>
       <c r="C50" t="str">
-        <v>武汉·徐东</v>
+        <v>武汉</v>
       </c>
       <c r="D50" t="str">
         <v>旅行</v>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2016-10-07</v>
+        <v>2017-04-29</v>
       </c>
       <c r="B51" t="str">
-        <v>2016-10-14</v>
+        <v>2017-05-01</v>
       </c>
       <c r="C51" t="str">
-        <v>武汉</v>
+        <v>大连 s</v>
       </c>
       <c r="D51" t="str">
         <v>旅行</v>
@@ -1275,13 +1275,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2016-10-01</v>
+        <v>2017-04-21</v>
       </c>
       <c r="B52" t="str">
-        <v>2016-10-07</v>
+        <v>2017-04-23</v>
       </c>
       <c r="C52" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>武汉</v>
       </c>
       <c r="D52" t="str">
         <v>旅行</v>
@@ -1292,117 +1292,117 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B53" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C53" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D53" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B54" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C54" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D54" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B55" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C55" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D55" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B56" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C56" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D56" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B53" t="str">
+      <c r="B57" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C53" t="str">
+      <c r="C57" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D53" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E53" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="54" xml:space="preserve">
-      <c r="A54" t="str">
+      <c r="D57" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58" xml:space="preserve">
+      <c r="A58" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B54" t="str">
+      <c r="B58" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C54" t="str">
+      <c r="C58" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D54" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E54" t="str" xml:space="preserve">
+      <c r="D58" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E58" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B55" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C55" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D55" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B56" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C56" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D56" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E56" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B57" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C57" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D57" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E57" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B58" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C58" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D58" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E58" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2015-12-31</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B59" t="str">
-        <v>2015-12-31</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C59" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D59" t="str">
         <v>观演</v>
@@ -1413,16 +1413,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2015-10-01</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B60" t="str">
-        <v>2015-10-07</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C60" t="str">
-        <v>大连 s</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D60" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -1430,33 +1430,33 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2015-06-09</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B61" t="str">
-        <v>2015-06-14</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C61" t="str">
-        <v>大连 s</v>
+        <v>待业343天</v>
       </c>
       <c r="D61" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E61" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2015-06-06</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B62" t="str">
-        <v>2015-06-08</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C62" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D62" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -1464,30 +1464,30 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2015-05-18</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B63" t="str">
-        <v>2016-07-16</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C63" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D63" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E63" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2015-05-01</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B64" t="str">
-        <v>2015-05-03</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C64" t="str">
-        <v>大连·游 s</v>
+        <v>大连 s</v>
       </c>
       <c r="D64" t="str">
         <v>旅行</v>
@@ -1498,10 +1498,10 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2015-03-28</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B65" t="str">
-        <v>2015-03-29</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C65" t="str">
         <v>大连 s</v>
@@ -1515,16 +1515,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2015-03-27</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B66" t="str">
-        <v>2015-03-27</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C66" t="str">
-        <v>北京接 s</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D66" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -1532,33 +1532,33 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2014-11-21</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B67" t="str">
-        <v>2014-11-23</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C67" t="str">
-        <v>天津旅游s</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D67" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E67" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2014-11-10</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B68" t="str">
-        <v>2014-11-30</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C68" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D68" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -1566,13 +1566,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2014-10-01</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B69" t="str">
-        <v>2014-10-01</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C69" t="str">
-        <v>青海聚五姨</v>
+        <v>大连 s</v>
       </c>
       <c r="D69" t="str">
         <v>旅行</v>
@@ -1583,30 +1583,30 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2014-05-18</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B70" t="str">
-        <v>2015-05-18</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C70" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>北京接 s</v>
       </c>
       <c r="D70" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E70" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2014-05-01</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B71" t="str">
-        <v>2014-05-01</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C71" t="str">
-        <v>青海聚</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D71" t="str">
         <v>旅行</v>
@@ -1617,16 +1617,16 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2014-03-27</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B72" t="str">
-        <v>2014-03-27</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C72" t="str">
-        <v>二次入职世代泉源</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D72" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -1634,16 +1634,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2014-03-20</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B73" t="str">
-        <v>2014-05-18</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C73" t="str">
-        <v>清缘商厦</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D73" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -1651,33 +1651,33 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2014-03-20</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B74" t="str">
-        <v>2014-03-22</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C74" t="str">
-        <v>上海韩后全智贤</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D74" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2013-11-26</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B75" t="str">
-        <v>2013-11-26</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C75" t="str">
-        <v>大连和s小聚</v>
+        <v>青海聚</v>
       </c>
       <c r="D75" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -1685,16 +1685,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2013-06-11</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B76" t="str">
-        <v>2013-09-16</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C76" t="str">
-        <v>青海聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D76" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -1702,33 +1702,33 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B77" t="str">
-        <v>2014-03-26</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C77" t="str">
-        <v>待业291天</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D77" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E77" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2013-06-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B78" t="str">
-        <v>2013-09-16</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C78" t="str">
-        <v>青海·海石湾</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D78" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -1736,13 +1736,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2013-02-01</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B79" t="str">
-        <v>2013-02-01</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C79" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D79" t="str">
         <v>其他</v>
@@ -1753,16 +1753,16 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2012-12-07</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B80" t="str">
-        <v>2013-06-08</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C80" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>青海聚</v>
       </c>
       <c r="D80" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -1770,33 +1770,33 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2012-11-04</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B81" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C81" t="str">
-        <v>北京送返鸡西</v>
+        <v>待业291天</v>
       </c>
       <c r="D81" t="str">
         <v>其他</v>
       </c>
       <c r="E81" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2012-09-24</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B82" t="str">
-        <v>2012-09-24</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C82" t="str">
-        <v>入职世代泉源</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D82" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -1804,16 +1804,16 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2012-08-21</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B83" t="str">
-        <v>2012-08-23</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C83" t="str">
-        <v>辽宁兴城</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D83" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2012-02-07</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B84" t="str">
-        <v>2012-11-29</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C84" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D84" t="str">
         <v>居住</v>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2012-02-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B85" t="str">
-        <v>2012-02-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C85" t="str">
-        <v>北京接站sister</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D85" t="str">
         <v>其他</v>
@@ -1855,33 +1855,33 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2010-07-20</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B86" t="str">
-        <v>2012-02-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C86" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D86" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E86" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2010-07-01</v>
+        <v>2012-08-21</v>
       </c>
       <c r="B87" t="str">
-        <v>2011-12-01</v>
+        <v>2012-08-23</v>
       </c>
       <c r="C87" t="str">
-        <v>北京北大青鸟</v>
+        <v>辽宁兴城</v>
       </c>
       <c r="D87" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -1889,16 +1889,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2010-06-01</v>
+        <v>2012-02-07</v>
       </c>
       <c r="B88" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-29</v>
       </c>
       <c r="C88" t="str">
-        <v>高考</v>
+        <v>北京清河永泰庄新地标31-9-5</v>
       </c>
       <c r="D88" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2010-01-01</v>
+        <v>2012-02-01</v>
       </c>
       <c r="B89" t="str">
-        <v>2010-01-01</v>
+        <v>2012-02-01</v>
       </c>
       <c r="C89" t="str">
-        <v>YY语音相识·若</v>
+        <v>北京接站sister</v>
       </c>
       <c r="D89" t="str">
         <v>其他</v>
@@ -1921,9 +1921,77 @@
         <v/>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C90" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D90" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E90" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B91" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C91" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D91" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B92" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C92" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D92" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>2010-01-01</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2010-01-01</v>
+      </c>
+      <c r="C93" t="str">
+        <v>YY语音相识·若</v>
+      </c>
+      <c r="D93" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E93"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E108"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -442,33 +442,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2022-10-16</v>
+        <v>2023-12-31</v>
       </c>
       <c r="B3" t="str">
-        <v>2024-11-15</v>
+        <v>2023-12-31</v>
       </c>
       <c r="C3" t="str">
-        <v>松江区启民苑20栋201</v>
+        <v>杭州·蝴蝶剧场</v>
       </c>
       <c r="D3" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>君霄</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2021-10-31</v>
+        <v>2023-12-16</v>
       </c>
       <c r="B4" t="str">
-        <v>2022-10-31</v>
+        <v>2023-12-17</v>
       </c>
       <c r="C4" t="str">
-        <v>松江区启民苑15号楼102</v>
+        <v>杭州🍊☁️</v>
       </c>
       <c r="D4" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -476,16 +476,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2021-10-05</v>
+        <v>2023-12-02</v>
       </c>
       <c r="B5" t="str">
-        <v>1007-01-01</v>
+        <v>2023-12-03</v>
       </c>
       <c r="C5" t="str">
-        <v>舟山·嵊泗岛 🧑🏻</v>
+        <v>杭州/苏州 君霄/ZSH演唱会</v>
       </c>
       <c r="D5" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -493,16 +493,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2021-09-17</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B6" t="str">
-        <v>2021-09-17</v>
+        <v>2023-11-16</v>
       </c>
       <c r="C6" t="str">
-        <v>舟山·海宁(杭州)·萌·鑫</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D6" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -510,16 +510,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2021-06-10</v>
+        <v>2023-11-17</v>
       </c>
       <c r="B7" t="str">
-        <v>2021-06-10</v>
+        <v>2023-11-19</v>
       </c>
       <c r="C7" t="str">
-        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
+        <v>🐻·上海</v>
       </c>
       <c r="D7" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -527,13 +527,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2021-05-01</v>
+        <v>2023-09-27</v>
       </c>
       <c r="B8" t="str">
-        <v>2021-05-01</v>
+        <v>2023-10-05</v>
       </c>
       <c r="C8" t="str">
-        <v>舟山·嵊泗岛 发小</v>
+        <v>温州百丈漈·常州·海宁·杭州周游记</v>
       </c>
       <c r="D8" t="str">
         <v>旅行</v>
@@ -544,16 +544,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2020-11-02</v>
+        <v>2023-09-23</v>
       </c>
       <c r="B9" t="str">
-        <v>2020-11-02</v>
+        <v>2023-09-23</v>
       </c>
       <c r="C9" t="str">
-        <v>入职上海齐獭</v>
+        <v>南京·小狮子音乐会🦁</v>
       </c>
       <c r="D9" t="str">
-        <v>工作</v>
+        <v>观演</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -561,16 +561,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2020-08-09</v>
+        <v>2023-09-16</v>
       </c>
       <c r="B10" t="str">
-        <v>2021-11-01</v>
+        <v>2023-09-16</v>
       </c>
       <c r="C10" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>合肥·蔡依林演唱会</v>
       </c>
       <c r="D10" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2020-07-31</v>
+        <v>2023-09-09</v>
       </c>
       <c r="B11" t="str">
-        <v>2020-07-31</v>
+        <v>2023-09-09</v>
       </c>
       <c r="C11" t="str">
-        <v>到达上海</v>
+        <v>苏州·杨丞琳演唱会</v>
       </c>
       <c r="D11" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,16 +595,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2020-07-17</v>
+        <v>2023-08-19</v>
       </c>
       <c r="B12" t="str">
-        <v>2020-07-31</v>
+        <v>2023-08-20</v>
       </c>
       <c r="C12" t="str">
-        <v>安徽 芜湖×宣城×马鞍山</v>
+        <v>常州·S</v>
       </c>
       <c r="D12" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,16 +612,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2020-06-06</v>
+        <v>2023-07-22</v>
       </c>
       <c r="B13" t="str">
-        <v>2020-07-17</v>
+        <v>2023-07-23</v>
       </c>
       <c r="C13" t="str">
-        <v>❤️·厦门</v>
+        <v>青岛·小狮子音乐会🦁</v>
       </c>
       <c r="D13" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -629,16 +629,16 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2020-05-30</v>
+        <v>2023-05-20</v>
       </c>
       <c r="B14" t="str">
-        <v>2020-05-31</v>
+        <v>2023-05-21</v>
       </c>
       <c r="C14" t="str">
-        <v>秦皇岛</v>
+        <v>合肥·小狮子音乐会🦁</v>
       </c>
       <c r="D14" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -646,33 +646,33 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2020-05-29</v>
+        <v>2023-04-14</v>
       </c>
       <c r="B15" t="str">
-        <v>2020-11-01</v>
+        <v>2023-04-16</v>
       </c>
       <c r="C15" t="str">
-        <v>待业155天</v>
+        <v>舟山·朱家尖 同事</v>
       </c>
       <c r="D15" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E15" t="str">
-        <v>155天</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2020-05-29</v>
+        <v>2023-01-26</v>
       </c>
       <c r="B16" t="str">
-        <v>2020-05-29</v>
+        <v>2023-01-29</v>
       </c>
       <c r="C16" t="str">
-        <v>离职中科达奥</v>
+        <v>福建·平潭岛 萌</v>
       </c>
       <c r="D16" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,16 +680,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2020-04-30</v>
+        <v>2022-12-31</v>
       </c>
       <c r="B17" t="str">
-        <v>2020-05-05</v>
+        <v>2023-01-02</v>
       </c>
       <c r="C17" t="str">
-        <v>❤·厦门</v>
+        <v>南昌·小狮子音乐会🦁</v>
       </c>
       <c r="D17" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -697,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2020-01-27</v>
+        <v>2022-10-16</v>
       </c>
       <c r="B18" t="str">
-        <v>2020-02-04</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C18" t="str">
-        <v>❤·南京</v>
+        <v>松江区启民苑20栋201</v>
       </c>
       <c r="D18" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2019-12-31</v>
+        <v>2021-10-31</v>
       </c>
       <c r="B19" t="str">
-        <v>2020-01-05</v>
+        <v>2022-10-31</v>
       </c>
       <c r="C19" t="str">
-        <v>❤·LangX 南京</v>
+        <v>松江区启民苑15号楼102</v>
       </c>
       <c r="D19" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,13 +731,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2019-11-29</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B20" t="str">
-        <v>2019-12-10</v>
+        <v>1007-01-01</v>
       </c>
       <c r="C20" t="str">
-        <v>❤·北京</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D20" t="str">
         <v>旅行</v>
@@ -748,13 +748,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2019-09-26</v>
+        <v>2021-09-17</v>
       </c>
       <c r="B21" t="str">
-        <v>2019-11-14</v>
+        <v>2021-09-17</v>
       </c>
       <c r="C21" t="str">
-        <v>❤·北京</v>
+        <v>舟山·海宁(杭州)·萌·鑫</v>
       </c>
       <c r="D21" t="str">
         <v>旅行</v>
@@ -765,13 +765,13 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2019-09-13</v>
+        <v>2021-06-10</v>
       </c>
       <c r="B22" t="str">
-        <v>2019-09-15</v>
+        <v>2021-06-10</v>
       </c>
       <c r="C22" t="str">
-        <v>❤·秦皇岛</v>
+        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
       </c>
       <c r="D22" t="str">
         <v>旅行</v>
@@ -782,13 +782,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2019-08-22</v>
+        <v>2021-05-01</v>
       </c>
       <c r="B23" t="str">
-        <v>2019-09-17</v>
+        <v>2021-05-01</v>
       </c>
       <c r="C23" t="str">
-        <v>❤·北京</v>
+        <v>舟山·嵊泗岛 发小</v>
       </c>
       <c r="D23" t="str">
         <v>旅行</v>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2019-08-09</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B24" t="str">
-        <v>2019-08-11</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C24" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D24" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,13 +816,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2019-07-26</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B25" t="str">
-        <v>2019-07-28</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C25" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D25" t="str">
         <v>居住</v>
@@ -833,13 +833,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2019-07-13</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B26" t="str">
-        <v>2019-07-14</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C26" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>到达上海</v>
       </c>
       <c r="D26" t="str">
         <v>居住</v>
@@ -850,16 +850,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2019-06-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B27" t="str">
-        <v>2019-06-30</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C27" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D27" t="str">
-        <v>居住</v>
+        <v>家庭</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -867,16 +867,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2019-06-20</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B28" t="str">
-        <v>2019-06-25</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C28" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D28" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -884,13 +884,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2019-06-07</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B29" t="str">
-        <v>2019-06-09</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C29" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D29" t="str">
         <v>旅行</v>
@@ -901,33 +901,33 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2019-05-01</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B30" t="str">
-        <v>2019-05-01</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C30" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>待业155天</v>
       </c>
       <c r="D30" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E30" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2019-05-01</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B31" t="str">
-        <v>2019-05-04</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C31" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D31" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -935,13 +935,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2019-04-04</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B32" t="str">
-        <v>2019-04-07</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C32" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D32" t="str">
         <v>旅行</v>
@@ -952,13 +952,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2019-02-10</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B33" t="str">
-        <v>2019-02-17</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C33" t="str">
-        <v>深圳 萌</v>
+        <v>❤·南京</v>
       </c>
       <c r="D33" t="str">
         <v>旅行</v>
@@ -969,13 +969,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2018-10-05</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B34" t="str">
-        <v>2018-10-07</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C34" t="str">
-        <v>广州·萌</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D34" t="str">
         <v>旅行</v>
@@ -986,13 +986,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2018-10-01</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B35" t="str">
-        <v>2018-10-04</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C35" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·北京</v>
       </c>
       <c r="D35" t="str">
         <v>旅行</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2018-06-01</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B36" t="str">
-        <v>2018-06-03</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C36" t="str">
-        <v>河北 秦皇河</v>
+        <v>❤·北京</v>
       </c>
       <c r="D36" t="str">
         <v>旅行</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2018-02-18</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B37" t="str">
-        <v>2018-02-25</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C37" t="str">
-        <v>广州 深圳</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D37" t="str">
         <v>旅行</v>
@@ -1037,16 +1037,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2018-02-02</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B38" t="str">
-        <v>2018-02-03</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C38" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>❤·北京</v>
       </c>
       <c r="D38" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2017-12-23</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B39" t="str">
-        <v>2017-22-24</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C39" t="str">
-        <v>上海·路演</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D39" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1071,50 +1071,50 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2017-11-11</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B40" t="str">
-        <v>2017-11-16</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C40" t="str">
-        <v>小熊 北京</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D40" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E40" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2017-10-10</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B41" t="str">
-        <v>2017-10-17</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C41" t="str">
-        <v>萌 北京</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D41" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E41" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2017-09-29</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B42" t="str">
-        <v>2017-10-09</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C42" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D42" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1122,16 +1122,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2017-09-27</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B43" t="str">
-        <v>2017-09-29</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C43" t="str">
-        <v>萌 北京</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D43" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1139,13 +1139,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2017-09-09</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B44" t="str">
-        <v>2017-09-10</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C44" t="str">
-        <v>武汉·游</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D44" t="str">
         <v>旅行</v>
@@ -1156,13 +1156,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2017-08-18</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B45" t="str">
-        <v>2017-08-20</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C45" t="str">
-        <v>萌 北京</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D45" t="str">
         <v>旅行</v>
@@ -1173,30 +1173,30 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2017-08-11</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B46" t="str">
-        <v>2017-08-13</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C46" t="str">
-        <v>武汉</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D46" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E46" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2017-08-04</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B47" t="str">
-        <v>2017-08-07</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C47" t="str">
-        <v>武汉</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D47" t="str">
         <v>旅行</v>
@@ -1207,16 +1207,16 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2017-06-15</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B48" t="str">
-        <v>2020-06-15</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C48" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D48" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -1224,13 +1224,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2017-06-10</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B49" t="str">
-        <v>2017-06-11</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C49" t="str">
-        <v>萌 北京</v>
+        <v>广州·萌</v>
       </c>
       <c r="D49" t="str">
         <v>旅行</v>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2017-05-28</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B50" t="str">
-        <v>2017-05-30</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C50" t="str">
-        <v>武汉</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D50" t="str">
         <v>旅行</v>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2017-04-29</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B51" t="str">
-        <v>2017-05-01</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C51" t="str">
-        <v>大连 s</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D51" t="str">
         <v>旅行</v>
@@ -1275,13 +1275,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2017-04-21</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B52" t="str">
-        <v>2017-04-23</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C52" t="str">
-        <v>武汉</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D52" t="str">
         <v>旅行</v>
@@ -1292,16 +1292,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2017-03-13</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B53" t="str">
-        <v>2017-03-13</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C53" t="str">
-        <v>入职ZKDA</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D53" t="str">
-        <v>工作</v>
+        <v>家庭</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1309,16 +1309,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2016-12-23</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B54" t="str">
-        <v>2017-01-08</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C54" t="str">
-        <v>武汉·徐东</v>
+        <v>上海·路演</v>
       </c>
       <c r="D54" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -1326,358 +1326,358 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2016-10-07</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B55" t="str">
-        <v>2016-10-14</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C55" t="str">
-        <v>武汉</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D55" t="str">
         <v>旅行</v>
       </c>
       <c r="E55" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2016-10-01</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B56" t="str">
-        <v>2016-10-07</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C56" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>萌 北京</v>
       </c>
       <c r="D56" t="str">
         <v>旅行</v>
       </c>
       <c r="E56" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
+        <v>2017-09-29</v>
+      </c>
+      <c r="B57" t="str">
+        <v>2017-10-09</v>
+      </c>
+      <c r="C57" t="str">
+        <v>西藏·珠穆朗玛</v>
+      </c>
+      <c r="D57" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>2017-09-27</v>
+      </c>
+      <c r="B58" t="str">
+        <v>2017-09-29</v>
+      </c>
+      <c r="C58" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D58" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>2017-09-09</v>
+      </c>
+      <c r="B59" t="str">
+        <v>2017-09-10</v>
+      </c>
+      <c r="C59" t="str">
+        <v>武汉·游</v>
+      </c>
+      <c r="D59" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>2017-08-18</v>
+      </c>
+      <c r="B60" t="str">
+        <v>2017-08-20</v>
+      </c>
+      <c r="C60" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D60" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>2017-08-11</v>
+      </c>
+      <c r="B61" t="str">
+        <v>2017-08-13</v>
+      </c>
+      <c r="C61" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D61" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E61" t="str">
+        <v>大聚会</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>2017-08-04</v>
+      </c>
+      <c r="B62" t="str">
+        <v>2017-08-07</v>
+      </c>
+      <c r="C62" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D62" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>2017-06-15</v>
+      </c>
+      <c r="B63" t="str">
+        <v>2020-06-15</v>
+      </c>
+      <c r="C63" t="str">
+        <v>北京华严北里小区59-6-501</v>
+      </c>
+      <c r="D63" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>2017-06-10</v>
+      </c>
+      <c r="B64" t="str">
+        <v>2017-06-11</v>
+      </c>
+      <c r="C64" t="str">
+        <v>萌 北京</v>
+      </c>
+      <c r="D64" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>2017-05-28</v>
+      </c>
+      <c r="B65" t="str">
+        <v>2017-05-30</v>
+      </c>
+      <c r="C65" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D65" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>2017-04-29</v>
+      </c>
+      <c r="B66" t="str">
+        <v>2017-05-01</v>
+      </c>
+      <c r="C66" t="str">
+        <v>大连 s</v>
+      </c>
+      <c r="D66" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E66" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B67" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C67" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D67" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B68" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C68" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D68" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B69" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C69" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D69" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B70" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C70" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D70" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B71" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C71" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D71" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B57" t="str">
+      <c r="B72" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C57" t="str">
+      <c r="C72" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D57" t="str">
+      <c r="D72" t="str">
         <v>居住</v>
       </c>
-      <c r="E57" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="58" xml:space="preserve">
-      <c r="A58" t="str">
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73" xml:space="preserve">
+      <c r="A73" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B58" t="str">
+      <c r="B73" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C58" t="str">
+      <c r="C73" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D58" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E58" t="str" xml:space="preserve">
+      <c r="D73" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E73" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B59" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C59" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D59" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E59" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B60" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C60" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D60" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E60" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B61" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C61" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D61" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E61" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B62" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C62" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D62" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E62" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B63" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C63" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D63" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E63" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>2015-10-01</v>
-      </c>
-      <c r="B64" t="str">
-        <v>2015-10-07</v>
-      </c>
-      <c r="C64" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D64" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>2015-06-09</v>
-      </c>
-      <c r="B65" t="str">
-        <v>2015-06-14</v>
-      </c>
-      <c r="C65" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D65" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E65" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>2015-06-06</v>
-      </c>
-      <c r="B66" t="str">
-        <v>2015-06-08</v>
-      </c>
-      <c r="C66" t="str">
-        <v>湘西·凤凰古城</v>
-      </c>
-      <c r="D66" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>2015-05-18</v>
-      </c>
-      <c r="B67" t="str">
-        <v>2016-07-16</v>
-      </c>
-      <c r="C67" t="str">
-        <v>永泰东里16-6-601</v>
-      </c>
-      <c r="D67" t="str">
-        <v>居住</v>
-      </c>
-      <c r="E67" t="str">
-        <v>11500</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>2015-05-01</v>
-      </c>
-      <c r="B68" t="str">
-        <v>2015-05-03</v>
-      </c>
-      <c r="C68" t="str">
-        <v>大连·游 s</v>
-      </c>
-      <c r="D68" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E68" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>2015-03-28</v>
-      </c>
-      <c r="B69" t="str">
-        <v>2015-03-29</v>
-      </c>
-      <c r="C69" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D69" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E69" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>2015-03-27</v>
-      </c>
-      <c r="B70" t="str">
-        <v>2015-03-27</v>
-      </c>
-      <c r="C70" t="str">
-        <v>北京接 s</v>
-      </c>
-      <c r="D70" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E70" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>2014-11-21</v>
-      </c>
-      <c r="B71" t="str">
-        <v>2014-11-23</v>
-      </c>
-      <c r="C71" t="str">
-        <v>天津旅游s</v>
-      </c>
-      <c r="D71" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E71" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>2014-11-10</v>
-      </c>
-      <c r="B72" t="str">
-        <v>2014-11-30</v>
-      </c>
-      <c r="C72" t="str">
-        <v>北京转车聚 新地标租房</v>
-      </c>
-      <c r="D72" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>2014-10-01</v>
-      </c>
-      <c r="B73" t="str">
-        <v>2014-10-01</v>
-      </c>
-      <c r="C73" t="str">
-        <v>青海聚五姨</v>
-      </c>
-      <c r="D73" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E73" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2014-05-18</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B74" t="str">
-        <v>2015-05-18</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C74" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D74" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E74" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2014-05-01</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B75" t="str">
-        <v>2014-05-01</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C75" t="str">
-        <v>青海聚</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D75" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -1685,33 +1685,33 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2014-03-27</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B76" t="str">
-        <v>2014-03-27</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C76" t="str">
-        <v>二次入职世代泉源</v>
+        <v>待业343天</v>
       </c>
       <c r="D76" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E76" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2014-03-20</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B77" t="str">
-        <v>2014-05-18</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C77" t="str">
-        <v>清缘商厦</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D77" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2014-03-20</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B78" t="str">
-        <v>2014-03-22</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C78" t="str">
-        <v>上海韩后全智贤</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D78" t="str">
         <v>观演</v>
@@ -1736,16 +1736,16 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2013-11-26</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B79" t="str">
-        <v>2013-11-26</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C79" t="str">
-        <v>大连和s小聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D79" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -1753,13 +1753,13 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2013-06-11</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B80" t="str">
-        <v>2013-09-16</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C80" t="str">
-        <v>青海聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D80" t="str">
         <v>旅行</v>
@@ -1770,50 +1770,50 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2013-06-08</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B81" t="str">
-        <v>2014-03-26</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C81" t="str">
-        <v>待业291天</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D81" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E81" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2013-06-07</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B82" t="str">
-        <v>2013-09-16</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C82" t="str">
-        <v>青海·海石湾</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D82" t="str">
         <v>居住</v>
       </c>
       <c r="E82" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2013-02-01</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B83" t="str">
-        <v>2013-02-01</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C83" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D83" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -1821,16 +1821,16 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2012-12-07</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B84" t="str">
-        <v>2013-06-08</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C84" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>大连 s</v>
       </c>
       <c r="D84" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -1838,13 +1838,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2012-11-04</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B85" t="str">
-        <v>2012-11-04</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C85" t="str">
-        <v>北京送返鸡西</v>
+        <v>北京接 s</v>
       </c>
       <c r="D85" t="str">
         <v>其他</v>
@@ -1855,16 +1855,16 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2012-09-24</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B86" t="str">
-        <v>2012-09-24</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C86" t="str">
-        <v>入职世代泉源</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D86" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -1872,16 +1872,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2012-08-21</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B87" t="str">
-        <v>2012-08-23</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C87" t="str">
-        <v>辽宁兴城</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D87" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -1889,16 +1889,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2012-02-07</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B88" t="str">
-        <v>2012-11-29</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C88" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D88" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -1906,50 +1906,50 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2012-02-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B89" t="str">
-        <v>2012-02-01</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C89" t="str">
-        <v>北京接站sister</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D89" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2010-07-20</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B90" t="str">
-        <v>2012-02-01</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C90" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>青海聚</v>
       </c>
       <c r="D90" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E90" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2010-07-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B91" t="str">
-        <v>2011-12-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C91" t="str">
-        <v>北京北大青鸟</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D91" t="str">
-        <v>学业</v>
+        <v>工作</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -1957,16 +1957,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2010-06-01</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B92" t="str">
-        <v>2010-06-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C92" t="str">
-        <v>高考</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D92" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -1974,24 +1974,279 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
+        <v>2014-03-20</v>
+      </c>
+      <c r="B93" t="str">
+        <v>2014-03-22</v>
+      </c>
+      <c r="C93" t="str">
+        <v>上海韩后全智贤</v>
+      </c>
+      <c r="D93" t="str">
+        <v>观演</v>
+      </c>
+      <c r="E93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>2013-11-26</v>
+      </c>
+      <c r="B94" t="str">
+        <v>2013-11-26</v>
+      </c>
+      <c r="C94" t="str">
+        <v>大连和s小聚</v>
+      </c>
+      <c r="D94" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>2013-06-11</v>
+      </c>
+      <c r="B95" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C95" t="str">
+        <v>青海聚</v>
+      </c>
+      <c r="D95" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="B96" t="str">
+        <v>2014-03-26</v>
+      </c>
+      <c r="C96" t="str">
+        <v>待业291天</v>
+      </c>
+      <c r="D96" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E96" t="str">
+        <v>291天</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>2013-06-07</v>
+      </c>
+      <c r="B97" t="str">
+        <v>2013-09-16</v>
+      </c>
+      <c r="C97" t="str">
+        <v>青海·海石湾</v>
+      </c>
+      <c r="D97" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>2013-02-01</v>
+      </c>
+      <c r="B98" t="str">
+        <v>2013-02-01</v>
+      </c>
+      <c r="C98" t="str">
+        <v>不详s至青海转乘 北京聚</v>
+      </c>
+      <c r="D98" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>2012-12-07</v>
+      </c>
+      <c r="B99" t="str">
+        <v>2013-06-08</v>
+      </c>
+      <c r="C99" t="str">
+        <v>北京清河永泰庄新地标32-12</v>
+      </c>
+      <c r="D99" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="B100" t="str">
+        <v>2012-11-04</v>
+      </c>
+      <c r="C100" t="str">
+        <v>北京送返鸡西</v>
+      </c>
+      <c r="D100" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B101" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C101" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D101" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B102" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C102" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D102" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B103" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C103" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D103" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B104" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C104" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D104" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B105" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C105" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D105" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E105" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B106" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C106" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D106" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B107" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C107" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D107" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B93" t="str">
+      <c r="B108" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C93" t="str">
+      <c r="C108" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D93" t="str">
+      <c r="D108" t="str">
         <v>其他</v>
       </c>
-      <c r="E93" t="str">
+      <c r="E108" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E93"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E111"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -442,33 +442,33 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2023-12-31</v>
+        <v>2024-09-17</v>
       </c>
       <c r="B3" t="str">
-        <v>2023-12-31</v>
+        <v>2024-09-22</v>
       </c>
       <c r="C3" t="str">
-        <v>杭州·蝴蝶剧场</v>
+        <v>北海涠洲岛·九寨沟·重庆</v>
       </c>
       <c r="D3" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E3" t="str">
-        <v>君霄</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2023-12-16</v>
+        <v>2024-05-01</v>
       </c>
       <c r="B4" t="str">
-        <v>2023-12-17</v>
+        <v>2024-05-01</v>
       </c>
       <c r="C4" t="str">
-        <v>杭州🍊☁️</v>
+        <v>芜湖</v>
       </c>
       <c r="D4" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -476,13 +476,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2023-12-02</v>
+        <v>2024-02-17</v>
       </c>
       <c r="B5" t="str">
-        <v>2023-12-03</v>
+        <v>2024-03-03</v>
       </c>
       <c r="C5" t="str">
-        <v>杭州/苏州 君霄/ZSH演唱会</v>
+        <v>浙百春巡 杭州/扬州/南京/无锡</v>
       </c>
       <c r="D5" t="str">
         <v>观演</v>
@@ -493,30 +493,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2023-11-25</v>
+        <v>2023-12-31</v>
       </c>
       <c r="B6" t="str">
-        <v>2023-11-16</v>
+        <v>2023-12-31</v>
       </c>
       <c r="C6" t="str">
-        <v>武汉·小狮子音乐会🦁</v>
+        <v>杭州·蝴蝶剧场</v>
       </c>
       <c r="D6" t="str">
         <v>观演</v>
       </c>
       <c r="E6" t="str">
-        <v/>
+        <v>君霄</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2023-11-17</v>
+        <v>2023-12-16</v>
       </c>
       <c r="B7" t="str">
-        <v>2023-11-19</v>
+        <v>2023-12-17</v>
       </c>
       <c r="C7" t="str">
-        <v>🐻·上海</v>
+        <v>杭州🍊☁️</v>
       </c>
       <c r="D7" t="str">
         <v>观演</v>
@@ -527,16 +527,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2023-09-27</v>
+        <v>2023-12-02</v>
       </c>
       <c r="B8" t="str">
-        <v>2023-10-05</v>
+        <v>2023-12-03</v>
       </c>
       <c r="C8" t="str">
-        <v>温州百丈漈·常州·海宁·杭州周游记</v>
+        <v>杭州/苏州 君霄/ZSH演唱会</v>
       </c>
       <c r="D8" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -544,13 +544,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2023-09-23</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B9" t="str">
-        <v>2023-09-23</v>
+        <v>2023-11-16</v>
       </c>
       <c r="C9" t="str">
-        <v>南京·小狮子音乐会🦁</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D9" t="str">
         <v>观演</v>
@@ -561,13 +561,13 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2023-09-16</v>
+        <v>2023-11-17</v>
       </c>
       <c r="B10" t="str">
-        <v>2023-09-16</v>
+        <v>2023-11-19</v>
       </c>
       <c r="C10" t="str">
-        <v>合肥·蔡依林演唱会</v>
+        <v>🐻·上海</v>
       </c>
       <c r="D10" t="str">
         <v>观演</v>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2023-09-09</v>
+        <v>2023-09-27</v>
       </c>
       <c r="B11" t="str">
-        <v>2023-09-09</v>
+        <v>2023-10-05</v>
       </c>
       <c r="C11" t="str">
-        <v>苏州·杨丞琳演唱会</v>
+        <v>温州百丈漈·常州·海宁·杭州周游记</v>
       </c>
       <c r="D11" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,16 +595,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2023-08-19</v>
+        <v>2023-09-23</v>
       </c>
       <c r="B12" t="str">
-        <v>2023-08-20</v>
+        <v>2023-09-23</v>
       </c>
       <c r="C12" t="str">
-        <v>常州·S</v>
+        <v>南京·小狮子音乐会🦁</v>
       </c>
       <c r="D12" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,13 +612,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2023-07-22</v>
+        <v>2023-09-16</v>
       </c>
       <c r="B13" t="str">
-        <v>2023-07-23</v>
+        <v>2023-09-16</v>
       </c>
       <c r="C13" t="str">
-        <v>青岛·小狮子音乐会🦁</v>
+        <v>合肥·蔡依林演唱会</v>
       </c>
       <c r="D13" t="str">
         <v>观演</v>
@@ -629,13 +629,13 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2023-05-20</v>
+        <v>2023-09-09</v>
       </c>
       <c r="B14" t="str">
-        <v>2023-05-21</v>
+        <v>2023-09-09</v>
       </c>
       <c r="C14" t="str">
-        <v>合肥·小狮子音乐会🦁</v>
+        <v>苏州·杨丞琳演唱会</v>
       </c>
       <c r="D14" t="str">
         <v>观演</v>
@@ -646,13 +646,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2023-04-14</v>
+        <v>2023-08-19</v>
       </c>
       <c r="B15" t="str">
-        <v>2023-04-16</v>
+        <v>2023-08-20</v>
       </c>
       <c r="C15" t="str">
-        <v>舟山·朱家尖 同事</v>
+        <v>常州·S</v>
       </c>
       <c r="D15" t="str">
         <v>旅行</v>
@@ -663,16 +663,16 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2023-01-26</v>
+        <v>2023-07-22</v>
       </c>
       <c r="B16" t="str">
-        <v>2023-01-29</v>
+        <v>2023-07-23</v>
       </c>
       <c r="C16" t="str">
-        <v>福建·平潭岛 萌</v>
+        <v>青岛·小狮子音乐会🦁</v>
       </c>
       <c r="D16" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -680,13 +680,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2022-12-31</v>
+        <v>2023-05-20</v>
       </c>
       <c r="B17" t="str">
-        <v>2023-01-02</v>
+        <v>2023-05-21</v>
       </c>
       <c r="C17" t="str">
-        <v>南昌·小狮子音乐会🦁</v>
+        <v>合肥·小狮子音乐会🦁</v>
       </c>
       <c r="D17" t="str">
         <v>观演</v>
@@ -697,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2022-10-16</v>
+        <v>2023-04-14</v>
       </c>
       <c r="B18" t="str">
-        <v>2024-11-15</v>
+        <v>2023-04-16</v>
       </c>
       <c r="C18" t="str">
-        <v>松江区启民苑20栋201</v>
+        <v>舟山·朱家尖 同事</v>
       </c>
       <c r="D18" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2021-10-31</v>
+        <v>2023-01-26</v>
       </c>
       <c r="B19" t="str">
-        <v>2022-10-31</v>
+        <v>2023-01-29</v>
       </c>
       <c r="C19" t="str">
-        <v>松江区启民苑15号楼102</v>
+        <v>福建·平潭岛 萌</v>
       </c>
       <c r="D19" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,16 +731,16 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2021-10-05</v>
+        <v>2022-12-31</v>
       </c>
       <c r="B20" t="str">
-        <v>1007-01-01</v>
+        <v>2023-01-02</v>
       </c>
       <c r="C20" t="str">
-        <v>舟山·嵊泗岛 🧑🏻</v>
+        <v>南昌·小狮子音乐会🦁</v>
       </c>
       <c r="D20" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2021-09-17</v>
+        <v>2022-10-16</v>
       </c>
       <c r="B21" t="str">
-        <v>2021-09-17</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C21" t="str">
-        <v>舟山·海宁(杭州)·萌·鑫</v>
+        <v>松江区启民苑20栋201</v>
       </c>
       <c r="D21" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,16 +765,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2021-06-10</v>
+        <v>2021-10-31</v>
       </c>
       <c r="B22" t="str">
-        <v>2021-06-10</v>
+        <v>2022-10-31</v>
       </c>
       <c r="C22" t="str">
-        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
+        <v>松江区启民苑15号楼102</v>
       </c>
       <c r="D22" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,13 +782,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2021-05-01</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B23" t="str">
-        <v>2021-05-01</v>
+        <v>1007-01-01</v>
       </c>
       <c r="C23" t="str">
-        <v>舟山·嵊泗岛 发小</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D23" t="str">
         <v>旅行</v>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2020-11-02</v>
+        <v>2021-09-17</v>
       </c>
       <c r="B24" t="str">
-        <v>2020-11-02</v>
+        <v>2021-09-17</v>
       </c>
       <c r="C24" t="str">
-        <v>入职上海齐獭</v>
+        <v>舟山·海宁(杭州)·萌·鑫</v>
       </c>
       <c r="D24" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,16 +816,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2020-08-09</v>
+        <v>2021-06-10</v>
       </c>
       <c r="B25" t="str">
-        <v>2021-11-01</v>
+        <v>2021-06-10</v>
       </c>
       <c r="C25" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
       </c>
       <c r="D25" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2020-07-31</v>
+        <v>2021-05-01</v>
       </c>
       <c r="B26" t="str">
-        <v>2020-07-31</v>
+        <v>2021-05-01</v>
       </c>
       <c r="C26" t="str">
-        <v>到达上海</v>
+        <v>舟山·嵊泗岛 发小</v>
       </c>
       <c r="D26" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,16 +850,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2020-07-17</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B27" t="str">
-        <v>2020-07-31</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C27" t="str">
-        <v>安徽 芜湖×宣城×马鞍山</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D27" t="str">
-        <v>家庭</v>
+        <v>工作</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -867,16 +867,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2020-06-06</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B28" t="str">
-        <v>2020-07-17</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C28" t="str">
-        <v>❤️·厦门</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D28" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -884,16 +884,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2020-05-30</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B29" t="str">
-        <v>2020-05-31</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C29" t="str">
-        <v>秦皇岛</v>
+        <v>到达上海</v>
       </c>
       <c r="D29" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -901,33 +901,33 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B30" t="str">
-        <v>2020-11-01</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C30" t="str">
-        <v>待业155天</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D30" t="str">
-        <v>其他</v>
+        <v>家庭</v>
       </c>
       <c r="E30" t="str">
-        <v>155天</v>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2020-05-29</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B31" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C31" t="str">
-        <v>离职中科达奥</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D31" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -935,13 +935,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2020-04-30</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B32" t="str">
-        <v>2020-05-05</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C32" t="str">
-        <v>❤·厦门</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D32" t="str">
         <v>旅行</v>
@@ -952,33 +952,33 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2020-01-27</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B33" t="str">
-        <v>2020-02-04</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C33" t="str">
-        <v>❤·南京</v>
+        <v>待业155天</v>
       </c>
       <c r="D33" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E33" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2019-12-31</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B34" t="str">
-        <v>2020-01-05</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C34" t="str">
-        <v>❤·LangX 南京</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D34" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -986,13 +986,13 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2019-11-29</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B35" t="str">
-        <v>2019-12-10</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C35" t="str">
-        <v>❤·北京</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D35" t="str">
         <v>旅行</v>
@@ -1003,13 +1003,13 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2019-09-26</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B36" t="str">
-        <v>2019-11-14</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C36" t="str">
-        <v>❤·北京</v>
+        <v>❤·南京</v>
       </c>
       <c r="D36" t="str">
         <v>旅行</v>
@@ -1020,13 +1020,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2019-09-13</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B37" t="str">
-        <v>2019-09-15</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C37" t="str">
-        <v>❤·秦皇岛</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D37" t="str">
         <v>旅行</v>
@@ -1037,10 +1037,10 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2019-08-22</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B38" t="str">
-        <v>2019-09-17</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C38" t="str">
         <v>❤·北京</v>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2019-08-09</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B39" t="str">
-        <v>2019-08-11</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C39" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>❤·北京</v>
       </c>
       <c r="D39" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1071,16 +1071,16 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2019-07-26</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B40" t="str">
-        <v>2019-07-28</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C40" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D40" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1088,16 +1088,16 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2019-07-13</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B41" t="str">
-        <v>2019-07-14</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C41" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D41" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2019-06-29</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B42" t="str">
-        <v>2019-06-30</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C42" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D42" t="str">
         <v>居住</v>
@@ -1122,13 +1122,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2019-06-20</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B43" t="str">
-        <v>2019-06-25</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C43" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D43" t="str">
         <v>居住</v>
@@ -1139,16 +1139,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2019-06-07</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B44" t="str">
-        <v>2019-06-09</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C44" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D44" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1156,16 +1156,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B45" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C45" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D45" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1173,13 +1173,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B46" t="str">
-        <v>2019-05-04</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C46" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D46" t="str">
         <v>居住</v>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2019-04-04</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B47" t="str">
-        <v>2019-04-07</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C47" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D47" t="str">
         <v>旅行</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2019-02-10</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B48" t="str">
-        <v>2019-02-17</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C48" t="str">
-        <v>深圳 萌</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D48" t="str">
         <v>旅行</v>
@@ -1224,16 +1224,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2018-10-05</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B49" t="str">
-        <v>2018-10-07</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C49" t="str">
-        <v>广州·萌</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D49" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1241,13 +1241,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2018-10-01</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B50" t="str">
-        <v>2018-10-04</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C50" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D50" t="str">
         <v>旅行</v>
@@ -1258,13 +1258,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2018-06-01</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B51" t="str">
-        <v>2018-06-03</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C51" t="str">
-        <v>河北 秦皇河</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D51" t="str">
         <v>旅行</v>
@@ -1275,13 +1275,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2018-02-18</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B52" t="str">
-        <v>2018-02-25</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C52" t="str">
-        <v>广州 深圳</v>
+        <v>广州·萌</v>
       </c>
       <c r="D52" t="str">
         <v>旅行</v>
@@ -1292,16 +1292,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2018-02-02</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B53" t="str">
-        <v>2018-02-03</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C53" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D53" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1309,16 +1309,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2017-12-23</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B54" t="str">
-        <v>2017-22-24</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C54" t="str">
-        <v>上海·路演</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D54" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -1326,50 +1326,50 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2017-11-11</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B55" t="str">
-        <v>2017-11-16</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C55" t="str">
-        <v>小熊 北京</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D55" t="str">
         <v>旅行</v>
       </c>
       <c r="E55" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2017-10-10</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B56" t="str">
-        <v>2017-10-17</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C56" t="str">
-        <v>萌 北京</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D56" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E56" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2017-09-29</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B57" t="str">
-        <v>2017-10-09</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C57" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>上海·路演</v>
       </c>
       <c r="D57" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -1377,47 +1377,47 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2017-09-27</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B58" t="str">
-        <v>2017-09-29</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C58" t="str">
-        <v>萌 北京</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D58" t="str">
         <v>旅行</v>
       </c>
       <c r="E58" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2017-09-09</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B59" t="str">
-        <v>2017-09-10</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C59" t="str">
-        <v>武汉·游</v>
+        <v>萌 北京</v>
       </c>
       <c r="D59" t="str">
         <v>旅行</v>
       </c>
       <c r="E59" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2017-08-18</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B60" t="str">
-        <v>2017-08-20</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C60" t="str">
-        <v>萌 北京</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D60" t="str">
         <v>旅行</v>
@@ -1428,30 +1428,30 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2017-08-11</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B61" t="str">
-        <v>2017-08-13</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C61" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D61" t="str">
         <v>旅行</v>
       </c>
       <c r="E61" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2017-08-04</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B62" t="str">
-        <v>2017-08-07</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C62" t="str">
-        <v>武汉</v>
+        <v>武汉·游</v>
       </c>
       <c r="D62" t="str">
         <v>旅行</v>
@@ -1462,16 +1462,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2017-06-15</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B63" t="str">
-        <v>2020-06-15</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C63" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>萌 北京</v>
       </c>
       <c r="D63" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -1479,27 +1479,27 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2017-06-10</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B64" t="str">
-        <v>2017-06-11</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C64" t="str">
-        <v>萌 北京</v>
+        <v>武汉</v>
       </c>
       <c r="D64" t="str">
         <v>旅行</v>
       </c>
       <c r="E64" t="str">
-        <v/>
+        <v>大聚会</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2017-05-28</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B65" t="str">
-        <v>2017-05-30</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C65" t="str">
         <v>武汉</v>
@@ -1513,16 +1513,16 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2017-04-29</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B66" t="str">
-        <v>2017-05-01</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C66" t="str">
-        <v>大连 s</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D66" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -1530,13 +1530,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2017-04-21</v>
+        <v>2017-06-10</v>
       </c>
       <c r="B67" t="str">
-        <v>2017-04-23</v>
+        <v>2017-06-11</v>
       </c>
       <c r="C67" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D67" t="str">
         <v>旅行</v>
@@ -1547,16 +1547,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2017-03-13</v>
+        <v>2017-05-28</v>
       </c>
       <c r="B68" t="str">
-        <v>2017-03-13</v>
+        <v>2017-05-30</v>
       </c>
       <c r="C68" t="str">
-        <v>入职ZKDA</v>
+        <v>武汉</v>
       </c>
       <c r="D68" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2016-12-23</v>
+        <v>2017-04-29</v>
       </c>
       <c r="B69" t="str">
-        <v>2017-01-08</v>
+        <v>2017-05-01</v>
       </c>
       <c r="C69" t="str">
-        <v>武汉·徐东</v>
+        <v>大连 s</v>
       </c>
       <c r="D69" t="str">
         <v>旅行</v>
@@ -1581,10 +1581,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2016-10-07</v>
+        <v>2017-04-21</v>
       </c>
       <c r="B70" t="str">
-        <v>2016-10-14</v>
+        <v>2017-04-23</v>
       </c>
       <c r="C70" t="str">
         <v>武汉</v>
@@ -1598,16 +1598,16 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2016-10-01</v>
+        <v>2017-03-13</v>
       </c>
       <c r="B71" t="str">
-        <v>2016-10-07</v>
+        <v>2017-03-13</v>
       </c>
       <c r="C71" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>入职ZKDA</v>
       </c>
       <c r="D71" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -1615,100 +1615,100 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B72" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C72" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D72" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B73" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C73" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D73" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B74" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C74" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D74" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B72" t="str">
+      <c r="B75" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C72" t="str">
+      <c r="C75" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D72" t="str">
+      <c r="D75" t="str">
         <v>居住</v>
       </c>
-      <c r="E72" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="73" xml:space="preserve">
-      <c r="A73" t="str">
+      <c r="E75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76" xml:space="preserve">
+      <c r="A76" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B73" t="str">
+      <c r="B76" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C73" t="str">
+      <c r="C76" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D73" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E73" t="str" xml:space="preserve">
+      <c r="D76" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E76" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B74" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C74" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D74" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E74" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B75" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C75" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D75" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B76" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C76" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D76" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E76" t="str">
-        <v>343天</v>
-      </c>
-    </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2016-04-01</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B77" t="str">
-        <v>2016-04-04</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C77" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D77" t="str">
         <v>观演</v>
@@ -1719,13 +1719,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2015-12-31</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B78" t="str">
-        <v>2015-12-31</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C78" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D78" t="str">
         <v>观演</v>
@@ -1736,33 +1736,33 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2015-10-01</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B79" t="str">
-        <v>2015-10-07</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C79" t="str">
-        <v>大连 s</v>
+        <v>待业343天</v>
       </c>
       <c r="D79" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E79" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2015-06-09</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B80" t="str">
-        <v>2015-06-14</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C80" t="str">
-        <v>大连 s</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D80" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -1770,16 +1770,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2015-06-06</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B81" t="str">
-        <v>2015-06-08</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C81" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D81" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -1787,30 +1787,30 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2015-05-18</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B82" t="str">
-        <v>2016-07-16</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C82" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>大连 s</v>
       </c>
       <c r="D82" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E82" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2015-05-01</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B83" t="str">
-        <v>2015-05-03</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C83" t="str">
-        <v>大连·游 s</v>
+        <v>大连 s</v>
       </c>
       <c r="D83" t="str">
         <v>旅行</v>
@@ -1821,13 +1821,13 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2015-03-28</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B84" t="str">
-        <v>2015-03-29</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C84" t="str">
-        <v>大连 s</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D84" t="str">
         <v>旅行</v>
@@ -1838,30 +1838,30 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2015-03-27</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B85" t="str">
-        <v>2015-03-27</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C85" t="str">
-        <v>北京接 s</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D85" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E85" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2014-11-21</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B86" t="str">
-        <v>2014-11-23</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C86" t="str">
-        <v>天津旅游s</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D86" t="str">
         <v>旅行</v>
@@ -1872,16 +1872,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2014-11-10</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B87" t="str">
-        <v>2014-11-30</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C87" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连 s</v>
       </c>
       <c r="D87" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -1889,16 +1889,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2014-10-01</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B88" t="str">
-        <v>2014-10-01</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C88" t="str">
-        <v>青海聚五姨</v>
+        <v>北京接 s</v>
       </c>
       <c r="D88" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -1906,33 +1906,33 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2014-05-18</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B89" t="str">
-        <v>2015-05-18</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C89" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D89" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E89" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2014-05-01</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B90" t="str">
-        <v>2014-05-01</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C90" t="str">
-        <v>青海聚</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D90" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -1940,16 +1940,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2014-03-27</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B91" t="str">
-        <v>2014-03-27</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C91" t="str">
-        <v>二次入职世代泉源</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D91" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -1957,33 +1957,33 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2014-03-20</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B92" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C92" t="str">
-        <v>清缘商厦</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D92" t="str">
         <v>居住</v>
       </c>
       <c r="E92" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2014-03-20</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B93" t="str">
-        <v>2014-03-22</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C93" t="str">
-        <v>上海韩后全智贤</v>
+        <v>青海聚</v>
       </c>
       <c r="D93" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E93" t="str">
         <v/>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2013-11-26</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B94" t="str">
-        <v>2013-11-26</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C94" t="str">
-        <v>大连和s小聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D94" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -2008,16 +2008,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2013-06-11</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B95" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C95" t="str">
-        <v>青海聚</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D95" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -2025,33 +2025,33 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B96" t="str">
-        <v>2014-03-26</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C96" t="str">
-        <v>待业291天</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D96" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E96" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2013-06-07</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B97" t="str">
-        <v>2013-09-16</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C97" t="str">
-        <v>青海·海石湾</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D97" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -2059,16 +2059,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2013-02-01</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B98" t="str">
-        <v>2013-02-01</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C98" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>青海聚</v>
       </c>
       <c r="D98" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -2076,33 +2076,33 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2012-12-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B99" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C99" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>待业291天</v>
       </c>
       <c r="D99" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E99" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2012-11-04</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B100" t="str">
-        <v>2012-11-04</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C100" t="str">
-        <v>北京送返鸡西</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D100" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2012-09-24</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B101" t="str">
-        <v>2012-09-24</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C101" t="str">
-        <v>入职世代泉源</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D101" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2012-08-21</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B102" t="str">
-        <v>2012-08-23</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C102" t="str">
-        <v>辽宁兴城</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D102" t="str">
         <v>居住</v>
@@ -2144,16 +2144,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2012-02-07</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B103" t="str">
-        <v>2012-11-29</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C103" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D103" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -2161,16 +2161,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2012-02-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B104" t="str">
-        <v>2012-02-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C104" t="str">
-        <v>北京接站sister</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D104" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -2178,33 +2178,33 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2010-07-20</v>
+        <v>2012-08-21</v>
       </c>
       <c r="B105" t="str">
-        <v>2012-02-01</v>
+        <v>2012-08-23</v>
       </c>
       <c r="C105" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>辽宁兴城</v>
       </c>
       <c r="D105" t="str">
         <v>居住</v>
       </c>
       <c r="E105" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2010-07-01</v>
+        <v>2012-02-07</v>
       </c>
       <c r="B106" t="str">
-        <v>2011-12-01</v>
+        <v>2012-11-29</v>
       </c>
       <c r="C106" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京清河永泰庄新地标31-9-5</v>
       </c>
       <c r="D106" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E106" t="str">
         <v/>
@@ -2212,16 +2212,16 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2010-06-01</v>
+        <v>2012-02-01</v>
       </c>
       <c r="B107" t="str">
-        <v>2010-06-01</v>
+        <v>2012-02-01</v>
       </c>
       <c r="C107" t="str">
-        <v>高考</v>
+        <v>北京接站sister</v>
       </c>
       <c r="D107" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -2229,24 +2229,75 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B108" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C108" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D108" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E108" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B109" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C109" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D109" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B110" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C110" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D110" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B108" t="str">
+      <c r="B111" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C108" t="str">
+      <c r="C111" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D108" t="str">
+      <c r="D111" t="str">
         <v>其他</v>
       </c>
-      <c r="E108" t="str">
+      <c r="E111" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E118"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -425,33 +425,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2024-11-15</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-09-21</v>
+        <v>2025-09-07</v>
       </c>
       <c r="C2" t="str">
-        <v>松江区启民苑19栋1402</v>
+        <v>安徽·黄山</v>
       </c>
       <c r="D2" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>黄山&amp;宏村</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2024-09-17</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B3" t="str">
-        <v>2024-09-22</v>
+        <v>2025-08-31</v>
       </c>
       <c r="C3" t="str">
-        <v>北海涠洲岛·九寨沟·重庆</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D3" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -459,16 +459,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2024-05-01</v>
+        <v>2025-07-19</v>
       </c>
       <c r="B4" t="str">
-        <v>2024-05-01</v>
+        <v>2025-07-20</v>
       </c>
       <c r="C4" t="str">
-        <v>芜湖</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D4" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -476,13 +476,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2024-02-17</v>
+        <v>2025-06-28</v>
       </c>
       <c r="B5" t="str">
-        <v>2024-03-03</v>
+        <v>2025-06-29</v>
       </c>
       <c r="C5" t="str">
-        <v>浙百春巡 杭州/扬州/南京/无锡</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D5" t="str">
         <v>观演</v>
@@ -493,30 +493,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2023-12-31</v>
+        <v>2025-05-17</v>
       </c>
       <c r="B6" t="str">
-        <v>2023-12-31</v>
+        <v>2025-05-18</v>
       </c>
       <c r="C6" t="str">
-        <v>杭州·蝴蝶剧场</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D6" t="str">
         <v>观演</v>
       </c>
       <c r="E6" t="str">
-        <v>君霄</v>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2023-12-16</v>
+        <v>2025-03-22</v>
       </c>
       <c r="B7" t="str">
-        <v>2023-12-17</v>
+        <v>2025-03-22</v>
       </c>
       <c r="C7" t="str">
-        <v>杭州🍊☁️</v>
+        <v>苏州🦁GFY演唱会</v>
       </c>
       <c r="D7" t="str">
         <v>观演</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2023-12-02</v>
+        <v>2025-01-11</v>
       </c>
       <c r="B8" t="str">
-        <v>2023-12-03</v>
+        <v>2025-01-12</v>
       </c>
       <c r="C8" t="str">
-        <v>杭州/苏州 君霄/ZSH演唱会</v>
+        <v>广东·香港·LingOrm FM</v>
       </c>
       <c r="D8" t="str">
         <v>观演</v>
@@ -544,16 +544,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2023-11-25</v>
+        <v>2024-11-15</v>
       </c>
       <c r="B9" t="str">
-        <v>2023-11-16</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C9" t="str">
-        <v>武汉·小狮子音乐会🦁</v>
+        <v>松江区启民苑19栋1402</v>
       </c>
       <c r="D9" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -561,16 +561,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2023-11-17</v>
+        <v>2024-09-17</v>
       </c>
       <c r="B10" t="str">
-        <v>2023-11-19</v>
+        <v>2024-09-22</v>
       </c>
       <c r="C10" t="str">
-        <v>🐻·上海</v>
+        <v>北海涠洲岛·九寨沟·重庆</v>
       </c>
       <c r="D10" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2023-09-27</v>
+        <v>2024-05-01</v>
       </c>
       <c r="B11" t="str">
-        <v>2023-10-05</v>
+        <v>2024-05-01</v>
       </c>
       <c r="C11" t="str">
-        <v>温州百丈漈·常州·海宁·杭州周游记</v>
+        <v>芜湖</v>
       </c>
       <c r="D11" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,13 +595,13 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2023-09-23</v>
+        <v>2024-02-17</v>
       </c>
       <c r="B12" t="str">
-        <v>2023-09-23</v>
+        <v>2024-03-03</v>
       </c>
       <c r="C12" t="str">
-        <v>南京·小狮子音乐会🦁</v>
+        <v>浙百春巡 杭州/扬州/南京/无锡</v>
       </c>
       <c r="D12" t="str">
         <v>观演</v>
@@ -612,30 +612,30 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2023-09-16</v>
+        <v>2023-12-31</v>
       </c>
       <c r="B13" t="str">
-        <v>2023-09-16</v>
+        <v>2023-12-31</v>
       </c>
       <c r="C13" t="str">
-        <v>合肥·蔡依林演唱会</v>
+        <v>杭州·蝴蝶剧场</v>
       </c>
       <c r="D13" t="str">
         <v>观演</v>
       </c>
       <c r="E13" t="str">
-        <v/>
+        <v>君霄</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2023-09-09</v>
+        <v>2023-12-16</v>
       </c>
       <c r="B14" t="str">
-        <v>2023-09-09</v>
+        <v>2023-12-17</v>
       </c>
       <c r="C14" t="str">
-        <v>苏州·杨丞琳演唱会</v>
+        <v>杭州🍊☁️</v>
       </c>
       <c r="D14" t="str">
         <v>观演</v>
@@ -646,16 +646,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2023-08-19</v>
+        <v>2023-12-02</v>
       </c>
       <c r="B15" t="str">
-        <v>2023-08-20</v>
+        <v>2023-12-03</v>
       </c>
       <c r="C15" t="str">
-        <v>常州·S</v>
+        <v>杭州/苏州 君霄/ZSH演唱会</v>
       </c>
       <c r="D15" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -663,13 +663,13 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2023-07-22</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B16" t="str">
-        <v>2023-07-23</v>
+        <v>2023-11-16</v>
       </c>
       <c r="C16" t="str">
-        <v>青岛·小狮子音乐会🦁</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D16" t="str">
         <v>观演</v>
@@ -680,13 +680,13 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2023-05-20</v>
+        <v>2023-11-17</v>
       </c>
       <c r="B17" t="str">
-        <v>2023-05-21</v>
+        <v>2023-11-19</v>
       </c>
       <c r="C17" t="str">
-        <v>合肥·小狮子音乐会🦁</v>
+        <v>🐻·上海</v>
       </c>
       <c r="D17" t="str">
         <v>观演</v>
@@ -697,13 +697,13 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2023-04-14</v>
+        <v>2023-09-27</v>
       </c>
       <c r="B18" t="str">
-        <v>2023-04-16</v>
+        <v>2023-10-05</v>
       </c>
       <c r="C18" t="str">
-        <v>舟山·朱家尖 同事</v>
+        <v>温州百丈漈·常州·海宁·杭州周游记</v>
       </c>
       <c r="D18" t="str">
         <v>旅行</v>
@@ -714,16 +714,16 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2023-01-26</v>
+        <v>2023-09-23</v>
       </c>
       <c r="B19" t="str">
-        <v>2023-01-29</v>
+        <v>2023-09-23</v>
       </c>
       <c r="C19" t="str">
-        <v>福建·平潭岛 萌</v>
+        <v>南京·小狮子音乐会🦁</v>
       </c>
       <c r="D19" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -731,13 +731,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2022-12-31</v>
+        <v>2023-09-16</v>
       </c>
       <c r="B20" t="str">
-        <v>2023-01-02</v>
+        <v>2023-09-16</v>
       </c>
       <c r="C20" t="str">
-        <v>南昌·小狮子音乐会🦁</v>
+        <v>合肥·蔡依林演唱会</v>
       </c>
       <c r="D20" t="str">
         <v>观演</v>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2022-10-16</v>
+        <v>2023-09-09</v>
       </c>
       <c r="B21" t="str">
-        <v>2024-11-15</v>
+        <v>2023-09-09</v>
       </c>
       <c r="C21" t="str">
-        <v>松江区启民苑20栋201</v>
+        <v>苏州·杨丞琳演唱会</v>
       </c>
       <c r="D21" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,16 +765,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2021-10-31</v>
+        <v>2023-08-19</v>
       </c>
       <c r="B22" t="str">
-        <v>2022-10-31</v>
+        <v>2023-08-20</v>
       </c>
       <c r="C22" t="str">
-        <v>松江区启民苑15号楼102</v>
+        <v>常州·S</v>
       </c>
       <c r="D22" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,16 +782,16 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2021-10-05</v>
+        <v>2023-07-22</v>
       </c>
       <c r="B23" t="str">
-        <v>1007-01-01</v>
+        <v>2023-07-23</v>
       </c>
       <c r="C23" t="str">
-        <v>舟山·嵊泗岛 🧑🏻</v>
+        <v>青岛·小狮子音乐会🦁</v>
       </c>
       <c r="D23" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -799,16 +799,16 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2021-09-17</v>
+        <v>2023-05-20</v>
       </c>
       <c r="B24" t="str">
-        <v>2021-09-17</v>
+        <v>2023-05-21</v>
       </c>
       <c r="C24" t="str">
-        <v>舟山·海宁(杭州)·萌·鑫</v>
+        <v>合肥·小狮子音乐会🦁</v>
       </c>
       <c r="D24" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -816,13 +816,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2021-06-10</v>
+        <v>2023-04-14</v>
       </c>
       <c r="B25" t="str">
-        <v>2021-06-10</v>
+        <v>2023-04-16</v>
       </c>
       <c r="C25" t="str">
-        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
+        <v>舟山·朱家尖 同事</v>
       </c>
       <c r="D25" t="str">
         <v>旅行</v>
@@ -833,13 +833,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2021-05-01</v>
+        <v>2023-01-26</v>
       </c>
       <c r="B26" t="str">
-        <v>2021-05-01</v>
+        <v>2023-01-29</v>
       </c>
       <c r="C26" t="str">
-        <v>舟山·嵊泗岛 发小</v>
+        <v>福建·平潭岛 萌</v>
       </c>
       <c r="D26" t="str">
         <v>旅行</v>
@@ -850,16 +850,16 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2020-11-02</v>
+        <v>2022-12-31</v>
       </c>
       <c r="B27" t="str">
-        <v>2020-11-02</v>
+        <v>2023-01-02</v>
       </c>
       <c r="C27" t="str">
-        <v>入职上海齐獭</v>
+        <v>南昌·小狮子音乐会🦁</v>
       </c>
       <c r="D27" t="str">
-        <v>工作</v>
+        <v>观演</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -867,13 +867,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2020-08-09</v>
+        <v>2022-10-16</v>
       </c>
       <c r="B28" t="str">
-        <v>2021-11-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C28" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>松江区启民苑20栋201</v>
       </c>
       <c r="D28" t="str">
         <v>居住</v>
@@ -884,13 +884,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2020-07-31</v>
+        <v>2021-10-31</v>
       </c>
       <c r="B29" t="str">
-        <v>2020-07-31</v>
+        <v>2022-10-31</v>
       </c>
       <c r="C29" t="str">
-        <v>到达上海</v>
+        <v>松江区启民苑15号楼102</v>
       </c>
       <c r="D29" t="str">
         <v>居住</v>
@@ -901,16 +901,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2020-07-17</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B30" t="str">
-        <v>2020-07-31</v>
+        <v>1007-01-01</v>
       </c>
       <c r="C30" t="str">
-        <v>安徽 芜湖×宣城×马鞍山</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D30" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -918,13 +918,13 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2020-06-06</v>
+        <v>2021-09-17</v>
       </c>
       <c r="B31" t="str">
-        <v>2020-07-17</v>
+        <v>2021-09-17</v>
       </c>
       <c r="C31" t="str">
-        <v>❤️·厦门</v>
+        <v>舟山·海宁(杭州)·萌·鑫</v>
       </c>
       <c r="D31" t="str">
         <v>旅行</v>
@@ -935,13 +935,13 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2020-05-30</v>
+        <v>2021-06-10</v>
       </c>
       <c r="B32" t="str">
-        <v>2020-05-31</v>
+        <v>2021-06-10</v>
       </c>
       <c r="C32" t="str">
-        <v>秦皇岛</v>
+        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
       </c>
       <c r="D32" t="str">
         <v>旅行</v>
@@ -952,30 +952,30 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2020-05-29</v>
+        <v>2021-05-01</v>
       </c>
       <c r="B33" t="str">
-        <v>2020-11-01</v>
+        <v>2021-05-01</v>
       </c>
       <c r="C33" t="str">
-        <v>待业155天</v>
+        <v>舟山·嵊泗岛 发小</v>
       </c>
       <c r="D33" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E33" t="str">
-        <v>155天</v>
+        <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2020-05-29</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B34" t="str">
-        <v>2020-05-29</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C34" t="str">
-        <v>离职中科达奥</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D34" t="str">
         <v>工作</v>
@@ -986,16 +986,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2020-04-30</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B35" t="str">
-        <v>2020-05-05</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C35" t="str">
-        <v>❤·厦门</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D35" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2020-01-27</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B36" t="str">
-        <v>2020-02-04</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C36" t="str">
-        <v>❤·南京</v>
+        <v>到达上海</v>
       </c>
       <c r="D36" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1020,16 +1020,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2019-12-31</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B37" t="str">
-        <v>2020-01-05</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C37" t="str">
-        <v>❤·LangX 南京</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D37" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1037,13 +1037,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2019-11-29</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B38" t="str">
-        <v>2019-12-10</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C38" t="str">
-        <v>❤·北京</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D38" t="str">
         <v>旅行</v>
@@ -1054,13 +1054,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2019-09-26</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B39" t="str">
-        <v>2019-11-14</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C39" t="str">
-        <v>❤·北京</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D39" t="str">
         <v>旅行</v>
@@ -1071,33 +1071,33 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2019-09-13</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B40" t="str">
-        <v>2019-09-15</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C40" t="str">
-        <v>❤·秦皇岛</v>
+        <v>待业155天</v>
       </c>
       <c r="D40" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E40" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2019-08-22</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B41" t="str">
-        <v>2019-09-17</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C41" t="str">
-        <v>❤·北京</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D41" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2019-08-09</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B42" t="str">
-        <v>2019-08-11</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C42" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D42" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1122,16 +1122,16 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2019-07-26</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B43" t="str">
-        <v>2019-07-28</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C43" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>❤·南京</v>
       </c>
       <c r="D43" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1139,16 +1139,16 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2019-07-13</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B44" t="str">
-        <v>2019-07-14</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C44" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D44" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1156,16 +1156,16 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2019-06-29</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B45" t="str">
-        <v>2019-06-30</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C45" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D45" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1173,16 +1173,16 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2019-06-20</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B46" t="str">
-        <v>2019-06-25</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C46" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤·北京</v>
       </c>
       <c r="D46" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2019-06-07</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B47" t="str">
-        <v>2019-06-09</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C47" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D47" t="str">
         <v>旅行</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2019-05-01</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B48" t="str">
-        <v>2019-05-01</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C48" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>❤·北京</v>
       </c>
       <c r="D48" t="str">
         <v>旅行</v>
@@ -1224,13 +1224,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2019-05-01</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B49" t="str">
-        <v>2019-05-04</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C49" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D49" t="str">
         <v>居住</v>
@@ -1241,16 +1241,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2019-04-04</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B50" t="str">
-        <v>2019-04-07</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C50" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D50" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1258,16 +1258,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2019-02-10</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B51" t="str">
-        <v>2019-02-17</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C51" t="str">
-        <v>深圳 萌</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D51" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1275,16 +1275,16 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2018-10-05</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B52" t="str">
-        <v>2018-10-07</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C52" t="str">
-        <v>广州·萌</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D52" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -1292,16 +1292,16 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2018-10-01</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B53" t="str">
-        <v>2018-10-04</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C53" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D53" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -1309,13 +1309,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2018-06-01</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B54" t="str">
-        <v>2018-06-03</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C54" t="str">
-        <v>河北 秦皇河</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D54" t="str">
         <v>旅行</v>
@@ -1326,13 +1326,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2018-02-18</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B55" t="str">
-        <v>2018-02-25</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C55" t="str">
-        <v>广州 深圳</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D55" t="str">
         <v>旅行</v>
@@ -1343,16 +1343,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2018-02-02</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B56" t="str">
-        <v>2018-02-03</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C56" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D56" t="str">
-        <v>家庭</v>
+        <v>居住</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -1360,16 +1360,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2017-12-23</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B57" t="str">
-        <v>2017-22-24</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C57" t="str">
-        <v>上海·路演</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D57" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -1377,47 +1377,47 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2017-11-11</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B58" t="str">
-        <v>2017-11-16</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C58" t="str">
-        <v>小熊 北京</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D58" t="str">
         <v>旅行</v>
       </c>
       <c r="E58" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2017-10-10</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B59" t="str">
-        <v>2017-10-17</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C59" t="str">
-        <v>萌 北京</v>
+        <v>广州·萌</v>
       </c>
       <c r="D59" t="str">
         <v>旅行</v>
       </c>
       <c r="E59" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2017-09-29</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B60" t="str">
-        <v>2017-10-09</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C60" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D60" t="str">
         <v>旅行</v>
@@ -1428,13 +1428,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2017-09-27</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B61" t="str">
-        <v>2017-09-29</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C61" t="str">
-        <v>萌 北京</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D61" t="str">
         <v>旅行</v>
@@ -1445,13 +1445,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2017-09-09</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B62" t="str">
-        <v>2017-09-10</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C62" t="str">
-        <v>武汉·游</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D62" t="str">
         <v>旅行</v>
@@ -1462,16 +1462,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2017-08-18</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B63" t="str">
-        <v>2017-08-20</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C63" t="str">
-        <v>萌 北京</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D63" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -1479,64 +1479,64 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2017-08-11</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B64" t="str">
-        <v>2017-08-13</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C64" t="str">
-        <v>武汉</v>
+        <v>上海·路演</v>
       </c>
       <c r="D64" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E64" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2017-08-04</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B65" t="str">
-        <v>2017-08-07</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C65" t="str">
-        <v>武汉</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D65" t="str">
         <v>旅行</v>
       </c>
       <c r="E65" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2017-06-15</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B66" t="str">
-        <v>2020-06-15</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C66" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>萌 北京</v>
       </c>
       <c r="D66" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E66" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2017-06-10</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B67" t="str">
-        <v>2017-06-11</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C67" t="str">
-        <v>萌 北京</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D67" t="str">
         <v>旅行</v>
@@ -1547,13 +1547,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2017-05-28</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B68" t="str">
-        <v>2017-05-30</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C68" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D68" t="str">
         <v>旅行</v>
@@ -1564,13 +1564,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2017-04-29</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B69" t="str">
-        <v>2017-05-01</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C69" t="str">
-        <v>大连 s</v>
+        <v>武汉·游</v>
       </c>
       <c r="D69" t="str">
         <v>旅行</v>
@@ -1581,13 +1581,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2017-04-21</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B70" t="str">
-        <v>2017-04-23</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C70" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D70" t="str">
         <v>旅行</v>
@@ -1598,30 +1598,30 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2017-03-13</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B71" t="str">
-        <v>2017-03-13</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C71" t="str">
-        <v>入职ZKDA</v>
+        <v>武汉</v>
       </c>
       <c r="D71" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E71" t="str">
-        <v/>
+        <v>大聚会</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2016-12-23</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B72" t="str">
-        <v>2017-01-08</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C72" t="str">
-        <v>武汉·徐东</v>
+        <v>武汉</v>
       </c>
       <c r="D72" t="str">
         <v>旅行</v>
@@ -1632,16 +1632,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2016-10-07</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B73" t="str">
-        <v>2016-10-14</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C73" t="str">
-        <v>武汉</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D73" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -1649,13 +1649,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2016-10-01</v>
+        <v>2017-06-10</v>
       </c>
       <c r="B74" t="str">
-        <v>2016-10-07</v>
+        <v>2017-06-11</v>
       </c>
       <c r="C74" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>萌 北京</v>
       </c>
       <c r="D74" t="str">
         <v>旅行</v>
@@ -1666,171 +1666,171 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
+        <v>2017-05-28</v>
+      </c>
+      <c r="B75" t="str">
+        <v>2017-05-30</v>
+      </c>
+      <c r="C75" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D75" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>2017-04-29</v>
+      </c>
+      <c r="B76" t="str">
+        <v>2017-05-01</v>
+      </c>
+      <c r="C76" t="str">
+        <v>大连 s</v>
+      </c>
+      <c r="D76" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B77" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C77" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D77" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B78" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C78" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D78" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B79" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C79" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D79" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B80" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C80" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D80" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B81" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C81" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D81" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B75" t="str">
+      <c r="B82" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C75" t="str">
+      <c r="C82" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D75" t="str">
+      <c r="D82" t="str">
         <v>居住</v>
       </c>
-      <c r="E75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76" xml:space="preserve">
-      <c r="A76" t="str">
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83" xml:space="preserve">
+      <c r="A83" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B76" t="str">
+      <c r="B83" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C76" t="str">
+      <c r="C83" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D76" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E76" t="str" xml:space="preserve">
+      <c r="D83" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E83" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B77" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C77" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D77" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E77" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B78" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C78" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D78" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E78" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B79" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C79" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D79" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E79" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B80" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C80" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D80" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E80" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B81" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C81" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D81" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E81" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="str">
-        <v>2015-10-01</v>
-      </c>
-      <c r="B82" t="str">
-        <v>2015-10-07</v>
-      </c>
-      <c r="C82" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D82" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="str">
-        <v>2015-06-09</v>
-      </c>
-      <c r="B83" t="str">
-        <v>2015-06-14</v>
-      </c>
-      <c r="C83" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D83" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E83" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2015-06-06</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B84" t="str">
-        <v>2015-06-08</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C84" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D84" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -1838,50 +1838,50 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2015-05-18</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B85" t="str">
-        <v>2016-07-16</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C85" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D85" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E85" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2015-05-01</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B86" t="str">
-        <v>2015-05-03</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C86" t="str">
-        <v>大连·游 s</v>
+        <v>待业343天</v>
       </c>
       <c r="D86" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E86" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2015-03-28</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B87" t="str">
-        <v>2015-03-29</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C87" t="str">
-        <v>大连 s</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D87" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -1889,16 +1889,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2015-03-27</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B88" t="str">
-        <v>2015-03-27</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C88" t="str">
-        <v>北京接 s</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D88" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -1906,13 +1906,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2014-11-21</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B89" t="str">
-        <v>2014-11-23</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C89" t="str">
-        <v>天津旅游s</v>
+        <v>大连 s</v>
       </c>
       <c r="D89" t="str">
         <v>旅行</v>
@@ -1923,16 +1923,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2014-11-10</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B90" t="str">
-        <v>2014-11-30</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C90" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连 s</v>
       </c>
       <c r="D90" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -1940,13 +1940,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B91" t="str">
-        <v>2014-10-01</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C91" t="str">
-        <v>青海聚五姨</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D91" t="str">
         <v>旅行</v>
@@ -1957,30 +1957,30 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B92" t="str">
-        <v>2015-05-18</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C92" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D92" t="str">
         <v>居住</v>
       </c>
       <c r="E92" t="str">
-        <v>10400</v>
+        <v>11500</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B93" t="str">
-        <v>2014-05-01</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C93" t="str">
-        <v>青海聚</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D93" t="str">
         <v>旅行</v>
@@ -1991,16 +1991,16 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B94" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C94" t="str">
-        <v>二次入职世代泉源</v>
+        <v>大连 s</v>
       </c>
       <c r="D94" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E94" t="str">
         <v/>
@@ -2008,16 +2008,16 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2014-03-20</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B95" t="str">
-        <v>2014-05-18</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C95" t="str">
-        <v>清缘商厦</v>
+        <v>北京接 s</v>
       </c>
       <c r="D95" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E95" t="str">
         <v/>
@@ -2025,16 +2025,16 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B96" t="str">
-        <v>2014-03-22</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C96" t="str">
-        <v>上海韩后全智贤</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D96" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E96" t="str">
         <v/>
@@ -2042,13 +2042,13 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B97" t="str">
-        <v>2013-11-26</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C97" t="str">
-        <v>大连和s小聚</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D97" t="str">
         <v>其他</v>
@@ -2059,13 +2059,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2013-06-11</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B98" t="str">
-        <v>2013-09-16</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C98" t="str">
-        <v>青海聚</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D98" t="str">
         <v>旅行</v>
@@ -2076,33 +2076,33 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B99" t="str">
-        <v>2014-03-26</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C99" t="str">
-        <v>待业291天</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D99" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E99" t="str">
-        <v>291天</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2013-06-07</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B100" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C100" t="str">
-        <v>青海·海石湾</v>
+        <v>青海聚</v>
       </c>
       <c r="D100" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B101" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C101" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D101" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -2127,13 +2127,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2012-12-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B102" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C102" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D102" t="str">
         <v>居住</v>
@@ -2144,16 +2144,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B103" t="str">
-        <v>2012-11-04</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C103" t="str">
-        <v>北京送返鸡西</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D103" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -2161,16 +2161,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2012-09-24</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B104" t="str">
-        <v>2012-09-24</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C104" t="str">
-        <v>入职世代泉源</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D104" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -2178,16 +2178,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2012-08-21</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B105" t="str">
-        <v>2012-08-23</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C105" t="str">
-        <v>辽宁兴城</v>
+        <v>青海聚</v>
       </c>
       <c r="D105" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -2195,33 +2195,33 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2012-02-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B106" t="str">
-        <v>2012-11-29</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C106" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>待业291天</v>
       </c>
       <c r="D106" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E106" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2012-02-01</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B107" t="str">
-        <v>2012-02-01</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C107" t="str">
-        <v>北京接站sister</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D107" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -2229,33 +2229,33 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2010-07-20</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B108" t="str">
-        <v>2012-02-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C108" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D108" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E108" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2010-07-01</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B109" t="str">
-        <v>2011-12-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C109" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D109" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E109" t="str">
         <v/>
@@ -2263,16 +2263,16 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B110" t="str">
-        <v>2010-06-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C110" t="str">
-        <v>高考</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D110" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -2280,24 +2280,143 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="B111" t="str">
+        <v>2012-09-24</v>
+      </c>
+      <c r="C111" t="str">
+        <v>入职世代泉源</v>
+      </c>
+      <c r="D111" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B112" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C112" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D112" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B113" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C113" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D113" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B114" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C114" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D114" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B115" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C115" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D115" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E115" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B116" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C116" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D116" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B117" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C117" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D117" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B111" t="str">
+      <c r="B118" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C111" t="str">
+      <c r="C118" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D111" t="str">
+      <c r="D118" t="str">
         <v>其他</v>
       </c>
-      <c r="E111" t="str">
+      <c r="E118" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E118"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E121"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
@@ -425,33 +425,33 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2025-09-05</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B2" t="str">
-        <v>2025-09-07</v>
+        <v>2026-06-26</v>
       </c>
       <c r="C2" t="str">
-        <v>安徽·黄山</v>
+        <v>🦁常州生日会×2场</v>
       </c>
       <c r="D2" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E2" t="str">
-        <v>黄山&amp;宏村</v>
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2025-08-30</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B3" t="str">
-        <v>2025-08-31</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C3" t="str">
         <v>泰国·曼谷</v>
       </c>
       <c r="D3" t="str">
-        <v>观演</v>
+        <v>其他</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -459,16 +459,16 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2025-07-19</v>
+        <v>2026-02-17</v>
       </c>
       <c r="B4" t="str">
-        <v>2025-07-20</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C4" t="str">
-        <v>泰国·曼谷</v>
+        <v>云南·昆明大理丽江</v>
       </c>
       <c r="D4" t="str">
-        <v>观演</v>
+        <v>其他</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -476,27 +476,27 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-06-28</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-06-29</v>
+        <v>2025-09-07</v>
       </c>
       <c r="C5" t="str">
-        <v>泰国·曼谷</v>
+        <v>安徽·黄山</v>
       </c>
       <c r="D5" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E5" t="str">
-        <v/>
+        <v>黄山&amp;宏村</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-05-17</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-05-18</v>
+        <v>2025-08-31</v>
       </c>
       <c r="C6" t="str">
         <v>泰国·曼谷</v>
@@ -510,13 +510,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-03-22</v>
+        <v>2025-07-19</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-03-22</v>
+        <v>2025-07-20</v>
       </c>
       <c r="C7" t="str">
-        <v>苏州🦁GFY演唱会</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D7" t="str">
         <v>观演</v>
@@ -527,13 +527,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-01-11</v>
+        <v>2025-06-28</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-01-12</v>
+        <v>2025-06-29</v>
       </c>
       <c r="C8" t="str">
-        <v>广东·香港·LingOrm FM</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D8" t="str">
         <v>观演</v>
@@ -544,16 +544,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2024-11-15</v>
+        <v>2025-05-17</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-09-21</v>
+        <v>2025-05-18</v>
       </c>
       <c r="C9" t="str">
-        <v>松江区启民苑19栋1402</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D9" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -561,16 +561,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2024-09-17</v>
+        <v>2025-03-22</v>
       </c>
       <c r="B10" t="str">
-        <v>2024-09-22</v>
+        <v>2025-03-22</v>
       </c>
       <c r="C10" t="str">
-        <v>北海涠洲岛·九寨沟·重庆</v>
+        <v>苏州🦁GFY演唱会</v>
       </c>
       <c r="D10" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -578,16 +578,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2024-05-01</v>
+        <v>2025-01-11</v>
       </c>
       <c r="B11" t="str">
-        <v>2024-05-01</v>
+        <v>2025-01-12</v>
       </c>
       <c r="C11" t="str">
-        <v>芜湖</v>
+        <v>广东·香港·LingOrm FM</v>
       </c>
       <c r="D11" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -595,16 +595,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2024-02-17</v>
+        <v>2024-11-15</v>
       </c>
       <c r="B12" t="str">
-        <v>2024-03-03</v>
+        <v>2026-09-21</v>
       </c>
       <c r="C12" t="str">
-        <v>浙百春巡 杭州/扬州/南京/无锡</v>
+        <v>松江区启民苑19栋1402</v>
       </c>
       <c r="D12" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -612,33 +612,33 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2023-12-31</v>
+        <v>2024-09-17</v>
       </c>
       <c r="B13" t="str">
-        <v>2023-12-31</v>
+        <v>2024-09-22</v>
       </c>
       <c r="C13" t="str">
-        <v>杭州·蝴蝶剧场</v>
+        <v>北海涠洲岛·九寨沟·重庆</v>
       </c>
       <c r="D13" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E13" t="str">
-        <v>君霄</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2023-12-16</v>
+        <v>2024-05-01</v>
       </c>
       <c r="B14" t="str">
-        <v>2023-12-17</v>
+        <v>2024-05-01</v>
       </c>
       <c r="C14" t="str">
-        <v>杭州🍊☁️</v>
+        <v>芜湖</v>
       </c>
       <c r="D14" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -646,13 +646,13 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2023-12-02</v>
+        <v>2024-02-17</v>
       </c>
       <c r="B15" t="str">
-        <v>2023-12-03</v>
+        <v>2024-03-03</v>
       </c>
       <c r="C15" t="str">
-        <v>杭州/苏州 君霄/ZSH演唱会</v>
+        <v>浙百春巡 杭州/扬州/南京/无锡</v>
       </c>
       <c r="D15" t="str">
         <v>观演</v>
@@ -663,30 +663,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2023-11-25</v>
+        <v>2023-12-31</v>
       </c>
       <c r="B16" t="str">
-        <v>2023-11-16</v>
+        <v>2023-12-31</v>
       </c>
       <c r="C16" t="str">
-        <v>武汉·小狮子音乐会🦁</v>
+        <v>杭州·蝴蝶剧场</v>
       </c>
       <c r="D16" t="str">
         <v>观演</v>
       </c>
       <c r="E16" t="str">
-        <v/>
+        <v>君霄</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2023-11-17</v>
+        <v>2023-12-16</v>
       </c>
       <c r="B17" t="str">
-        <v>2023-11-19</v>
+        <v>2023-12-17</v>
       </c>
       <c r="C17" t="str">
-        <v>🐻·上海</v>
+        <v>杭州🍊☁️</v>
       </c>
       <c r="D17" t="str">
         <v>观演</v>
@@ -697,16 +697,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2023-09-27</v>
+        <v>2023-12-02</v>
       </c>
       <c r="B18" t="str">
-        <v>2023-10-05</v>
+        <v>2023-12-03</v>
       </c>
       <c r="C18" t="str">
-        <v>温州百丈漈·常州·海宁·杭州周游记</v>
+        <v>杭州/苏州 君霄/ZSH演唱会</v>
       </c>
       <c r="D18" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -714,13 +714,13 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2023-09-23</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B19" t="str">
-        <v>2023-09-23</v>
+        <v>2023-11-16</v>
       </c>
       <c r="C19" t="str">
-        <v>南京·小狮子音乐会🦁</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D19" t="str">
         <v>观演</v>
@@ -731,13 +731,13 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2023-09-16</v>
+        <v>2023-11-17</v>
       </c>
       <c r="B20" t="str">
-        <v>2023-09-16</v>
+        <v>2023-11-19</v>
       </c>
       <c r="C20" t="str">
-        <v>合肥·蔡依林演唱会</v>
+        <v>🐻·上海</v>
       </c>
       <c r="D20" t="str">
         <v>观演</v>
@@ -748,16 +748,16 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2023-09-09</v>
+        <v>2023-09-27</v>
       </c>
       <c r="B21" t="str">
-        <v>2023-09-09</v>
+        <v>2023-10-05</v>
       </c>
       <c r="C21" t="str">
-        <v>苏州·杨丞琳演唱会</v>
+        <v>温州百丈漈·常州·海宁·杭州周游记</v>
       </c>
       <c r="D21" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -765,16 +765,16 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2023-08-19</v>
+        <v>2023-09-23</v>
       </c>
       <c r="B22" t="str">
-        <v>2023-08-20</v>
+        <v>2023-09-23</v>
       </c>
       <c r="C22" t="str">
-        <v>常州·S</v>
+        <v>南京·小狮子音乐会🦁</v>
       </c>
       <c r="D22" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -782,13 +782,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2023-07-22</v>
+        <v>2023-09-16</v>
       </c>
       <c r="B23" t="str">
-        <v>2023-07-23</v>
+        <v>2023-09-16</v>
       </c>
       <c r="C23" t="str">
-        <v>青岛·小狮子音乐会🦁</v>
+        <v>合肥·蔡依林演唱会</v>
       </c>
       <c r="D23" t="str">
         <v>观演</v>
@@ -799,13 +799,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2023-05-20</v>
+        <v>2023-09-09</v>
       </c>
       <c r="B24" t="str">
-        <v>2023-05-21</v>
+        <v>2023-09-09</v>
       </c>
       <c r="C24" t="str">
-        <v>合肥·小狮子音乐会🦁</v>
+        <v>苏州·杨丞琳演唱会</v>
       </c>
       <c r="D24" t="str">
         <v>观演</v>
@@ -816,13 +816,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2023-04-14</v>
+        <v>2023-08-19</v>
       </c>
       <c r="B25" t="str">
-        <v>2023-04-16</v>
+        <v>2023-08-20</v>
       </c>
       <c r="C25" t="str">
-        <v>舟山·朱家尖 同事</v>
+        <v>常州·S</v>
       </c>
       <c r="D25" t="str">
         <v>旅行</v>
@@ -833,16 +833,16 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2023-01-26</v>
+        <v>2023-07-22</v>
       </c>
       <c r="B26" t="str">
-        <v>2023-01-29</v>
+        <v>2023-07-23</v>
       </c>
       <c r="C26" t="str">
-        <v>福建·平潭岛 萌</v>
+        <v>青岛·小狮子音乐会🦁</v>
       </c>
       <c r="D26" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -850,13 +850,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2022-12-31</v>
+        <v>2023-05-20</v>
       </c>
       <c r="B27" t="str">
-        <v>2023-01-02</v>
+        <v>2023-05-21</v>
       </c>
       <c r="C27" t="str">
-        <v>南昌·小狮子音乐会🦁</v>
+        <v>合肥·小狮子音乐会🦁</v>
       </c>
       <c r="D27" t="str">
         <v>观演</v>
@@ -867,16 +867,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2022-10-16</v>
+        <v>2023-04-14</v>
       </c>
       <c r="B28" t="str">
-        <v>2024-11-15</v>
+        <v>2023-04-16</v>
       </c>
       <c r="C28" t="str">
-        <v>松江区启民苑20栋201</v>
+        <v>舟山·朱家尖 同事</v>
       </c>
       <c r="D28" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -884,16 +884,16 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2021-10-31</v>
+        <v>2023-01-26</v>
       </c>
       <c r="B29" t="str">
-        <v>2022-10-31</v>
+        <v>2023-01-29</v>
       </c>
       <c r="C29" t="str">
-        <v>松江区启民苑15号楼102</v>
+        <v>福建·平潭岛 萌</v>
       </c>
       <c r="D29" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E29" t="str">
         <v/>
@@ -901,16 +901,16 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2021-10-05</v>
+        <v>2022-12-31</v>
       </c>
       <c r="B30" t="str">
-        <v>1007-01-01</v>
+        <v>2023-01-02</v>
       </c>
       <c r="C30" t="str">
-        <v>舟山·嵊泗岛 🧑🏻</v>
+        <v>南昌·小狮子音乐会🦁</v>
       </c>
       <c r="D30" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E30" t="str">
         <v/>
@@ -918,16 +918,16 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2021-09-17</v>
+        <v>2022-10-16</v>
       </c>
       <c r="B31" t="str">
-        <v>2021-09-17</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C31" t="str">
-        <v>舟山·海宁(杭州)·萌·鑫</v>
+        <v>松江区启民苑20栋201</v>
       </c>
       <c r="D31" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E31" t="str">
         <v/>
@@ -935,16 +935,16 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2021-06-10</v>
+        <v>2021-10-31</v>
       </c>
       <c r="B32" t="str">
-        <v>2021-06-10</v>
+        <v>2022-10-31</v>
       </c>
       <c r="C32" t="str">
-        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
+        <v>松江区启民苑15号楼102</v>
       </c>
       <c r="D32" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -952,13 +952,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2021-05-01</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B33" t="str">
-        <v>2021-05-01</v>
+        <v>1007-01-01</v>
       </c>
       <c r="C33" t="str">
-        <v>舟山·嵊泗岛 发小</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D33" t="str">
         <v>旅行</v>
@@ -969,16 +969,16 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2020-11-02</v>
+        <v>2021-09-17</v>
       </c>
       <c r="B34" t="str">
-        <v>2020-11-02</v>
+        <v>2021-09-17</v>
       </c>
       <c r="C34" t="str">
-        <v>入职上海齐獭</v>
+        <v>舟山·海宁(杭州)·萌·鑫</v>
       </c>
       <c r="D34" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -986,16 +986,16 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2020-08-09</v>
+        <v>2021-06-10</v>
       </c>
       <c r="B35" t="str">
-        <v>2021-11-01</v>
+        <v>2021-06-10</v>
       </c>
       <c r="C35" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
       </c>
       <c r="D35" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1003,16 +1003,16 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2020-07-31</v>
+        <v>2021-05-01</v>
       </c>
       <c r="B36" t="str">
-        <v>2020-07-31</v>
+        <v>2021-05-01</v>
       </c>
       <c r="C36" t="str">
-        <v>到达上海</v>
+        <v>舟山·嵊泗岛 发小</v>
       </c>
       <c r="D36" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1020,16 +1020,16 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2020-07-17</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B37" t="str">
-        <v>2020-07-31</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C37" t="str">
-        <v>安徽 芜湖×宣城×马鞍山</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D37" t="str">
-        <v>家庭</v>
+        <v>工作</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1037,16 +1037,16 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2020-06-06</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B38" t="str">
-        <v>2020-07-17</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C38" t="str">
-        <v>❤️·厦门</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D38" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1054,16 +1054,16 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2020-05-30</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B39" t="str">
-        <v>2020-05-31</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C39" t="str">
-        <v>秦皇岛</v>
+        <v>到达上海</v>
       </c>
       <c r="D39" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1071,33 +1071,33 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B40" t="str">
-        <v>2020-11-01</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C40" t="str">
-        <v>待业155天</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D40" t="str">
-        <v>其他</v>
+        <v>家庭</v>
       </c>
       <c r="E40" t="str">
-        <v>155天</v>
+        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2020-05-29</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B41" t="str">
-        <v>2020-05-29</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C41" t="str">
-        <v>离职中科达奥</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D41" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2020-04-30</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B42" t="str">
-        <v>2020-05-05</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C42" t="str">
-        <v>❤·厦门</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D42" t="str">
         <v>旅行</v>
@@ -1122,33 +1122,33 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2020-01-27</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B43" t="str">
-        <v>2020-02-04</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C43" t="str">
-        <v>❤·南京</v>
+        <v>待业155天</v>
       </c>
       <c r="D43" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E43" t="str">
-        <v/>
+        <v>155天</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2019-12-31</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B44" t="str">
-        <v>2020-01-05</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C44" t="str">
-        <v>❤·LangX 南京</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D44" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1156,13 +1156,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2019-11-29</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B45" t="str">
-        <v>2019-12-10</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C45" t="str">
-        <v>❤·北京</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D45" t="str">
         <v>旅行</v>
@@ -1173,13 +1173,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2019-09-26</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B46" t="str">
-        <v>2019-11-14</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C46" t="str">
-        <v>❤·北京</v>
+        <v>❤·南京</v>
       </c>
       <c r="D46" t="str">
         <v>旅行</v>
@@ -1190,13 +1190,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2019-09-13</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B47" t="str">
-        <v>2019-09-15</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C47" t="str">
-        <v>❤·秦皇岛</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D47" t="str">
         <v>旅行</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2019-08-22</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B48" t="str">
-        <v>2019-09-17</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C48" t="str">
         <v>❤·北京</v>
@@ -1224,16 +1224,16 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2019-08-09</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B49" t="str">
-        <v>2019-08-11</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C49" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>❤·北京</v>
       </c>
       <c r="D49" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -1241,16 +1241,16 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2019-07-26</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B50" t="str">
-        <v>2019-07-28</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C50" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D50" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -1258,16 +1258,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2019-07-13</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B51" t="str">
-        <v>2019-07-14</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C51" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D51" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -1275,13 +1275,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2019-06-29</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B52" t="str">
-        <v>2019-06-30</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C52" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D52" t="str">
         <v>居住</v>
@@ -1292,13 +1292,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2019-06-20</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B53" t="str">
-        <v>2019-06-25</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C53" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D53" t="str">
         <v>居住</v>
@@ -1309,16 +1309,16 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2019-06-07</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B54" t="str">
-        <v>2019-06-09</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C54" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D54" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -1326,16 +1326,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B55" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C55" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D55" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -1343,13 +1343,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2019-05-01</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B56" t="str">
-        <v>2019-05-04</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C56" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D56" t="str">
         <v>居住</v>
@@ -1360,13 +1360,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2019-04-04</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B57" t="str">
-        <v>2019-04-07</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C57" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D57" t="str">
         <v>旅行</v>
@@ -1377,13 +1377,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2019-02-10</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B58" t="str">
-        <v>2019-02-17</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C58" t="str">
-        <v>深圳 萌</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D58" t="str">
         <v>旅行</v>
@@ -1394,16 +1394,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2018-10-05</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B59" t="str">
-        <v>2018-10-07</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C59" t="str">
-        <v>广州·萌</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D59" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -1411,13 +1411,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2018-10-01</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B60" t="str">
-        <v>2018-10-04</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C60" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D60" t="str">
         <v>旅行</v>
@@ -1428,13 +1428,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2018-06-01</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B61" t="str">
-        <v>2018-06-03</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C61" t="str">
-        <v>河北 秦皇河</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D61" t="str">
         <v>旅行</v>
@@ -1445,13 +1445,13 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2018-02-18</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B62" t="str">
-        <v>2018-02-25</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C62" t="str">
-        <v>广州 深圳</v>
+        <v>广州·萌</v>
       </c>
       <c r="D62" t="str">
         <v>旅行</v>
@@ -1462,16 +1462,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2018-02-02</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B63" t="str">
-        <v>2018-02-03</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C63" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D63" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -1479,16 +1479,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2017-12-23</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B64" t="str">
-        <v>2017-22-24</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C64" t="str">
-        <v>上海·路演</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D64" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -1496,50 +1496,50 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2017-11-11</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B65" t="str">
-        <v>2017-11-16</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C65" t="str">
-        <v>小熊 北京</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D65" t="str">
         <v>旅行</v>
       </c>
       <c r="E65" t="str">
-        <v>Z97</v>
+        <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2017-10-10</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B66" t="str">
-        <v>2017-10-17</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C66" t="str">
-        <v>萌 北京</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D66" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E66" t="str">
-        <v>11:47</v>
+        <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2017-09-29</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B67" t="str">
-        <v>2017-10-09</v>
+        <v>2017-22-24</v>
       </c>
       <c r="C67" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>上海·路演</v>
       </c>
       <c r="D67" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -1547,47 +1547,47 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2017-09-27</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B68" t="str">
-        <v>2017-09-29</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C68" t="str">
-        <v>萌 北京</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D68" t="str">
         <v>旅行</v>
       </c>
       <c r="E68" t="str">
-        <v/>
+        <v>Z97</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2017-09-09</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B69" t="str">
-        <v>2017-09-10</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C69" t="str">
-        <v>武汉·游</v>
+        <v>萌 北京</v>
       </c>
       <c r="D69" t="str">
         <v>旅行</v>
       </c>
       <c r="E69" t="str">
-        <v/>
+        <v>11:47</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2017-08-18</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B70" t="str">
-        <v>2017-08-20</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C70" t="str">
-        <v>萌 北京</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D70" t="str">
         <v>旅行</v>
@@ -1598,30 +1598,30 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2017-08-11</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B71" t="str">
-        <v>2017-08-13</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C71" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D71" t="str">
         <v>旅行</v>
       </c>
       <c r="E71" t="str">
-        <v>大聚会</v>
+        <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2017-08-04</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B72" t="str">
-        <v>2017-08-07</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C72" t="str">
-        <v>武汉</v>
+        <v>武汉·游</v>
       </c>
       <c r="D72" t="str">
         <v>旅行</v>
@@ -1632,16 +1632,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2017-06-15</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B73" t="str">
-        <v>2020-06-15</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C73" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>萌 北京</v>
       </c>
       <c r="D73" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -1649,27 +1649,27 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2017-06-10</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B74" t="str">
-        <v>2017-06-11</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C74" t="str">
-        <v>萌 北京</v>
+        <v>武汉</v>
       </c>
       <c r="D74" t="str">
         <v>旅行</v>
       </c>
       <c r="E74" t="str">
-        <v/>
+        <v>大聚会</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2017-05-28</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B75" t="str">
-        <v>2017-05-30</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C75" t="str">
         <v>武汉</v>
@@ -1683,16 +1683,16 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2017-04-29</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B76" t="str">
-        <v>2017-05-01</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C76" t="str">
-        <v>大连 s</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D76" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -1700,13 +1700,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2017-04-21</v>
+        <v>2017-06-10</v>
       </c>
       <c r="B77" t="str">
-        <v>2017-04-23</v>
+        <v>2017-06-11</v>
       </c>
       <c r="C77" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D77" t="str">
         <v>旅行</v>
@@ -1717,16 +1717,16 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2017-03-13</v>
+        <v>2017-05-28</v>
       </c>
       <c r="B78" t="str">
-        <v>2017-03-13</v>
+        <v>2017-05-30</v>
       </c>
       <c r="C78" t="str">
-        <v>入职ZKDA</v>
+        <v>武汉</v>
       </c>
       <c r="D78" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -1734,13 +1734,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2016-12-23</v>
+        <v>2017-04-29</v>
       </c>
       <c r="B79" t="str">
-        <v>2017-01-08</v>
+        <v>2017-05-01</v>
       </c>
       <c r="C79" t="str">
-        <v>武汉·徐东</v>
+        <v>大连 s</v>
       </c>
       <c r="D79" t="str">
         <v>旅行</v>
@@ -1751,10 +1751,10 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2016-10-07</v>
+        <v>2017-04-21</v>
       </c>
       <c r="B80" t="str">
-        <v>2016-10-14</v>
+        <v>2017-04-23</v>
       </c>
       <c r="C80" t="str">
         <v>武汉</v>
@@ -1768,16 +1768,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2016-10-01</v>
+        <v>2017-03-13</v>
       </c>
       <c r="B81" t="str">
-        <v>2016-10-07</v>
+        <v>2017-03-13</v>
       </c>
       <c r="C81" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>入职ZKDA</v>
       </c>
       <c r="D81" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -1785,100 +1785,100 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B82" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C82" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D82" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B83" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C83" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D83" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B84" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C84" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D84" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B82" t="str">
+      <c r="B85" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C82" t="str">
+      <c r="C85" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D82" t="str">
+      <c r="D85" t="str">
         <v>居住</v>
       </c>
-      <c r="E82" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="83" xml:space="preserve">
-      <c r="A83" t="str">
+      <c r="E85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86" xml:space="preserve">
+      <c r="A86" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B83" t="str">
+      <c r="B86" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C83" t="str">
+      <c r="C86" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D83" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E83" t="str" xml:space="preserve">
+      <c r="D86" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E86" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B84" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C84" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D84" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E84" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B85" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C85" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D85" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B86" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C86" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D86" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E86" t="str">
-        <v>343天</v>
-      </c>
-    </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2016-04-01</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B87" t="str">
-        <v>2016-04-04</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C87" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D87" t="str">
         <v>观演</v>
@@ -1889,13 +1889,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2015-12-31</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B88" t="str">
-        <v>2015-12-31</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C88" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D88" t="str">
         <v>观演</v>
@@ -1906,33 +1906,33 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2015-10-01</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B89" t="str">
-        <v>2015-10-07</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C89" t="str">
-        <v>大连 s</v>
+        <v>待业343天</v>
       </c>
       <c r="D89" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E89" t="str">
-        <v/>
+        <v>343天</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2015-06-09</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B90" t="str">
-        <v>2015-06-14</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C90" t="str">
-        <v>大连 s</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D90" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -1940,16 +1940,16 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2015-06-06</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B91" t="str">
-        <v>2015-06-08</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C91" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D91" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -1957,30 +1957,30 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2015-05-18</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B92" t="str">
-        <v>2016-07-16</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C92" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>大连 s</v>
       </c>
       <c r="D92" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E92" t="str">
-        <v>11500</v>
+        <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2015-05-01</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B93" t="str">
-        <v>2015-05-03</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C93" t="str">
-        <v>大连·游 s</v>
+        <v>大连 s</v>
       </c>
       <c r="D93" t="str">
         <v>旅行</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2015-03-28</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B94" t="str">
-        <v>2015-03-29</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C94" t="str">
-        <v>大连 s</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D94" t="str">
         <v>旅行</v>
@@ -2008,30 +2008,30 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2015-03-27</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B95" t="str">
-        <v>2015-03-27</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C95" t="str">
-        <v>北京接 s</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D95" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E95" t="str">
-        <v/>
+        <v>11500</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2014-11-21</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B96" t="str">
-        <v>2014-11-23</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C96" t="str">
-        <v>天津旅游s</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D96" t="str">
         <v>旅行</v>
@@ -2042,16 +2042,16 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2014-11-10</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B97" t="str">
-        <v>2014-11-30</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C97" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>大连 s</v>
       </c>
       <c r="D97" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E97" t="str">
         <v/>
@@ -2059,16 +2059,16 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2014-10-01</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B98" t="str">
-        <v>2014-10-01</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C98" t="str">
-        <v>青海聚五姨</v>
+        <v>北京接 s</v>
       </c>
       <c r="D98" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E98" t="str">
         <v/>
@@ -2076,33 +2076,33 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2014-05-18</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B99" t="str">
-        <v>2015-05-18</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C99" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D99" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E99" t="str">
-        <v>10400</v>
+        <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2014-05-01</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B100" t="str">
-        <v>2014-05-01</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C100" t="str">
-        <v>青海聚</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D100" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E100" t="str">
         <v/>
@@ -2110,16 +2110,16 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2014-03-27</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B101" t="str">
-        <v>2014-03-27</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C101" t="str">
-        <v>二次入职世代泉源</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D101" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E101" t="str">
         <v/>
@@ -2127,33 +2127,33 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2014-03-20</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B102" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C102" t="str">
-        <v>清缘商厦</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D102" t="str">
         <v>居住</v>
       </c>
       <c r="E102" t="str">
-        <v/>
+        <v>10400</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2014-03-20</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B103" t="str">
-        <v>2014-03-22</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C103" t="str">
-        <v>上海韩后全智贤</v>
+        <v>青海聚</v>
       </c>
       <c r="D103" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E103" t="str">
         <v/>
@@ -2161,16 +2161,16 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2013-11-26</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B104" t="str">
-        <v>2013-11-26</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C104" t="str">
-        <v>大连和s小聚</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D104" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E104" t="str">
         <v/>
@@ -2178,16 +2178,16 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2013-06-11</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B105" t="str">
-        <v>2013-09-16</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C105" t="str">
-        <v>青海聚</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D105" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E105" t="str">
         <v/>
@@ -2195,33 +2195,33 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B106" t="str">
-        <v>2014-03-26</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C106" t="str">
-        <v>待业291天</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D106" t="str">
-        <v>其他</v>
+        <v>观演</v>
       </c>
       <c r="E106" t="str">
-        <v>291天</v>
+        <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2013-06-07</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B107" t="str">
-        <v>2013-09-16</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C107" t="str">
-        <v>青海·海石湾</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D107" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E107" t="str">
         <v/>
@@ -2229,16 +2229,16 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2013-02-01</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B108" t="str">
-        <v>2013-02-01</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C108" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>青海聚</v>
       </c>
       <c r="D108" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E108" t="str">
         <v/>
@@ -2246,33 +2246,33 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2012-12-07</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B109" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C109" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>待业291天</v>
       </c>
       <c r="D109" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E109" t="str">
-        <v/>
+        <v>291天</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2012-11-04</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B110" t="str">
-        <v>2012-11-04</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C110" t="str">
-        <v>北京送返鸡西</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D110" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E110" t="str">
         <v/>
@@ -2280,16 +2280,16 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2012-09-24</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B111" t="str">
-        <v>2012-09-24</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C111" t="str">
-        <v>入职世代泉源</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D111" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E111" t="str">
         <v/>
@@ -2297,13 +2297,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2012-08-21</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B112" t="str">
-        <v>2012-08-23</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C112" t="str">
-        <v>辽宁兴城</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D112" t="str">
         <v>居住</v>
@@ -2314,16 +2314,16 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2012-02-07</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B113" t="str">
-        <v>2012-11-29</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C113" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D113" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E113" t="str">
         <v/>
@@ -2331,16 +2331,16 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2012-02-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B114" t="str">
-        <v>2012-02-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C114" t="str">
-        <v>北京接站sister</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D114" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E114" t="str">
         <v/>
@@ -2348,33 +2348,33 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2010-07-20</v>
+        <v>2012-08-21</v>
       </c>
       <c r="B115" t="str">
-        <v>2012-02-01</v>
+        <v>2012-08-23</v>
       </c>
       <c r="C115" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>辽宁兴城</v>
       </c>
       <c r="D115" t="str">
         <v>居住</v>
       </c>
       <c r="E115" t="str">
-        <v>宿舍</v>
+        <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2010-07-01</v>
+        <v>2012-02-07</v>
       </c>
       <c r="B116" t="str">
-        <v>2011-12-01</v>
+        <v>2012-11-29</v>
       </c>
       <c r="C116" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京清河永泰庄新地标31-9-5</v>
       </c>
       <c r="D116" t="str">
-        <v>学业</v>
+        <v>居住</v>
       </c>
       <c r="E116" t="str">
         <v/>
@@ -2382,16 +2382,16 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2010-06-01</v>
+        <v>2012-02-01</v>
       </c>
       <c r="B117" t="str">
-        <v>2010-06-01</v>
+        <v>2012-02-01</v>
       </c>
       <c r="C117" t="str">
-        <v>高考</v>
+        <v>北京接站sister</v>
       </c>
       <c r="D117" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E117" t="str">
         <v/>
@@ -2399,24 +2399,75 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B118" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C118" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D118" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E118" t="str">
+        <v>宿舍</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B119" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C119" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D119" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B120" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C120" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D120" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B118" t="str">
+      <c r="B121" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C118" t="str">
+      <c r="C121" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D118" t="str">
+      <c r="D121" t="str">
         <v>其他</v>
       </c>
-      <c r="E118" t="str">
+      <c r="E121" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E121"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/time.xlsx
+++ b/data/time.xlsx
@@ -4,6 +4,7 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="events" sheetId="1" r:id="rId1"/>
+    <sheet name="规则" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -397,13 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:G127"/>
   <cols>
     <col min="1" max="1" width="13.83203125" customWidth="1"/>
     <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="34.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="24.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
+    <col min="7" max="7" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -422,13 +425,19 @@
       <c r="E1" t="str">
         <v>备注</v>
       </c>
+      <c r="F1" t="str">
+        <v>重要(手动)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>规则判定</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>2026-06-27</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-26</v>
+        <v>2026-06-27</v>
       </c>
       <c r="C2" t="str">
         <v>🦁常州生日会×2场</v>
@@ -439,16 +448,22 @@
       <c r="E2" t="str">
         <v/>
       </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-04-04</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-05</v>
+        <v>2026-06-27</v>
       </c>
       <c r="C3" t="str">
-        <v>泰国·曼谷</v>
+        <v>🦁常州生日会×2场</v>
       </c>
       <c r="D3" t="str">
         <v>其他</v>
@@ -456,16 +471,22 @@
       <c r="E3" t="str">
         <v/>
       </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-02-17</v>
+        <v>2026-06-27</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-25</v>
+        <v>2026-06-27</v>
       </c>
       <c r="C4" t="str">
-        <v>云南·昆明大理丽江</v>
+        <v>🦁常州生日会×2场</v>
       </c>
       <c r="D4" t="str">
         <v>其他</v>
@@ -473,64 +494,88 @@
       <c r="E4" t="str">
         <v/>
       </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2025-09-05</v>
+        <v>2026-04-04</v>
       </c>
       <c r="B5" t="str">
-        <v>2025-09-07</v>
+        <v>2026-04-05</v>
       </c>
       <c r="C5" t="str">
-        <v>安徽·黄山</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D5" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E5" t="str">
-        <v>黄山&amp;宏村</v>
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2025-08-30</v>
+        <v>2026-02-17</v>
       </c>
       <c r="B6" t="str">
-        <v>2025-08-31</v>
+        <v>2026-02-25</v>
       </c>
       <c r="C6" t="str">
-        <v>泰国·曼谷</v>
+        <v>云南·昆明大理丽江</v>
       </c>
       <c r="D6" t="str">
-        <v>观演</v>
+        <v>其他</v>
       </c>
       <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2025-07-19</v>
+        <v>2025-09-05</v>
       </c>
       <c r="B7" t="str">
-        <v>2025-07-20</v>
+        <v>2025-09-07</v>
       </c>
       <c r="C7" t="str">
-        <v>泰国·曼谷</v>
+        <v>安徽·黄山</v>
       </c>
       <c r="D7" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E7" t="str">
+        <v>黄山&amp;宏村</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2025-06-28</v>
+        <v>2025-08-30</v>
       </c>
       <c r="B8" t="str">
-        <v>2025-06-29</v>
+        <v>2025-08-31</v>
       </c>
       <c r="C8" t="str">
         <v>泰国·曼谷</v>
@@ -541,13 +586,19 @@
       <c r="E8" t="str">
         <v/>
       </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2025-05-17</v>
+        <v>2025-07-19</v>
       </c>
       <c r="B9" t="str">
-        <v>2025-05-18</v>
+        <v>2025-07-20</v>
       </c>
       <c r="C9" t="str">
         <v>泰国·曼谷</v>
@@ -558,16 +609,22 @@
       <c r="E9" t="str">
         <v/>
       </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2025-03-22</v>
+        <v>2025-06-28</v>
       </c>
       <c r="B10" t="str">
-        <v>2025-03-22</v>
+        <v>2025-06-29</v>
       </c>
       <c r="C10" t="str">
-        <v>苏州🦁GFY演唱会</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D10" t="str">
         <v>观演</v>
@@ -575,16 +632,22 @@
       <c r="E10" t="str">
         <v/>
       </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2025-01-11</v>
+        <v>2025-05-17</v>
       </c>
       <c r="B11" t="str">
-        <v>2025-01-12</v>
+        <v>2025-05-18</v>
       </c>
       <c r="C11" t="str">
-        <v>广东·香港·LingOrm FM</v>
+        <v>泰国·曼谷</v>
       </c>
       <c r="D11" t="str">
         <v>观演</v>
@@ -592,50 +655,68 @@
       <c r="E11" t="str">
         <v/>
       </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2024-11-15</v>
+        <v>2025-03-22</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-09-21</v>
+        <v>2025-03-22</v>
       </c>
       <c r="C12" t="str">
-        <v>松江区启民苑19栋1402</v>
+        <v>苏州🦁GFY演唱会</v>
       </c>
       <c r="D12" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2024-09-17</v>
+        <v>2025-01-11</v>
       </c>
       <c r="B13" t="str">
-        <v>2024-09-22</v>
+        <v>2025-01-12</v>
       </c>
       <c r="C13" t="str">
-        <v>北海涠洲岛·九寨沟·重庆</v>
+        <v>广东·香港·LingOrm FM</v>
       </c>
       <c r="D13" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2024-05-01</v>
+        <v>2024-11-15</v>
       </c>
       <c r="B14" t="str">
-        <v>2024-05-01</v>
+        <v>2026-10-30</v>
       </c>
       <c r="C14" t="str">
-        <v>芜湖</v>
+        <v>松江区启民苑19栋1402</v>
       </c>
       <c r="D14" t="str">
         <v>居住</v>
@@ -643,50 +724,68 @@
       <c r="E14" t="str">
         <v/>
       </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2024-02-17</v>
+        <v>2024-09-17</v>
       </c>
       <c r="B15" t="str">
-        <v>2024-03-03</v>
+        <v>2024-09-22</v>
       </c>
       <c r="C15" t="str">
-        <v>浙百春巡 杭州/扬州/南京/无锡</v>
+        <v>北海涠洲岛·九寨沟·重庆</v>
       </c>
       <c r="D15" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2023-12-31</v>
+        <v>2024-05-01</v>
       </c>
       <c r="B16" t="str">
-        <v>2023-12-31</v>
+        <v>2024-05-01</v>
       </c>
       <c r="C16" t="str">
-        <v>杭州·蝴蝶剧场</v>
+        <v>芜湖</v>
       </c>
       <c r="D16" t="str">
-        <v>观演</v>
+        <v>居住</v>
       </c>
       <c r="E16" t="str">
-        <v>君霄</v>
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2023-12-16</v>
+        <v>2024-02-17</v>
       </c>
       <c r="B17" t="str">
-        <v>2023-12-17</v>
+        <v>2024-03-03</v>
       </c>
       <c r="C17" t="str">
-        <v>杭州🍊☁️</v>
+        <v>浙百春巡 杭州/扬州/南京/无锡</v>
       </c>
       <c r="D17" t="str">
         <v>观演</v>
@@ -694,33 +793,45 @@
       <c r="E17" t="str">
         <v/>
       </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2023-12-02</v>
+        <v>2023-12-31</v>
       </c>
       <c r="B18" t="str">
-        <v>2023-12-03</v>
+        <v>2023-12-31</v>
       </c>
       <c r="C18" t="str">
-        <v>杭州/苏州 君霄/ZSH演唱会</v>
+        <v>杭州·蝴蝶剧场</v>
       </c>
       <c r="D18" t="str">
         <v>观演</v>
       </c>
       <c r="E18" t="str">
+        <v>君霄</v>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2023-11-25</v>
+        <v>2023-12-16</v>
       </c>
       <c r="B19" t="str">
-        <v>2023-11-16</v>
+        <v>2023-12-17</v>
       </c>
       <c r="C19" t="str">
-        <v>武汉·小狮子音乐会🦁</v>
+        <v>杭州🍊☁️</v>
       </c>
       <c r="D19" t="str">
         <v>观演</v>
@@ -728,16 +839,22 @@
       <c r="E19" t="str">
         <v/>
       </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2023-11-17</v>
+        <v>2023-12-02</v>
       </c>
       <c r="B20" t="str">
-        <v>2023-11-19</v>
+        <v>2023-12-03</v>
       </c>
       <c r="C20" t="str">
-        <v>🐻·上海</v>
+        <v>杭州/苏州 君霄/ZSH演唱会</v>
       </c>
       <c r="D20" t="str">
         <v>观演</v>
@@ -745,33 +862,45 @@
       <c r="E20" t="str">
         <v/>
       </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2023-09-27</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B21" t="str">
-        <v>2023-10-05</v>
+        <v>2023-11-25</v>
       </c>
       <c r="C21" t="str">
-        <v>温州百丈漈·常州·海宁·杭州周游记</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D21" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2023-09-23</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B22" t="str">
-        <v>2023-09-23</v>
+        <v>2023-11-25</v>
       </c>
       <c r="C22" t="str">
-        <v>南京·小狮子音乐会🦁</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D22" t="str">
         <v>观演</v>
@@ -779,16 +908,22 @@
       <c r="E22" t="str">
         <v/>
       </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2023-09-16</v>
+        <v>2023-11-25</v>
       </c>
       <c r="B23" t="str">
-        <v>2023-09-16</v>
+        <v>2023-11-25</v>
       </c>
       <c r="C23" t="str">
-        <v>合肥·蔡依林演唱会</v>
+        <v>武汉·小狮子音乐会🦁</v>
       </c>
       <c r="D23" t="str">
         <v>观演</v>
@@ -796,16 +931,22 @@
       <c r="E23" t="str">
         <v/>
       </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2023-09-09</v>
+        <v>2023-11-17</v>
       </c>
       <c r="B24" t="str">
-        <v>2023-09-09</v>
+        <v>2023-11-19</v>
       </c>
       <c r="C24" t="str">
-        <v>苏州·杨丞琳演唱会</v>
+        <v>🐻·上海</v>
       </c>
       <c r="D24" t="str">
         <v>观演</v>
@@ -813,33 +954,45 @@
       <c r="E24" t="str">
         <v/>
       </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2023-08-19</v>
+        <v>2023-09-27</v>
       </c>
       <c r="B25" t="str">
-        <v>2023-08-20</v>
+        <v>2023-10-05</v>
       </c>
       <c r="C25" t="str">
-        <v>常州·S</v>
+        <v>温州百丈漈·常州·海宁·杭州周游记</v>
       </c>
       <c r="D25" t="str">
         <v>旅行</v>
       </c>
       <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2023-07-22</v>
+        <v>2023-09-23</v>
       </c>
       <c r="B26" t="str">
-        <v>2023-07-23</v>
+        <v>2023-09-23</v>
       </c>
       <c r="C26" t="str">
-        <v>青岛·小狮子音乐会🦁</v>
+        <v>南京·小狮子音乐会🦁</v>
       </c>
       <c r="D26" t="str">
         <v>观演</v>
@@ -847,16 +1000,22 @@
       <c r="E26" t="str">
         <v/>
       </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2023-05-20</v>
+        <v>2023-09-16</v>
       </c>
       <c r="B27" t="str">
-        <v>2023-05-21</v>
+        <v>2023-09-16</v>
       </c>
       <c r="C27" t="str">
-        <v>合肥·小狮子音乐会🦁</v>
+        <v>合肥·蔡依林演唱会</v>
       </c>
       <c r="D27" t="str">
         <v>观演</v>
@@ -864,50 +1023,68 @@
       <c r="E27" t="str">
         <v/>
       </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2023-04-14</v>
+        <v>2023-09-09</v>
       </c>
       <c r="B28" t="str">
-        <v>2023-04-16</v>
+        <v>2023-09-09</v>
       </c>
       <c r="C28" t="str">
-        <v>舟山·朱家尖 同事</v>
+        <v>苏州·杨丞琳演唱会</v>
       </c>
       <c r="D28" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2023-01-26</v>
+        <v>2023-08-19</v>
       </c>
       <c r="B29" t="str">
-        <v>2023-01-29</v>
+        <v>2023-08-20</v>
       </c>
       <c r="C29" t="str">
-        <v>福建·平潭岛 萌</v>
+        <v>常州·S</v>
       </c>
       <c r="D29" t="str">
         <v>旅行</v>
       </c>
       <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2022-12-31</v>
+        <v>2023-07-22</v>
       </c>
       <c r="B30" t="str">
-        <v>2023-01-02</v>
+        <v>2023-07-23</v>
       </c>
       <c r="C30" t="str">
-        <v>南昌·小狮子音乐会🦁</v>
+        <v>青岛·小狮子音乐会🦁</v>
       </c>
       <c r="D30" t="str">
         <v>观演</v>
@@ -915,492 +1092,666 @@
       <c r="E30" t="str">
         <v/>
       </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2022-10-16</v>
+        <v>2023-05-20</v>
       </c>
       <c r="B31" t="str">
-        <v>2024-11-15</v>
+        <v>2023-05-21</v>
       </c>
       <c r="C31" t="str">
-        <v>松江区启民苑20栋201</v>
+        <v>合肥·小狮子音乐会🦁</v>
       </c>
       <c r="D31" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2021-10-31</v>
+        <v>2023-04-14</v>
       </c>
       <c r="B32" t="str">
-        <v>2022-10-31</v>
+        <v>2023-04-16</v>
       </c>
       <c r="C32" t="str">
-        <v>松江区启民苑15号楼102</v>
+        <v>舟山·朱家尖 同事</v>
       </c>
       <c r="D32" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2021-10-05</v>
+        <v>2023-01-26</v>
       </c>
       <c r="B33" t="str">
-        <v>1007-01-01</v>
+        <v>2023-01-29</v>
       </c>
       <c r="C33" t="str">
-        <v>舟山·嵊泗岛 🧑🏻</v>
+        <v>福建·平潭岛 萌</v>
       </c>
       <c r="D33" t="str">
         <v>旅行</v>
       </c>
       <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2021-09-17</v>
+        <v>2022-12-31</v>
       </c>
       <c r="B34" t="str">
-        <v>2021-09-17</v>
+        <v>2023-01-02</v>
       </c>
       <c r="C34" t="str">
-        <v>舟山·海宁(杭州)·萌·鑫</v>
+        <v>南昌·小狮子音乐会🦁</v>
       </c>
       <c r="D34" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2021-06-10</v>
+        <v>2022-10-16</v>
       </c>
       <c r="B35" t="str">
-        <v>2021-06-10</v>
+        <v>2024-11-15</v>
       </c>
       <c r="C35" t="str">
-        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
+        <v>松江区启民苑20栋201</v>
       </c>
       <c r="D35" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2021-05-01</v>
+        <v>2021-10-31</v>
       </c>
       <c r="B36" t="str">
-        <v>2021-05-01</v>
+        <v>2022-10-31</v>
       </c>
       <c r="C36" t="str">
-        <v>舟山·嵊泗岛 发小</v>
+        <v>松江区启民苑15号楼102</v>
       </c>
       <c r="D36" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2020-11-02</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B37" t="str">
-        <v>2020-11-02</v>
+        <v>2021-10-05</v>
       </c>
       <c r="C37" t="str">
-        <v>入职上海齐獭</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D37" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2020-08-09</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B38" t="str">
-        <v>2021-11-01</v>
+        <v>2021-10-05</v>
       </c>
       <c r="C38" t="str">
-        <v>宝山区和家欣苑B区40-201</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D38" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2020-07-31</v>
+        <v>2021-10-05</v>
       </c>
       <c r="B39" t="str">
-        <v>2020-07-31</v>
+        <v>2021-10-05</v>
       </c>
       <c r="C39" t="str">
-        <v>到达上海</v>
+        <v>舟山·嵊泗岛 🧑🏻</v>
       </c>
       <c r="D39" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2020-07-17</v>
+        <v>2021-09-17</v>
       </c>
       <c r="B40" t="str">
-        <v>2020-07-31</v>
+        <v>2021-09-17</v>
       </c>
       <c r="C40" t="str">
-        <v>安徽 芜湖×宣城×马鞍山</v>
+        <v>舟山·海宁(杭州)·萌·鑫</v>
       </c>
       <c r="D40" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2020-06-06</v>
+        <v>2021-06-10</v>
       </c>
       <c r="B41" t="str">
-        <v>2020-07-17</v>
+        <v>2021-06-10</v>
       </c>
       <c r="C41" t="str">
-        <v>❤️·厦门</v>
+        <v>宁波·舟山·普陀山 傻蛋 2K-</v>
       </c>
       <c r="D41" t="str">
         <v>旅行</v>
       </c>
       <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2020-05-30</v>
+        <v>2021-05-01</v>
       </c>
       <c r="B42" t="str">
-        <v>2020-05-31</v>
+        <v>2021-05-01</v>
       </c>
       <c r="C42" t="str">
-        <v>秦皇岛</v>
+        <v>舟山·嵊泗岛 发小</v>
       </c>
       <c r="D42" t="str">
         <v>旅行</v>
       </c>
       <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2020-05-29</v>
+        <v>2020-11-02</v>
       </c>
       <c r="B43" t="str">
-        <v>2020-11-01</v>
+        <v>2020-11-02</v>
       </c>
       <c r="C43" t="str">
-        <v>待业155天</v>
+        <v>入职上海齐獭</v>
       </c>
       <c r="D43" t="str">
-        <v>其他</v>
+        <v>工作</v>
       </c>
       <c r="E43" t="str">
-        <v>155天</v>
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>★</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2020-05-29</v>
+        <v>2020-08-09</v>
       </c>
       <c r="B44" t="str">
-        <v>2020-05-29</v>
+        <v>2021-11-01</v>
       </c>
       <c r="C44" t="str">
-        <v>离职中科达奥</v>
+        <v>宝山区和家欣苑B区40-201</v>
       </c>
       <c r="D44" t="str">
-        <v>工作</v>
+        <v>居住</v>
       </c>
       <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2020-04-30</v>
+        <v>2020-07-31</v>
       </c>
       <c r="B45" t="str">
-        <v>2020-05-05</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C45" t="str">
-        <v>❤·厦门</v>
+        <v>到达上海</v>
       </c>
       <c r="D45" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E45" t="str">
+        <v/>
+      </c>
+      <c r="F45" t="str">
+        <v/>
+      </c>
+      <c r="G45" t="str">
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2020-01-27</v>
+        <v>2020-07-17</v>
       </c>
       <c r="B46" t="str">
-        <v>2020-02-04</v>
+        <v>2020-07-31</v>
       </c>
       <c r="C46" t="str">
-        <v>❤·南京</v>
+        <v>安徽 芜湖×宣城×马鞍山</v>
       </c>
       <c r="D46" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E46" t="str">
+        <v/>
+      </c>
+      <c r="F46" t="str">
+        <v/>
+      </c>
+      <c r="G46" t="str">
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2019-12-31</v>
+        <v>2020-06-06</v>
       </c>
       <c r="B47" t="str">
-        <v>2020-01-05</v>
+        <v>2020-07-17</v>
       </c>
       <c r="C47" t="str">
-        <v>❤·LangX 南京</v>
+        <v>❤️·厦门</v>
       </c>
       <c r="D47" t="str">
         <v>旅行</v>
       </c>
       <c r="E47" t="str">
+        <v/>
+      </c>
+      <c r="F47" t="str">
+        <v/>
+      </c>
+      <c r="G47" t="str">
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2019-11-29</v>
+        <v>2020-05-30</v>
       </c>
       <c r="B48" t="str">
-        <v>2019-12-10</v>
+        <v>2020-05-31</v>
       </c>
       <c r="C48" t="str">
-        <v>❤·北京</v>
+        <v>秦皇岛</v>
       </c>
       <c r="D48" t="str">
         <v>旅行</v>
       </c>
       <c r="E48" t="str">
+        <v/>
+      </c>
+      <c r="F48" t="str">
+        <v/>
+      </c>
+      <c r="G48" t="str">
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2019-09-26</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B49" t="str">
-        <v>2019-11-14</v>
+        <v>2020-11-01</v>
       </c>
       <c r="C49" t="str">
-        <v>❤·北京</v>
+        <v>待业155天</v>
       </c>
       <c r="D49" t="str">
-        <v>旅行</v>
+        <v>其他</v>
       </c>
       <c r="E49" t="str">
+        <v>155天</v>
+      </c>
+      <c r="F49" t="str">
+        <v/>
+      </c>
+      <c r="G49" t="str">
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2019-09-13</v>
+        <v>2020-05-29</v>
       </c>
       <c r="B50" t="str">
-        <v>2019-09-15</v>
+        <v>2020-05-29</v>
       </c>
       <c r="C50" t="str">
-        <v>❤·秦皇岛</v>
+        <v>离职中科达奥</v>
       </c>
       <c r="D50" t="str">
-        <v>旅行</v>
+        <v>工作</v>
       </c>
       <c r="E50" t="str">
         <v/>
+      </c>
+      <c r="F50" t="str">
+        <v/>
+      </c>
+      <c r="G50" t="str">
+        <v>★</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2019-08-22</v>
+        <v>2020-04-30</v>
       </c>
       <c r="B51" t="str">
-        <v>2019-09-17</v>
+        <v>2020-05-05</v>
       </c>
       <c r="C51" t="str">
-        <v>❤·北京</v>
+        <v>❤·厦门</v>
       </c>
       <c r="D51" t="str">
         <v>旅行</v>
       </c>
       <c r="E51" t="str">
+        <v/>
+      </c>
+      <c r="F51" t="str">
+        <v/>
+      </c>
+      <c r="G51" t="str">
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2019-08-09</v>
+        <v>2020-01-27</v>
       </c>
       <c r="B52" t="str">
-        <v>2019-08-11</v>
+        <v>2020-02-04</v>
       </c>
       <c r="C52" t="str">
-        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
+        <v>❤·南京</v>
       </c>
       <c r="D52" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E52" t="str">
+        <v/>
+      </c>
+      <c r="F52" t="str">
+        <v/>
+      </c>
+      <c r="G52" t="str">
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2019-07-26</v>
+        <v>2019-12-31</v>
       </c>
       <c r="B53" t="str">
-        <v>2019-07-28</v>
+        <v>2020-01-05</v>
       </c>
       <c r="C53" t="str">
-        <v>❤·北京 云冈酒店2</v>
+        <v>❤·LangX 南京</v>
       </c>
       <c r="D53" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E53" t="str">
+        <v/>
+      </c>
+      <c r="F53" t="str">
+        <v/>
+      </c>
+      <c r="G53" t="str">
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2019-07-13</v>
+        <v>2019-11-29</v>
       </c>
       <c r="B54" t="str">
-        <v>2019-07-14</v>
+        <v>2019-12-10</v>
       </c>
       <c r="C54" t="str">
-        <v>❤·上海 七宝速八2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D54" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E54" t="str">
+        <v/>
+      </c>
+      <c r="F54" t="str">
+        <v/>
+      </c>
+      <c r="G54" t="str">
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2019-06-29</v>
+        <v>2019-09-26</v>
       </c>
       <c r="B55" t="str">
-        <v>2019-06-30</v>
+        <v>2019-11-14</v>
       </c>
       <c r="C55" t="str">
-        <v>❤·上海 弗思特_四川北路2</v>
+        <v>❤·北京</v>
       </c>
       <c r="D55" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E55" t="str">
+        <v/>
+      </c>
+      <c r="F55" t="str">
+        <v/>
+      </c>
+      <c r="G55" t="str">
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2019-06-20</v>
+        <v>2019-09-13</v>
       </c>
       <c r="B56" t="str">
-        <v>2019-06-25</v>
+        <v>2019-09-15</v>
       </c>
       <c r="C56" t="str">
-        <v>❤·北京 家 西单速八1</v>
+        <v>❤·秦皇岛</v>
       </c>
       <c r="D56" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E56" t="str">
+        <v/>
+      </c>
+      <c r="F56" t="str">
+        <v/>
+      </c>
+      <c r="G56" t="str">
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2019-06-07</v>
+        <v>2019-08-22</v>
       </c>
       <c r="B57" t="str">
-        <v>2019-06-09</v>
+        <v>2019-09-17</v>
       </c>
       <c r="C57" t="str">
-        <v>❤·上海·迪士尼￥≈3K</v>
+        <v>❤·北京</v>
       </c>
       <c r="D57" t="str">
         <v>旅行</v>
       </c>
       <c r="E57" t="str">
+        <v/>
+      </c>
+      <c r="F57" t="str">
+        <v/>
+      </c>
+      <c r="G57" t="str">
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2019-05-01</v>
+        <v>2019-08-09</v>
       </c>
       <c r="B58" t="str">
-        <v>2019-05-01</v>
+        <v>2019-08-11</v>
       </c>
       <c r="C58" t="str">
-        <v>❤·天津·👩‍❤️‍💋‍👩</v>
+        <v>❤·上海 宿适轻奢漕宝路3➠食￥937.42 住￥717 车票￥1022</v>
       </c>
       <c r="D58" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v/>
+      </c>
+      <c r="G58" t="str">
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2019-05-01</v>
+        <v>2019-07-26</v>
       </c>
       <c r="B59" t="str">
-        <v>2019-05-04</v>
+        <v>2019-07-28</v>
       </c>
       <c r="C59" t="str">
-        <v>❤·北京 华严北里_速八1</v>
+        <v>❤·北京 云冈酒店2</v>
       </c>
       <c r="D59" t="str">
         <v>居住</v>
@@ -1408,302 +1759,410 @@
       <c r="E59" t="str">
         <v/>
       </c>
+      <c r="F59" t="str">
+        <v/>
+      </c>
+      <c r="G59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2019-04-04</v>
+        <v>2019-07-13</v>
       </c>
       <c r="B60" t="str">
-        <v>2019-04-07</v>
+        <v>2019-07-14</v>
       </c>
       <c r="C60" t="str">
-        <v>❤·福建·厦门 💋</v>
+        <v>❤·上海 七宝速八2</v>
       </c>
       <c r="D60" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v/>
+      </c>
+      <c r="G60" t="str">
         <v/>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2019-02-10</v>
+        <v>2019-06-29</v>
       </c>
       <c r="B61" t="str">
-        <v>2019-02-17</v>
+        <v>2019-06-30</v>
       </c>
       <c r="C61" t="str">
-        <v>深圳 萌</v>
+        <v>❤·上海 弗思特_四川北路2</v>
       </c>
       <c r="D61" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v/>
+      </c>
+      <c r="G61" t="str">
         <v/>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2018-10-05</v>
+        <v>2019-06-20</v>
       </c>
       <c r="B62" t="str">
-        <v>2018-10-07</v>
+        <v>2019-06-25</v>
       </c>
       <c r="C62" t="str">
-        <v>广州·萌</v>
+        <v>❤·北京 家 西单速八1</v>
       </c>
       <c r="D62" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v/>
+      </c>
+      <c r="G62" t="str">
         <v/>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2018-10-01</v>
+        <v>2019-06-07</v>
       </c>
       <c r="B63" t="str">
-        <v>2018-10-04</v>
+        <v>2019-06-09</v>
       </c>
       <c r="C63" t="str">
-        <v>广西·北海·涠洲岛</v>
+        <v>❤·上海·迪士尼￥≈3K</v>
       </c>
       <c r="D63" t="str">
         <v>旅行</v>
       </c>
       <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v/>
+      </c>
+      <c r="G63" t="str">
         <v/>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2018-06-01</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B64" t="str">
-        <v>2018-06-03</v>
+        <v>2019-05-01</v>
       </c>
       <c r="C64" t="str">
-        <v>河北 秦皇河</v>
+        <v>❤·天津·👩‍❤️‍💋‍👩</v>
       </c>
       <c r="D64" t="str">
         <v>旅行</v>
       </c>
       <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v/>
+      </c>
+      <c r="G64" t="str">
         <v/>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2018-02-18</v>
+        <v>2019-05-01</v>
       </c>
       <c r="B65" t="str">
-        <v>2018-02-25</v>
+        <v>2019-05-04</v>
       </c>
       <c r="C65" t="str">
-        <v>广州 深圳</v>
+        <v>❤·北京 华严北里_速八1</v>
       </c>
       <c r="D65" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v/>
+      </c>
+      <c r="G65" t="str">
         <v/>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2018-02-02</v>
+        <v>2019-04-04</v>
       </c>
       <c r="B66" t="str">
-        <v>2018-02-03</v>
+        <v>2019-04-07</v>
       </c>
       <c r="C66" t="str">
-        <v>合肥 雅慧妹婚礼</v>
+        <v>❤·福建·厦门 💋</v>
       </c>
       <c r="D66" t="str">
-        <v>家庭</v>
+        <v>旅行</v>
       </c>
       <c r="E66" t="str">
+        <v/>
+      </c>
+      <c r="F66" t="str">
+        <v/>
+      </c>
+      <c r="G66" t="str">
         <v/>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2017-12-23</v>
+        <v>2019-02-10</v>
       </c>
       <c r="B67" t="str">
-        <v>2017-22-24</v>
+        <v>2019-02-17</v>
       </c>
       <c r="C67" t="str">
-        <v>上海·路演</v>
+        <v>深圳 萌</v>
       </c>
       <c r="D67" t="str">
-        <v>观演</v>
+        <v>旅行</v>
       </c>
       <c r="E67" t="str">
+        <v/>
+      </c>
+      <c r="F67" t="str">
+        <v/>
+      </c>
+      <c r="G67" t="str">
         <v/>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2017-11-11</v>
+        <v>2018-10-05</v>
       </c>
       <c r="B68" t="str">
-        <v>2017-11-16</v>
+        <v>2018-10-07</v>
       </c>
       <c r="C68" t="str">
-        <v>小熊 北京</v>
+        <v>广州·萌</v>
       </c>
       <c r="D68" t="str">
         <v>旅行</v>
       </c>
       <c r="E68" t="str">
-        <v>Z97</v>
+        <v/>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2017-10-10</v>
+        <v>2018-10-01</v>
       </c>
       <c r="B69" t="str">
-        <v>2017-10-17</v>
+        <v>2018-10-04</v>
       </c>
       <c r="C69" t="str">
-        <v>萌 北京</v>
+        <v>广西·北海·涠洲岛</v>
       </c>
       <c r="D69" t="str">
         <v>旅行</v>
       </c>
       <c r="E69" t="str">
-        <v>11:47</v>
+        <v/>
+      </c>
+      <c r="F69" t="str">
+        <v/>
+      </c>
+      <c r="G69" t="str">
+        <v/>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2017-09-29</v>
+        <v>2018-06-01</v>
       </c>
       <c r="B70" t="str">
-        <v>2017-10-09</v>
+        <v>2018-06-03</v>
       </c>
       <c r="C70" t="str">
-        <v>西藏·珠穆朗玛</v>
+        <v>河北 秦皇河</v>
       </c>
       <c r="D70" t="str">
         <v>旅行</v>
       </c>
       <c r="E70" t="str">
+        <v/>
+      </c>
+      <c r="F70" t="str">
+        <v/>
+      </c>
+      <c r="G70" t="str">
         <v/>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2017-09-27</v>
+        <v>2018-02-18</v>
       </c>
       <c r="B71" t="str">
-        <v>2017-09-29</v>
+        <v>2018-02-25</v>
       </c>
       <c r="C71" t="str">
-        <v>萌 北京</v>
+        <v>广州 深圳</v>
       </c>
       <c r="D71" t="str">
         <v>旅行</v>
       </c>
       <c r="E71" t="str">
+        <v/>
+      </c>
+      <c r="F71" t="str">
+        <v/>
+      </c>
+      <c r="G71" t="str">
         <v/>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2017-09-09</v>
+        <v>2018-02-02</v>
       </c>
       <c r="B72" t="str">
-        <v>2017-09-10</v>
+        <v>2018-02-03</v>
       </c>
       <c r="C72" t="str">
-        <v>武汉·游</v>
+        <v>合肥 雅慧妹婚礼</v>
       </c>
       <c r="D72" t="str">
-        <v>旅行</v>
+        <v>家庭</v>
       </c>
       <c r="E72" t="str">
         <v/>
+      </c>
+      <c r="F72" t="str">
+        <v/>
+      </c>
+      <c r="G72" t="str">
+        <v>★</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2017-08-18</v>
+        <v>2017-12-23</v>
       </c>
       <c r="B73" t="str">
-        <v>2017-08-20</v>
+        <v>2017-22-01</v>
       </c>
       <c r="C73" t="str">
-        <v>萌 北京</v>
+        <v>上海·路演</v>
       </c>
       <c r="D73" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E73" t="str">
+        <v/>
+      </c>
+      <c r="F73" t="str">
+        <v/>
+      </c>
+      <c r="G73" t="str">
         <v/>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2017-08-11</v>
+        <v>2017-11-11</v>
       </c>
       <c r="B74" t="str">
-        <v>2017-08-13</v>
+        <v>2017-11-16</v>
       </c>
       <c r="C74" t="str">
-        <v>武汉</v>
+        <v>小熊 北京</v>
       </c>
       <c r="D74" t="str">
         <v>旅行</v>
       </c>
       <c r="E74" t="str">
-        <v>大聚会</v>
+        <v>Z97</v>
+      </c>
+      <c r="F74" t="str">
+        <v/>
+      </c>
+      <c r="G74" t="str">
+        <v/>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2017-08-04</v>
+        <v>2017-10-10</v>
       </c>
       <c r="B75" t="str">
-        <v>2017-08-07</v>
+        <v>2017-10-17</v>
       </c>
       <c r="C75" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D75" t="str">
         <v>旅行</v>
       </c>
       <c r="E75" t="str">
+        <v>11:47</v>
+      </c>
+      <c r="F75" t="str">
+        <v/>
+      </c>
+      <c r="G75" t="str">
         <v/>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2017-06-15</v>
+        <v>2017-09-29</v>
       </c>
       <c r="B76" t="str">
-        <v>2020-06-15</v>
+        <v>2017-10-09</v>
       </c>
       <c r="C76" t="str">
-        <v>北京华严北里小区59-6-501</v>
+        <v>西藏·珠穆朗玛</v>
       </c>
       <c r="D76" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E76" t="str">
+        <v/>
+      </c>
+      <c r="F76" t="str">
+        <v/>
+      </c>
+      <c r="G76" t="str">
         <v/>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2017-06-10</v>
+        <v>2017-09-27</v>
       </c>
       <c r="B77" t="str">
-        <v>2017-06-11</v>
+        <v>2017-09-29</v>
       </c>
       <c r="C77" t="str">
         <v>萌 北京</v>
@@ -1714,47 +2173,65 @@
       <c r="E77" t="str">
         <v/>
       </c>
+      <c r="F77" t="str">
+        <v/>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2017-05-28</v>
+        <v>2017-09-09</v>
       </c>
       <c r="B78" t="str">
-        <v>2017-05-30</v>
+        <v>2017-09-10</v>
       </c>
       <c r="C78" t="str">
-        <v>武汉</v>
+        <v>武汉·游</v>
       </c>
       <c r="D78" t="str">
         <v>旅行</v>
       </c>
       <c r="E78" t="str">
+        <v/>
+      </c>
+      <c r="F78" t="str">
+        <v/>
+      </c>
+      <c r="G78" t="str">
         <v/>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2017-04-29</v>
+        <v>2017-08-18</v>
       </c>
       <c r="B79" t="str">
-        <v>2017-05-01</v>
+        <v>2017-08-20</v>
       </c>
       <c r="C79" t="str">
-        <v>大连 s</v>
+        <v>萌 北京</v>
       </c>
       <c r="D79" t="str">
         <v>旅行</v>
       </c>
       <c r="E79" t="str">
+        <v/>
+      </c>
+      <c r="F79" t="str">
+        <v/>
+      </c>
+      <c r="G79" t="str">
         <v/>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2017-04-21</v>
+        <v>2017-08-11</v>
       </c>
       <c r="B80" t="str">
-        <v>2017-04-23</v>
+        <v>2017-08-13</v>
       </c>
       <c r="C80" t="str">
         <v>武汉</v>
@@ -1763,564 +2240,762 @@
         <v>旅行</v>
       </c>
       <c r="E80" t="str">
+        <v>大聚会</v>
+      </c>
+      <c r="F80" t="str">
+        <v/>
+      </c>
+      <c r="G80" t="str">
         <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2017-03-13</v>
+        <v>2017-08-04</v>
       </c>
       <c r="B81" t="str">
-        <v>2017-03-13</v>
+        <v>2017-08-07</v>
       </c>
       <c r="C81" t="str">
-        <v>入职ZKDA</v>
+        <v>武汉</v>
       </c>
       <c r="D81" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E81" t="str">
+        <v/>
+      </c>
+      <c r="F81" t="str">
+        <v/>
+      </c>
+      <c r="G81" t="str">
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2016-12-23</v>
+        <v>2017-06-15</v>
       </c>
       <c r="B82" t="str">
-        <v>2017-01-08</v>
+        <v>2020-06-15</v>
       </c>
       <c r="C82" t="str">
-        <v>武汉·徐东</v>
+        <v>北京华严北里小区59-6-501</v>
       </c>
       <c r="D82" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E82" t="str">
+        <v/>
+      </c>
+      <c r="F82" t="str">
+        <v/>
+      </c>
+      <c r="G82" t="str">
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2016-10-07</v>
+        <v>2017-06-10</v>
       </c>
       <c r="B83" t="str">
-        <v>2016-10-14</v>
+        <v>2017-06-11</v>
       </c>
       <c r="C83" t="str">
-        <v>武汉</v>
+        <v>萌 北京</v>
       </c>
       <c r="D83" t="str">
         <v>旅行</v>
       </c>
       <c r="E83" t="str">
+        <v/>
+      </c>
+      <c r="F83" t="str">
+        <v/>
+      </c>
+      <c r="G83" t="str">
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2016-10-01</v>
+        <v>2017-05-28</v>
       </c>
       <c r="B84" t="str">
-        <v>2016-10-07</v>
+        <v>2017-05-30</v>
       </c>
       <c r="C84" t="str">
-        <v>兰州 陇南 天水</v>
+        <v>武汉</v>
       </c>
       <c r="D84" t="str">
         <v>旅行</v>
       </c>
       <c r="E84" t="str">
+        <v/>
+      </c>
+      <c r="F84" t="str">
+        <v/>
+      </c>
+      <c r="G84" t="str">
         <v/>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
+        <v>2017-04-29</v>
+      </c>
+      <c r="B85" t="str">
+        <v>2017-05-01</v>
+      </c>
+      <c r="C85" t="str">
+        <v>大连 s</v>
+      </c>
+      <c r="D85" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E85" t="str">
+        <v/>
+      </c>
+      <c r="F85" t="str">
+        <v/>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>2017-04-21</v>
+      </c>
+      <c r="B86" t="str">
+        <v>2017-04-23</v>
+      </c>
+      <c r="C86" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D86" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E86" t="str">
+        <v/>
+      </c>
+      <c r="F86" t="str">
+        <v/>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="B87" t="str">
+        <v>2017-03-13</v>
+      </c>
+      <c r="C87" t="str">
+        <v>入职ZKDA</v>
+      </c>
+      <c r="D87" t="str">
+        <v>工作</v>
+      </c>
+      <c r="E87" t="str">
+        <v/>
+      </c>
+      <c r="F87" t="str">
+        <v/>
+      </c>
+      <c r="G87" t="str">
+        <v>★</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>2016-12-23</v>
+      </c>
+      <c r="B88" t="str">
+        <v>2017-01-08</v>
+      </c>
+      <c r="C88" t="str">
+        <v>武汉·徐东</v>
+      </c>
+      <c r="D88" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E88" t="str">
+        <v/>
+      </c>
+      <c r="F88" t="str">
+        <v/>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="B89" t="str">
+        <v>2016-10-14</v>
+      </c>
+      <c r="C89" t="str">
+        <v>武汉</v>
+      </c>
+      <c r="D89" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E89" t="str">
+        <v/>
+      </c>
+      <c r="F89" t="str">
+        <v/>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>2016-10-01</v>
+      </c>
+      <c r="B90" t="str">
+        <v>2016-10-07</v>
+      </c>
+      <c r="C90" t="str">
+        <v>兰州 陇南 天水</v>
+      </c>
+      <c r="D90" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E90" t="str">
+        <v/>
+      </c>
+      <c r="F90" t="str">
+        <v/>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
         <v>2016-07-16</v>
       </c>
-      <c r="B85" t="str">
+      <c r="B91" t="str">
         <v>2017-07-16</v>
       </c>
-      <c r="C85" t="str">
+      <c r="C91" t="str">
         <v>北京清河清缘东里8-B102</v>
       </c>
-      <c r="D85" t="str">
+      <c r="D91" t="str">
         <v>居住</v>
       </c>
-      <c r="E85" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="86" xml:space="preserve">
-      <c r="A86" t="str">
+      <c r="E91" t="str">
+        <v/>
+      </c>
+      <c r="F91" t="str">
+        <v/>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92" xml:space="preserve">
+      <c r="A92" t="str">
         <v>2016-07-06</v>
       </c>
-      <c r="B86" t="str">
+      <c r="B92" t="str">
         <v>2016-07-13</v>
       </c>
-      <c r="C86" t="str">
+      <c r="C92" t="str">
         <v>武汉·游</v>
       </c>
-      <c r="D86" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E86" t="str" xml:space="preserve">
+      <c r="D92" t="str">
+        <v>旅行</v>
+      </c>
+      <c r="E92" t="str" xml:space="preserve">
         <v xml:space="preserve">┏ 20160706江南四季酒店/1晚
 ┣ 20160707 四季如家(徐东大街店)/1晚
 ┗ 20160708-0712 江南四季酒店302/5晚</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="str">
-        <v>2016-05-20</v>
-      </c>
-      <c r="B87" t="str">
-        <v>2016-05-23</v>
-      </c>
-      <c r="C87" t="str">
-        <v>武汉·夜孔雀路演</v>
-      </c>
-      <c r="D87" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E87" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="B88" t="str">
-        <v>2016-04-23</v>
-      </c>
-      <c r="C88" t="str">
-        <v>南京·刘若英演唱会</v>
-      </c>
-      <c r="D88" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E88" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="str">
-        <v>2016-04-03</v>
-      </c>
-      <c r="B89" t="str">
-        <v>2017-03-12</v>
-      </c>
-      <c r="C89" t="str">
-        <v>待业343天</v>
-      </c>
-      <c r="D89" t="str">
-        <v>其他</v>
-      </c>
-      <c r="E89" t="str">
-        <v>343天</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="str">
-        <v>2016-04-01</v>
-      </c>
-      <c r="B90" t="str">
-        <v>2016-04-04</v>
-      </c>
-      <c r="C90" t="str">
-        <v>河南·洛阳·夜孔雀路演</v>
-      </c>
-      <c r="D90" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E90" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="B91" t="str">
-        <v>2015-12-31</v>
-      </c>
-      <c r="C91" t="str">
-        <v>天津·刘若英跨年演唱会 昱</v>
-      </c>
-      <c r="D91" t="str">
-        <v>观演</v>
-      </c>
-      <c r="E91" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="str">
-        <v>2015-10-01</v>
-      </c>
-      <c r="B92" t="str">
-        <v>2015-10-07</v>
-      </c>
-      <c r="C92" t="str">
-        <v>大连 s</v>
-      </c>
-      <c r="D92" t="str">
-        <v>旅行</v>
-      </c>
-      <c r="E92" t="str">
+      <c r="F92" t="str">
+        <v/>
+      </c>
+      <c r="G92" t="str">
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2015-06-09</v>
+        <v>2016-05-20</v>
       </c>
       <c r="B93" t="str">
-        <v>2015-06-14</v>
+        <v>2016-05-23</v>
       </c>
       <c r="C93" t="str">
-        <v>大连 s</v>
+        <v>武汉·夜孔雀路演</v>
       </c>
       <c r="D93" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E93" t="str">
+        <v/>
+      </c>
+      <c r="F93" t="str">
+        <v/>
+      </c>
+      <c r="G93" t="str">
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2015-06-06</v>
+        <v>2016-04-23</v>
       </c>
       <c r="B94" t="str">
-        <v>2015-06-08</v>
+        <v>2016-04-23</v>
       </c>
       <c r="C94" t="str">
-        <v>湘西·凤凰古城</v>
+        <v>南京·刘若英演唱会</v>
       </c>
       <c r="D94" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E94" t="str">
+        <v/>
+      </c>
+      <c r="F94" t="str">
+        <v/>
+      </c>
+      <c r="G94" t="str">
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2015-05-18</v>
+        <v>2016-04-03</v>
       </c>
       <c r="B95" t="str">
-        <v>2016-07-16</v>
+        <v>2017-03-12</v>
       </c>
       <c r="C95" t="str">
-        <v>永泰东里16-6-601</v>
+        <v>待业343天</v>
       </c>
       <c r="D95" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E95" t="str">
-        <v>11500</v>
+        <v>343天</v>
+      </c>
+      <c r="F95" t="str">
+        <v/>
+      </c>
+      <c r="G95" t="str">
+        <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2015-05-01</v>
+        <v>2016-04-01</v>
       </c>
       <c r="B96" t="str">
-        <v>2015-05-03</v>
+        <v>2016-04-04</v>
       </c>
       <c r="C96" t="str">
-        <v>大连·游 s</v>
+        <v>河南·洛阳·夜孔雀路演</v>
       </c>
       <c r="D96" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E96" t="str">
+        <v/>
+      </c>
+      <c r="F96" t="str">
+        <v/>
+      </c>
+      <c r="G96" t="str">
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2015-03-28</v>
+        <v>2015-12-31</v>
       </c>
       <c r="B97" t="str">
-        <v>2015-03-29</v>
+        <v>2015-12-31</v>
       </c>
       <c r="C97" t="str">
-        <v>大连 s</v>
+        <v>天津·刘若英跨年演唱会 昱</v>
       </c>
       <c r="D97" t="str">
-        <v>旅行</v>
+        <v>观演</v>
       </c>
       <c r="E97" t="str">
+        <v/>
+      </c>
+      <c r="F97" t="str">
+        <v/>
+      </c>
+      <c r="G97" t="str">
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2015-03-27</v>
+        <v>2015-10-01</v>
       </c>
       <c r="B98" t="str">
-        <v>2015-03-27</v>
+        <v>2015-10-07</v>
       </c>
       <c r="C98" t="str">
-        <v>北京接 s</v>
+        <v>大连 s</v>
       </c>
       <c r="D98" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E98" t="str">
+        <v/>
+      </c>
+      <c r="F98" t="str">
+        <v/>
+      </c>
+      <c r="G98" t="str">
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2014-11-21</v>
+        <v>2015-06-09</v>
       </c>
       <c r="B99" t="str">
-        <v>2014-11-23</v>
+        <v>2015-06-14</v>
       </c>
       <c r="C99" t="str">
-        <v>天津旅游s</v>
+        <v>大连 s</v>
       </c>
       <c r="D99" t="str">
         <v>旅行</v>
       </c>
       <c r="E99" t="str">
+        <v/>
+      </c>
+      <c r="F99" t="str">
+        <v/>
+      </c>
+      <c r="G99" t="str">
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2014-11-10</v>
+        <v>2015-06-06</v>
       </c>
       <c r="B100" t="str">
-        <v>2014-11-30</v>
+        <v>2015-06-08</v>
       </c>
       <c r="C100" t="str">
-        <v>北京转车聚 新地标租房</v>
+        <v>湘西·凤凰古城</v>
       </c>
       <c r="D100" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E100" t="str">
+        <v/>
+      </c>
+      <c r="F100" t="str">
+        <v/>
+      </c>
+      <c r="G100" t="str">
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2014-10-01</v>
+        <v>2015-05-18</v>
       </c>
       <c r="B101" t="str">
-        <v>2014-10-01</v>
+        <v>2016-07-16</v>
       </c>
       <c r="C101" t="str">
-        <v>青海聚五姨</v>
+        <v>永泰东里16-6-601</v>
       </c>
       <c r="D101" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E101" t="str">
+        <v>11500</v>
+      </c>
+      <c r="F101" t="str">
+        <v/>
+      </c>
+      <c r="G101" t="str">
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2014-05-18</v>
+        <v>2015-05-01</v>
       </c>
       <c r="B102" t="str">
-        <v>2015-05-18</v>
+        <v>2015-05-03</v>
       </c>
       <c r="C102" t="str">
-        <v>永泰庄22-2-301</v>
+        <v>大连·游 s</v>
       </c>
       <c r="D102" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E102" t="str">
-        <v>10400</v>
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2014-05-01</v>
+        <v>2015-03-28</v>
       </c>
       <c r="B103" t="str">
-        <v>2014-05-01</v>
+        <v>2015-03-29</v>
       </c>
       <c r="C103" t="str">
-        <v>青海聚</v>
+        <v>大连 s</v>
       </c>
       <c r="D103" t="str">
         <v>旅行</v>
       </c>
       <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
         <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-27</v>
       </c>
       <c r="B104" t="str">
-        <v>2014-03-27</v>
+        <v>2015-03-27</v>
       </c>
       <c r="C104" t="str">
-        <v>二次入职世代泉源</v>
+        <v>北京接 s</v>
       </c>
       <c r="D104" t="str">
-        <v>工作</v>
+        <v>其他</v>
       </c>
       <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-21</v>
       </c>
       <c r="B105" t="str">
-        <v>2014-05-18</v>
+        <v>2014-11-23</v>
       </c>
       <c r="C105" t="str">
-        <v>清缘商厦</v>
+        <v>天津旅游s</v>
       </c>
       <c r="D105" t="str">
-        <v>居住</v>
+        <v>旅行</v>
       </c>
       <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2014-03-20</v>
+        <v>2014-11-10</v>
       </c>
       <c r="B106" t="str">
-        <v>2014-03-22</v>
+        <v>2014-11-30</v>
       </c>
       <c r="C106" t="str">
-        <v>上海韩后全智贤</v>
+        <v>北京转车聚 新地标租房</v>
       </c>
       <c r="D106" t="str">
-        <v>观演</v>
+        <v>其他</v>
       </c>
       <c r="E106" t="str">
+        <v/>
+      </c>
+      <c r="F106" t="str">
+        <v/>
+      </c>
+      <c r="G106" t="str">
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2013-11-26</v>
+        <v>2014-10-01</v>
       </c>
       <c r="B107" t="str">
-        <v>2013-11-26</v>
+        <v>2014-10-01</v>
       </c>
       <c r="C107" t="str">
-        <v>大连和s小聚</v>
+        <v>青海聚五姨</v>
       </c>
       <c r="D107" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E107" t="str">
+        <v/>
+      </c>
+      <c r="F107" t="str">
+        <v/>
+      </c>
+      <c r="G107" t="str">
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2013-06-11</v>
+        <v>2014-05-18</v>
       </c>
       <c r="B108" t="str">
-        <v>2013-09-16</v>
+        <v>2015-05-18</v>
       </c>
       <c r="C108" t="str">
-        <v>青海聚</v>
+        <v>永泰庄22-2-301</v>
       </c>
       <c r="D108" t="str">
-        <v>旅行</v>
+        <v>居住</v>
       </c>
       <c r="E108" t="str">
+        <v>10400</v>
+      </c>
+      <c r="F108" t="str">
+        <v/>
+      </c>
+      <c r="G108" t="str">
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2013-06-08</v>
+        <v>2014-05-01</v>
       </c>
       <c r="B109" t="str">
-        <v>2014-03-26</v>
+        <v>2014-05-01</v>
       </c>
       <c r="C109" t="str">
-        <v>待业291天</v>
+        <v>青海聚</v>
       </c>
       <c r="D109" t="str">
-        <v>其他</v>
+        <v>旅行</v>
       </c>
       <c r="E109" t="str">
-        <v>291天</v>
+        <v/>
+      </c>
+      <c r="F109" t="str">
+        <v/>
+      </c>
+      <c r="G109" t="str">
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2013-06-07</v>
+        <v>2014-03-27</v>
       </c>
       <c r="B110" t="str">
-        <v>2013-09-16</v>
+        <v>2014-03-27</v>
       </c>
       <c r="C110" t="str">
-        <v>青海·海石湾</v>
+        <v>二次入职世代泉源</v>
       </c>
       <c r="D110" t="str">
-        <v>居住</v>
+        <v>工作</v>
       </c>
       <c r="E110" t="str">
         <v/>
+      </c>
+      <c r="F110" t="str">
+        <v/>
+      </c>
+      <c r="G110" t="str">
+        <v>★</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2013-02-01</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B111" t="str">
-        <v>2013-02-01</v>
+        <v>2014-05-18</v>
       </c>
       <c r="C111" t="str">
-        <v>不详s至青海转乘 北京聚</v>
+        <v>清缘商厦</v>
       </c>
       <c r="D111" t="str">
-        <v>其他</v>
+        <v>居住</v>
       </c>
       <c r="E111" t="str">
+        <v/>
+      </c>
+      <c r="F111" t="str">
+        <v/>
+      </c>
+      <c r="G111" t="str">
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2012-12-07</v>
+        <v>2014-03-20</v>
       </c>
       <c r="B112" t="str">
-        <v>2013-06-08</v>
+        <v>2014-03-22</v>
       </c>
       <c r="C112" t="str">
-        <v>北京清河永泰庄新地标32-12</v>
+        <v>上海韩后全智贤</v>
       </c>
       <c r="D112" t="str">
-        <v>居住</v>
+        <v>观演</v>
       </c>
       <c r="E112" t="str">
+        <v/>
+      </c>
+      <c r="F112" t="str">
+        <v/>
+      </c>
+      <c r="G112" t="str">
         <v/>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2012-11-04</v>
+        <v>2013-11-26</v>
       </c>
       <c r="B113" t="str">
-        <v>2012-11-04</v>
+        <v>2013-11-26</v>
       </c>
       <c r="C113" t="str">
-        <v>北京送返鸡西</v>
+        <v>大连和s小聚</v>
       </c>
       <c r="D113" t="str">
         <v>其他</v>
@@ -2328,50 +3003,68 @@
       <c r="E113" t="str">
         <v/>
       </c>
+      <c r="F113" t="str">
+        <v/>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2012-09-24</v>
+        <v>2013-06-11</v>
       </c>
       <c r="B114" t="str">
-        <v>2012-09-24</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C114" t="str">
-        <v>入职世代泉源</v>
+        <v>青海聚</v>
       </c>
       <c r="D114" t="str">
-        <v>工作</v>
+        <v>旅行</v>
       </c>
       <c r="E114" t="str">
+        <v/>
+      </c>
+      <c r="F114" t="str">
+        <v/>
+      </c>
+      <c r="G114" t="str">
         <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2012-08-21</v>
+        <v>2013-06-08</v>
       </c>
       <c r="B115" t="str">
-        <v>2012-08-23</v>
+        <v>2014-03-26</v>
       </c>
       <c r="C115" t="str">
-        <v>辽宁兴城</v>
+        <v>待业291天</v>
       </c>
       <c r="D115" t="str">
-        <v>居住</v>
+        <v>其他</v>
       </c>
       <c r="E115" t="str">
+        <v>291天</v>
+      </c>
+      <c r="F115" t="str">
+        <v/>
+      </c>
+      <c r="G115" t="str">
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2012-02-07</v>
+        <v>2013-06-07</v>
       </c>
       <c r="B116" t="str">
-        <v>2012-11-29</v>
+        <v>2013-09-16</v>
       </c>
       <c r="C116" t="str">
-        <v>北京清河永泰庄新地标31-9-5</v>
+        <v>青海·海石湾</v>
       </c>
       <c r="D116" t="str">
         <v>居住</v>
@@ -2379,16 +3072,22 @@
       <c r="E116" t="str">
         <v/>
       </c>
+      <c r="F116" t="str">
+        <v/>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2012-02-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="B117" t="str">
-        <v>2012-02-01</v>
+        <v>2013-02-01</v>
       </c>
       <c r="C117" t="str">
-        <v>北京接站sister</v>
+        <v>不详s至青海转乘 北京聚</v>
       </c>
       <c r="D117" t="str">
         <v>其他</v>
@@ -2396,78 +3095,629 @@
       <c r="E117" t="str">
         <v/>
       </c>
+      <c r="F117" t="str">
+        <v/>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2010-07-20</v>
+        <v>2012-12-07</v>
       </c>
       <c r="B118" t="str">
-        <v>2012-02-01</v>
+        <v>2013-06-08</v>
       </c>
       <c r="C118" t="str">
-        <v>北京清河宝盛西里</v>
+        <v>北京清河永泰庄新地标32-12</v>
       </c>
       <c r="D118" t="str">
         <v>居住</v>
       </c>
       <c r="E118" t="str">
-        <v>宿舍</v>
+        <v/>
+      </c>
+      <c r="F118" t="str">
+        <v/>
+      </c>
+      <c r="G118" t="str">
+        <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2010-07-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="B119" t="str">
-        <v>2011-12-01</v>
+        <v>2012-11-04</v>
       </c>
       <c r="C119" t="str">
-        <v>北京北大青鸟</v>
+        <v>北京送返鸡西</v>
       </c>
       <c r="D119" t="str">
-        <v>学业</v>
+        <v>其他</v>
       </c>
       <c r="E119" t="str">
+        <v/>
+      </c>
+      <c r="F119" t="str">
+        <v/>
+      </c>
+      <c r="G119" t="str">
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2010-06-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="B120" t="str">
-        <v>2010-06-01</v>
+        <v>2012-09-24</v>
       </c>
       <c r="C120" t="str">
-        <v>高考</v>
+        <v>入职世代泉源</v>
       </c>
       <c r="D120" t="str">
-        <v>学业</v>
+        <v>工作</v>
       </c>
       <c r="E120" t="str">
         <v/>
+      </c>
+      <c r="F120" t="str">
+        <v/>
+      </c>
+      <c r="G120" t="str">
+        <v>★</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
+        <v>2012-08-21</v>
+      </c>
+      <c r="B121" t="str">
+        <v>2012-08-23</v>
+      </c>
+      <c r="C121" t="str">
+        <v>辽宁兴城</v>
+      </c>
+      <c r="D121" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E121" t="str">
+        <v/>
+      </c>
+      <c r="F121" t="str">
+        <v/>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>2012-02-07</v>
+      </c>
+      <c r="B122" t="str">
+        <v>2012-11-29</v>
+      </c>
+      <c r="C122" t="str">
+        <v>北京清河永泰庄新地标31-9-5</v>
+      </c>
+      <c r="D122" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E122" t="str">
+        <v/>
+      </c>
+      <c r="F122" t="str">
+        <v/>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="B123" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C123" t="str">
+        <v>北京接站sister</v>
+      </c>
+      <c r="D123" t="str">
+        <v>其他</v>
+      </c>
+      <c r="E123" t="str">
+        <v/>
+      </c>
+      <c r="F123" t="str">
+        <v/>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>2010-07-20</v>
+      </c>
+      <c r="B124" t="str">
+        <v>2012-02-01</v>
+      </c>
+      <c r="C124" t="str">
+        <v>北京清河宝盛西里</v>
+      </c>
+      <c r="D124" t="str">
+        <v>居住</v>
+      </c>
+      <c r="E124" t="str">
+        <v>宿舍</v>
+      </c>
+      <c r="F124" t="str">
+        <v/>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>2010-07-01</v>
+      </c>
+      <c r="B125" t="str">
+        <v>2011-12-01</v>
+      </c>
+      <c r="C125" t="str">
+        <v>北京北大青鸟</v>
+      </c>
+      <c r="D125" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E125" t="str">
+        <v/>
+      </c>
+      <c r="F125" t="str">
+        <v/>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="B126" t="str">
+        <v>2010-06-01</v>
+      </c>
+      <c r="C126" t="str">
+        <v>高考</v>
+      </c>
+      <c r="D126" t="str">
+        <v>学业</v>
+      </c>
+      <c r="E126" t="str">
+        <v/>
+      </c>
+      <c r="F126" t="str">
+        <v/>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="B121" t="str">
+      <c r="B127" t="str">
         <v>2010-01-01</v>
       </c>
-      <c r="C121" t="str">
+      <c r="C127" t="str">
         <v>YY语音相识·若</v>
       </c>
-      <c r="D121" t="str">
+      <c r="D127" t="str">
         <v>其他</v>
       </c>
-      <c r="E121" t="str">
+      <c r="E127" t="str">
+        <v/>
+      </c>
+      <c r="F127" t="str">
+        <v/>
+      </c>
+      <c r="G127" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G127"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B46"/>
+  <cols>
+    <col min="1" max="1" width="10.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>类型</v>
+      </c>
+      <c r="B1" t="str">
+        <v>词</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B2" t="str">
+        <v>结婚</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B3" t="str">
+        <v>离婚</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B4" t="str">
+        <v>订婚</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B5" t="str">
+        <v>婚礼</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B6" t="str">
+        <v>怀孕</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B7" t="str">
+        <v>出生</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B8" t="str">
+        <v>去世</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B9" t="str">
+        <v>逝世</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B10" t="str">
+        <v>离世</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B11" t="str">
+        <v>入学</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B12" t="str">
+        <v>开学</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B13" t="str">
+        <v>毕业</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B14" t="str">
+        <v>考研</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B15" t="str">
+        <v>读研</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B16" t="str">
+        <v>博士</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B17" t="str">
+        <v>留学</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B18" t="str">
+        <v>入职</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B19" t="str">
+        <v>离职</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B20" t="str">
+        <v>辞职</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B21" t="str">
+        <v>跳槽</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B22" t="str">
+        <v>升职</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B23" t="str">
+        <v>转正</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B24" t="str">
+        <v>裁员</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B25" t="str">
+        <v>失业</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B26" t="str">
+        <v>退休</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B27" t="str">
+        <v>创业</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B28" t="str">
+        <v>融资</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B29" t="str">
+        <v>上市</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B30" t="str">
+        <v>倒闭</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B31" t="str">
+        <v>搬家</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B32" t="str">
+        <v>搬进</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B33" t="str">
+        <v>搬出</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B34" t="str">
+        <v>落户</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B35" t="str">
+        <v>买房</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B36" t="str">
+        <v>卖房</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B37" t="str">
+        <v>装修</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B38" t="str">
+        <v>确诊</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B39" t="str">
+        <v>住院</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B40" t="str">
+        <v>手术</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B41" t="str">
+        <v>康复</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B42" t="str">
+        <v>车祸</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B43" t="str">
+        <v>获奖</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B44" t="str">
+        <v>冠军</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>关键词</v>
+      </c>
+      <c r="B45" t="str">
+        <v>夺冠</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>排除词</v>
+      </c>
+      <c r="B46" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B46"/>
   </ignoredErrors>
 </worksheet>
 </file>